--- a/uploads/ORIGINAL7.xlsx
+++ b/uploads/ORIGINAL7.xlsx
@@ -22049,8 +22049,8 @@
       <c r="O8" s="196" t="s">
         <v>47</v>
       </c>
-      <c r="P8" s="196" t="s">
-        <v>47</v>
+      <c r="P8" s="57" t="s">
+        <v>48</v>
       </c>
       <c r="Q8" s="196" t="s">
         <v>47</v>
@@ -22123,11 +22123,11 @@
       </c>
       <c r="AM8" s="51">
         <f t="shared" si="7"/>
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AN8" s="52">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO8" s="52">
         <f t="shared" si="9"/>
@@ -27636,7 +27636,7 @@
       </c>
       <c r="P50" s="238">
         <f t="shared" si="10"/>
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Q50" s="238">
         <f t="shared" si="10"/>
@@ -28476,7 +28476,7 @@
       </c>
       <c r="P56" s="140">
         <f t="shared" si="16"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q56" s="140">
         <f t="shared" si="16"/>
@@ -28756,7 +28756,7 @@
       </c>
       <c r="P58" s="242">
         <f t="shared" si="18"/>
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Q58" s="242">
         <f t="shared" si="18"/>
@@ -41377,7 +41377,7 @@
         <v>47</v>
       </c>
       <c r="P6" s="246" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="Q6" s="246" t="s">
         <v>47</v>
@@ -50261,7 +50261,7 @@
         <v>28.0</v>
       </c>
       <c r="O3" s="245">
-        <v>28.0</v>
+        <v>27.0</v>
       </c>
       <c r="P3" s="245">
         <v>26.0</v>
@@ -50831,7 +50831,7 @@
         <v>0.0</v>
       </c>
       <c r="O9" s="245">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="P9" s="245">
         <v>0.0</v>
@@ -51021,7 +51021,7 @@
         <v>28.0</v>
       </c>
       <c r="O11" s="245">
-        <v>28.0</v>
+        <v>27.0</v>
       </c>
       <c r="P11" s="245">
         <v>26.0</v>

--- a/uploads/ORIGINAL7.xlsx
+++ b/uploads/ORIGINAL7.xlsx
@@ -2245,14 +2245,14 @@
     <xf borderId="11" fillId="0" fontId="36" numFmtId="49" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
-    <xf borderId="19" fillId="0" fontId="36" numFmtId="49" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf borderId="19" fillId="2" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
     <xf borderId="11" fillId="0" fontId="13" numFmtId="49" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
+    </xf>
+    <xf borderId="19" fillId="0" fontId="36" numFmtId="49" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf borderId="11" fillId="2" fontId="37" numFmtId="49" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
@@ -21644,8 +21644,8 @@
       <c r="P5" s="196" t="s">
         <v>47</v>
       </c>
-      <c r="Q5" s="196" t="s">
-        <v>47</v>
+      <c r="Q5" s="57" t="s">
+        <v>48</v>
       </c>
       <c r="R5" s="194" t="s">
         <v>53</v>
@@ -21715,7 +21715,7 @@
       </c>
       <c r="AM5" s="51">
         <f t="shared" ref="AM5:AM46" si="7">COUNTIF($C5:$AD5,"A2")</f>
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AN5" s="52">
         <f t="shared" ref="AN5:AO5" si="1">COUNTIF($C5:$AD5,"PH")</f>
@@ -22188,8 +22188,8 @@
       <c r="P9" s="196" t="s">
         <v>47</v>
       </c>
-      <c r="Q9" s="201" t="s">
-        <v>49</v>
+      <c r="Q9" s="196" t="s">
+        <v>47</v>
       </c>
       <c r="R9" s="194" t="s">
         <v>53</v>
@@ -22259,7 +22259,7 @@
       </c>
       <c r="AM9" s="51">
         <f t="shared" si="7"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AN9" s="52">
         <f t="shared" si="8"/>
@@ -22267,7 +22267,7 @@
       </c>
       <c r="AO9" s="52">
         <f t="shared" si="9"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP9" s="67"/>
       <c r="AQ9" s="67"/>
@@ -22321,8 +22321,8 @@
       <c r="O10" s="196" t="s">
         <v>47</v>
       </c>
-      <c r="P10" s="194" t="s">
-        <v>53</v>
+      <c r="P10" s="196" t="s">
+        <v>47</v>
       </c>
       <c r="Q10" s="196" t="s">
         <v>47</v>
@@ -22330,8 +22330,8 @@
       <c r="R10" s="196" t="s">
         <v>47</v>
       </c>
-      <c r="S10" s="196" t="s">
-        <v>47</v>
+      <c r="S10" s="194" t="s">
+        <v>53</v>
       </c>
       <c r="T10" s="199" t="s">
         <v>53</v>
@@ -22593,8 +22593,8 @@
       <c r="O12" s="196" t="s">
         <v>47</v>
       </c>
-      <c r="P12" s="196" t="s">
-        <v>47</v>
+      <c r="P12" s="194" t="s">
+        <v>53</v>
       </c>
       <c r="Q12" s="196" t="s">
         <v>47</v>
@@ -22602,8 +22602,8 @@
       <c r="R12" s="196" t="s">
         <v>47</v>
       </c>
-      <c r="S12" s="195" t="s">
-        <v>53</v>
+      <c r="S12" s="196" t="s">
+        <v>47</v>
       </c>
       <c r="T12" s="199" t="s">
         <v>53</v>
@@ -22907,14 +22907,14 @@
       <c r="AC14" s="196" t="s">
         <v>47</v>
       </c>
-      <c r="AD14" s="201" t="s">
-        <v>49</v>
-      </c>
-      <c r="AE14" s="201" t="s">
-        <v>49</v>
-      </c>
-      <c r="AF14" s="204" t="s">
-        <v>49</v>
+      <c r="AD14" s="57" t="s">
+        <v>48</v>
+      </c>
+      <c r="AE14" s="57" t="s">
+        <v>48</v>
+      </c>
+      <c r="AF14" s="57" t="s">
+        <v>48</v>
       </c>
       <c r="AG14" s="25"/>
       <c r="AH14" s="47">
@@ -22943,11 +22943,11 @@
       </c>
       <c r="AN14" s="52">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO14" s="52">
         <f t="shared" si="9"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AP14" s="67"/>
       <c r="AQ14" s="67"/>
@@ -23031,7 +23031,7 @@
       <c r="Y15" s="196" t="s">
         <v>47</v>
       </c>
-      <c r="Z15" s="205" t="s">
+      <c r="Z15" s="204" t="s">
         <v>47</v>
       </c>
       <c r="AA15" s="199" t="s">
@@ -23173,7 +23173,7 @@
       <c r="AA16" s="193" t="s">
         <v>47</v>
       </c>
-      <c r="AB16" s="206" t="s">
+      <c r="AB16" s="205" t="s">
         <v>47</v>
       </c>
       <c r="AC16" s="194" t="s">
@@ -23261,7 +23261,7 @@
       <c r="K17" s="194" t="s">
         <v>53</v>
       </c>
-      <c r="L17" s="204" t="s">
+      <c r="L17" s="206" t="s">
         <v>49</v>
       </c>
       <c r="M17" s="193" t="s">
@@ -23282,7 +23282,7 @@
       <c r="R17" s="194" t="s">
         <v>53</v>
       </c>
-      <c r="S17" s="204" t="s">
+      <c r="S17" s="206" t="s">
         <v>49</v>
       </c>
       <c r="T17" s="193" t="s">
@@ -23729,7 +23729,7 @@
       <c r="AE20" s="194" t="s">
         <v>53</v>
       </c>
-      <c r="AF20" s="205" t="s">
+      <c r="AF20" s="204" t="s">
         <v>47</v>
       </c>
       <c r="AG20" s="25"/>
@@ -23805,7 +23805,7 @@
       <c r="K21" s="194" t="s">
         <v>53</v>
       </c>
-      <c r="L21" s="205" t="s">
+      <c r="L21" s="204" t="s">
         <v>47</v>
       </c>
       <c r="M21" s="198" t="s">
@@ -23847,7 +23847,7 @@
       <c r="Y21" s="194" t="s">
         <v>53</v>
       </c>
-      <c r="Z21" s="204" t="s">
+      <c r="Z21" s="206" t="s">
         <v>49</v>
       </c>
       <c r="AA21" s="202" t="s">
@@ -24001,7 +24001,7 @@
       <c r="AE22" s="194" t="s">
         <v>53</v>
       </c>
-      <c r="AF22" s="205" t="s">
+      <c r="AF22" s="204" t="s">
         <v>47</v>
       </c>
       <c r="AG22" s="25"/>
@@ -24056,7 +24056,7 @@
       <c r="D23" s="194" t="s">
         <v>53</v>
       </c>
-      <c r="E23" s="204" t="s">
+      <c r="E23" s="206" t="s">
         <v>49</v>
       </c>
       <c r="F23" s="193" t="s">
@@ -24077,7 +24077,7 @@
       <c r="K23" s="194" t="s">
         <v>53</v>
       </c>
-      <c r="L23" s="205" t="s">
+      <c r="L23" s="204" t="s">
         <v>47</v>
       </c>
       <c r="M23" s="198" t="s">
@@ -24098,7 +24098,7 @@
       <c r="R23" s="194" t="s">
         <v>53</v>
       </c>
-      <c r="S23" s="205" t="s">
+      <c r="S23" s="204" t="s">
         <v>47</v>
       </c>
       <c r="T23" s="198" t="s">
@@ -24119,7 +24119,7 @@
       <c r="Y23" s="194" t="s">
         <v>53</v>
       </c>
-      <c r="Z23" s="205" t="s">
+      <c r="Z23" s="204" t="s">
         <v>47</v>
       </c>
       <c r="AA23" s="193" t="s">
@@ -24192,7 +24192,7 @@
       <c r="D24" s="197" t="s">
         <v>47</v>
       </c>
-      <c r="E24" s="205" t="s">
+      <c r="E24" s="204" t="s">
         <v>47</v>
       </c>
       <c r="F24" s="198" t="s">
@@ -24328,7 +24328,7 @@
       <c r="D25" s="194" t="s">
         <v>53</v>
       </c>
-      <c r="E25" s="204" t="s">
+      <c r="E25" s="206" t="s">
         <v>49</v>
       </c>
       <c r="F25" s="193" t="s">
@@ -24349,7 +24349,7 @@
       <c r="K25" s="194" t="s">
         <v>53</v>
       </c>
-      <c r="L25" s="204" t="s">
+      <c r="L25" s="206" t="s">
         <v>49</v>
       </c>
       <c r="M25" s="193" t="s">
@@ -24370,7 +24370,7 @@
       <c r="R25" s="194" t="s">
         <v>53</v>
       </c>
-      <c r="S25" s="204" t="s">
+      <c r="S25" s="206" t="s">
         <v>49</v>
       </c>
       <c r="T25" s="193" t="s">
@@ -24464,7 +24464,7 @@
       <c r="D26" s="197" t="s">
         <v>47</v>
       </c>
-      <c r="E26" s="205" t="s">
+      <c r="E26" s="204" t="s">
         <v>47</v>
       </c>
       <c r="F26" s="193" t="s">
@@ -24600,7 +24600,7 @@
       <c r="D27" s="197" t="s">
         <v>47</v>
       </c>
-      <c r="E27" s="205" t="s">
+      <c r="E27" s="204" t="s">
         <v>47</v>
       </c>
       <c r="F27" s="198" t="s">
@@ -24621,7 +24621,7 @@
       <c r="K27" s="197" t="s">
         <v>47</v>
       </c>
-      <c r="L27" s="205" t="s">
+      <c r="L27" s="204" t="s">
         <v>47</v>
       </c>
       <c r="M27" s="198" t="s">
@@ -24663,7 +24663,7 @@
       <c r="Y27" s="201" t="s">
         <v>49</v>
       </c>
-      <c r="Z27" s="204" t="s">
+      <c r="Z27" s="206" t="s">
         <v>49</v>
       </c>
       <c r="AA27" s="202" t="s">
@@ -24914,7 +24914,7 @@
       <c r="R29" s="196" t="s">
         <v>47</v>
       </c>
-      <c r="S29" s="205" t="s">
+      <c r="S29" s="204" t="s">
         <v>47</v>
       </c>
       <c r="T29" s="199" t="s">
@@ -24935,7 +24935,7 @@
       <c r="Y29" s="196" t="s">
         <v>47</v>
       </c>
-      <c r="Z29" s="205" t="s">
+      <c r="Z29" s="204" t="s">
         <v>47</v>
       </c>
       <c r="AA29" s="199" t="s">
@@ -25186,7 +25186,7 @@
       <c r="R31" s="196" t="s">
         <v>47</v>
       </c>
-      <c r="S31" s="205" t="s">
+      <c r="S31" s="204" t="s">
         <v>47</v>
       </c>
       <c r="T31" s="199" t="s">
@@ -25207,7 +25207,7 @@
       <c r="Y31" s="196" t="s">
         <v>47</v>
       </c>
-      <c r="Z31" s="205" t="s">
+      <c r="Z31" s="204" t="s">
         <v>47</v>
       </c>
       <c r="AA31" s="199" t="s">
@@ -25416,7 +25416,7 @@
       <c r="D33" s="201" t="s">
         <v>49</v>
       </c>
-      <c r="E33" s="204" t="s">
+      <c r="E33" s="206" t="s">
         <v>49</v>
       </c>
       <c r="F33" s="60" t="s">
@@ -25690,7 +25690,7 @@
       <c r="D35" s="196" t="s">
         <v>47</v>
       </c>
-      <c r="E35" s="205" t="s">
+      <c r="E35" s="204" t="s">
         <v>47</v>
       </c>
       <c r="F35" s="198" t="s">
@@ -25983,7 +25983,7 @@
       <c r="K37" s="197" t="s">
         <v>47</v>
       </c>
-      <c r="L37" s="205" t="s">
+      <c r="L37" s="204" t="s">
         <v>47</v>
       </c>
       <c r="M37" s="199" t="s">
@@ -26004,7 +26004,7 @@
       <c r="R37" s="196" t="s">
         <v>47</v>
       </c>
-      <c r="S37" s="205" t="s">
+      <c r="S37" s="204" t="s">
         <v>47</v>
       </c>
       <c r="T37" s="199" t="s">
@@ -26255,7 +26255,7 @@
       <c r="K39" s="196" t="s">
         <v>47</v>
       </c>
-      <c r="L39" s="205" t="s">
+      <c r="L39" s="204" t="s">
         <v>47</v>
       </c>
       <c r="M39" s="199" t="s">
@@ -26264,7 +26264,7 @@
       <c r="N39" s="194" t="s">
         <v>53</v>
       </c>
-      <c r="O39" s="204" t="s">
+      <c r="O39" s="206" t="s">
         <v>49</v>
       </c>
       <c r="P39" s="196" t="s">
@@ -26276,7 +26276,7 @@
       <c r="R39" s="196" t="s">
         <v>47</v>
       </c>
-      <c r="S39" s="204" t="s">
+      <c r="S39" s="206" t="s">
         <v>49</v>
       </c>
       <c r="T39" s="199" t="s">
@@ -26297,7 +26297,7 @@
       <c r="Y39" s="196" t="s">
         <v>47</v>
       </c>
-      <c r="Z39" s="205" t="s">
+      <c r="Z39" s="204" t="s">
         <v>47</v>
       </c>
       <c r="AA39" s="199" t="s">
@@ -26684,7 +26684,7 @@
       <c r="R42" s="196" t="s">
         <v>47</v>
       </c>
-      <c r="S42" s="205" t="s">
+      <c r="S42" s="204" t="s">
         <v>47</v>
       </c>
       <c r="T42" s="211" t="s">
@@ -26826,10 +26826,10 @@
       <c r="T43" s="193" t="s">
         <v>47</v>
       </c>
-      <c r="U43" s="204" t="s">
+      <c r="U43" s="206" t="s">
         <v>49</v>
       </c>
-      <c r="V43" s="204" t="s">
+      <c r="V43" s="206" t="s">
         <v>49</v>
       </c>
       <c r="W43" s="194" t="s">
@@ -27050,7 +27050,7 @@
       <c r="D45" s="201" t="s">
         <v>49</v>
       </c>
-      <c r="E45" s="204" t="s">
+      <c r="E45" s="206" t="s">
         <v>49</v>
       </c>
       <c r="F45" s="211" t="s">
@@ -27131,7 +27131,7 @@
       <c r="AE45" s="194" t="s">
         <v>53</v>
       </c>
-      <c r="AF45" s="204" t="s">
+      <c r="AF45" s="206" t="s">
         <v>49</v>
       </c>
       <c r="AG45" s="112"/>
@@ -28480,7 +28480,7 @@
       </c>
       <c r="Q56" s="140">
         <f t="shared" si="16"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R56" s="140">
         <f t="shared" si="16"/>
@@ -28532,15 +28532,15 @@
       </c>
       <c r="AD56" s="140">
         <f t="shared" si="16"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AE56" s="140">
         <f t="shared" si="16"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AF56" s="141">
         <f t="shared" si="16"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG56" s="183"/>
       <c r="AH56" s="20"/>
@@ -28620,7 +28620,7 @@
       </c>
       <c r="Q57" s="140">
         <f t="shared" si="17"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R57" s="140">
         <f t="shared" si="17"/>
@@ -28672,15 +28672,15 @@
       </c>
       <c r="AD57" s="140">
         <f t="shared" si="17"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AE57" s="140">
         <f t="shared" si="17"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AF57" s="141">
         <f t="shared" si="17"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AG57" s="183"/>
       <c r="AH57" s="20"/>
@@ -41080,7 +41080,7 @@
         <v>47</v>
       </c>
       <c r="Q3" s="246" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="R3" s="246" t="s">
         <v>53</v>
@@ -41480,7 +41480,7 @@
         <v>47</v>
       </c>
       <c r="Q7" s="246" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="R7" s="246" t="s">
         <v>53</v>
@@ -41577,7 +41577,7 @@
         <v>47</v>
       </c>
       <c r="P8" s="246" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="Q8" s="246" t="s">
         <v>47</v>
@@ -41586,7 +41586,7 @@
         <v>47</v>
       </c>
       <c r="S8" s="246" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="T8" s="246" t="s">
         <v>53</v>
@@ -41777,7 +41777,7 @@
         <v>47</v>
       </c>
       <c r="P10" s="246" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="Q10" s="246" t="s">
         <v>47</v>
@@ -41786,7 +41786,7 @@
         <v>47</v>
       </c>
       <c r="S10" s="246" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="T10" s="246" t="s">
         <v>53</v>
@@ -42019,13 +42019,13 @@
         <v>47</v>
       </c>
       <c r="AD12" s="246" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="AE12" s="246" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="AF12" s="246" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="AG12" s="245"/>
       <c r="AH12" s="245"/>
@@ -50834,7 +50834,7 @@
         <v>1.0</v>
       </c>
       <c r="P9" s="245">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="Q9" s="245">
         <v>1.0</v>
@@ -50873,13 +50873,13 @@
         <v>4.0</v>
       </c>
       <c r="AC9" s="245">
+        <v>3.0</v>
+      </c>
+      <c r="AD9" s="245">
         <v>2.0</v>
       </c>
-      <c r="AD9" s="245">
+      <c r="AE9" s="245">
         <v>1.0</v>
-      </c>
-      <c r="AE9" s="245">
-        <v>0.0</v>
       </c>
     </row>
     <row r="10">
@@ -50929,7 +50929,7 @@
         <v>3.0</v>
       </c>
       <c r="P10" s="245">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="Q10" s="245">
         <v>1.0</v>
@@ -50968,13 +50968,13 @@
         <v>0.0</v>
       </c>
       <c r="AC10" s="245">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
       <c r="AD10" s="245">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="AE10" s="245">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="11">

--- a/uploads/ORIGINAL7.xlsx
+++ b/uploads/ORIGINAL7.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4487" uniqueCount="277">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4487" uniqueCount="276">
   <si>
     <t xml:space="preserve"> GA  MONTHLY ROSTER</t>
   </si>
@@ -837,9 +837,6 @@
     <t>*****</t>
   </si>
   <si>
-    <t>0</t>
-  </si>
-  <si>
     <t xml:space="preserve">OK </t>
   </si>
   <si>
@@ -1180,7 +1177,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="47">
+  <borders count="58">
     <border/>
     <border>
       <left/>
@@ -1656,11 +1653,165 @@
         <color rgb="FF000000"/>
       </bottom>
     </border>
+    <border>
+      <left style="thick">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thick">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thick">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thick">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thick">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thick">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thick">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thick">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thick">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thick">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thick">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thick">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thick">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thick">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thick">
+        <color rgb="FF000000"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thick">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thick">
+        <color rgb="FF000000"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thick">
+        <color rgb="FF000000"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thick">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thick">
+        <color rgb="FF000000"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="251">
+  <cellXfs count="264">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -2372,9 +2523,48 @@
     <xf borderId="11" fillId="0" fontId="32" numFmtId="49" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf borderId="11" fillId="0" fontId="32" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="11" fillId="0" fontId="32" numFmtId="49" xfId="0" applyBorder="1" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="11" fillId="0" fontId="32" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="32" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf borderId="47" fillId="0" fontId="32" numFmtId="49" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf borderId="48" fillId="0" fontId="32" numFmtId="49" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf borderId="49" fillId="0" fontId="32" numFmtId="49" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf borderId="50" fillId="0" fontId="32" numFmtId="49" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf borderId="51" fillId="0" fontId="32" numFmtId="49" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf borderId="52" fillId="0" fontId="32" numFmtId="49" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf borderId="53" fillId="0" fontId="32" numFmtId="49" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf borderId="52" fillId="0" fontId="32" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf borderId="53" fillId="0" fontId="32" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf borderId="54" fillId="0" fontId="32" numFmtId="49" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf borderId="55" fillId="0" fontId="32" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf borderId="56" fillId="0" fontId="32" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf borderId="57" fillId="0" fontId="32" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center"/>
     </xf>
     <xf borderId="0" fillId="15" fontId="40" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
@@ -21659,14 +21849,14 @@
       <c r="U5" s="196" t="s">
         <v>47</v>
       </c>
-      <c r="V5" s="196" t="s">
-        <v>47</v>
-      </c>
-      <c r="W5" s="196" t="s">
-        <v>47</v>
-      </c>
-      <c r="X5" s="197" t="s">
-        <v>47</v>
+      <c r="V5" s="57" t="s">
+        <v>48</v>
+      </c>
+      <c r="W5" s="57" t="s">
+        <v>48</v>
+      </c>
+      <c r="X5" s="57" t="s">
+        <v>48</v>
       </c>
       <c r="Y5" s="194" t="s">
         <v>53</v>
@@ -21715,7 +21905,7 @@
       </c>
       <c r="AM5" s="51">
         <f t="shared" ref="AM5:AM46" si="7">COUNTIF($C5:$AD5,"A2")</f>
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AN5" s="52">
         <f t="shared" ref="AN5:AO5" si="1">COUNTIF($C5:$AD5,"PH")</f>
@@ -22155,11 +22345,11 @@
       <c r="E9" s="195" t="s">
         <v>53</v>
       </c>
-      <c r="F9" s="193" t="s">
-        <v>47</v>
-      </c>
-      <c r="G9" s="196" t="s">
-        <v>47</v>
+      <c r="F9" s="201" t="s">
+        <v>49</v>
+      </c>
+      <c r="G9" s="201" t="s">
+        <v>49</v>
       </c>
       <c r="H9" s="196" t="s">
         <v>47</v>
@@ -22259,7 +22449,7 @@
       </c>
       <c r="AM9" s="51">
         <f t="shared" si="7"/>
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AN9" s="52">
         <f t="shared" si="8"/>
@@ -22267,7 +22457,7 @@
       </c>
       <c r="AO9" s="52">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AP9" s="67"/>
       <c r="AQ9" s="67"/>
@@ -22436,8 +22626,8 @@
       <c r="H11" s="196" t="s">
         <v>47</v>
       </c>
-      <c r="I11" s="196" t="s">
-        <v>47</v>
+      <c r="I11" s="201" t="s">
+        <v>49</v>
       </c>
       <c r="J11" s="201" t="s">
         <v>49</v>
@@ -22460,8 +22650,8 @@
       <c r="P11" s="196" t="s">
         <v>47</v>
       </c>
-      <c r="Q11" s="201" t="s">
-        <v>49</v>
+      <c r="Q11" s="57" t="s">
+        <v>48</v>
       </c>
       <c r="R11" s="194" t="s">
         <v>53</v>
@@ -22531,11 +22721,11 @@
       </c>
       <c r="AM11" s="51">
         <f t="shared" si="7"/>
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AN11" s="52">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO11" s="52">
         <f t="shared" si="9"/>
@@ -23309,8 +23499,8 @@
       <c r="AA17" s="193" t="s">
         <v>47</v>
       </c>
-      <c r="AB17" s="57" t="s">
-        <v>48</v>
+      <c r="AB17" s="196" t="s">
+        <v>47</v>
       </c>
       <c r="AC17" s="57" t="s">
         <v>48</v>
@@ -23347,11 +23537,11 @@
       </c>
       <c r="AM17" s="51">
         <f t="shared" si="7"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AN17" s="52">
         <f t="shared" si="8"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AO17" s="52">
         <f t="shared" si="9"/>
@@ -23533,8 +23723,8 @@
       <c r="K19" s="194" t="s">
         <v>53</v>
       </c>
-      <c r="L19" s="200" t="s">
-        <v>47</v>
+      <c r="L19" s="201" t="s">
+        <v>49</v>
       </c>
       <c r="M19" s="193" t="s">
         <v>47</v>
@@ -23619,7 +23809,7 @@
       </c>
       <c r="AM19" s="51">
         <f t="shared" si="7"/>
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AN19" s="52">
         <f t="shared" si="8"/>
@@ -23627,7 +23817,7 @@
       </c>
       <c r="AO19" s="52">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP19" s="67"/>
       <c r="AQ19" s="67"/>
@@ -24089,8 +24279,8 @@
       <c r="O23" s="197" t="s">
         <v>47</v>
       </c>
-      <c r="P23" s="197" t="s">
-        <v>47</v>
+      <c r="P23" s="201" t="s">
+        <v>49</v>
       </c>
       <c r="Q23" s="194" t="s">
         <v>53</v>
@@ -24110,8 +24300,8 @@
       <c r="V23" s="197" t="s">
         <v>47</v>
       </c>
-      <c r="W23" s="197" t="s">
-        <v>47</v>
+      <c r="W23" s="201" t="s">
+        <v>49</v>
       </c>
       <c r="X23" s="194" t="s">
         <v>53</v>
@@ -24163,7 +24353,7 @@
       </c>
       <c r="AM23" s="51">
         <f t="shared" si="7"/>
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AN23" s="52">
         <f t="shared" si="8"/>
@@ -24171,7 +24361,7 @@
       </c>
       <c r="AO23" s="52">
         <f t="shared" si="9"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AP23" s="67"/>
       <c r="AQ23" s="67"/>
@@ -24331,8 +24521,8 @@
       <c r="E25" s="206" t="s">
         <v>49</v>
       </c>
-      <c r="F25" s="193" t="s">
-        <v>47</v>
+      <c r="F25" s="201" t="s">
+        <v>49</v>
       </c>
       <c r="G25" s="196" t="s">
         <v>47</v>
@@ -24349,8 +24539,8 @@
       <c r="K25" s="194" t="s">
         <v>53</v>
       </c>
-      <c r="L25" s="206" t="s">
-        <v>49</v>
+      <c r="L25" s="196" t="s">
+        <v>47</v>
       </c>
       <c r="M25" s="193" t="s">
         <v>47</v>
@@ -24361,8 +24551,8 @@
       <c r="O25" s="196" t="s">
         <v>47</v>
       </c>
-      <c r="P25" s="196" t="s">
-        <v>47</v>
+      <c r="P25" s="57" t="s">
+        <v>48</v>
       </c>
       <c r="Q25" s="194" t="s">
         <v>53</v>
@@ -24370,8 +24560,8 @@
       <c r="R25" s="194" t="s">
         <v>53</v>
       </c>
-      <c r="S25" s="206" t="s">
-        <v>49</v>
+      <c r="S25" s="57" t="s">
+        <v>48</v>
       </c>
       <c r="T25" s="193" t="s">
         <v>47</v>
@@ -24435,15 +24625,15 @@
       </c>
       <c r="AM25" s="51">
         <f t="shared" si="7"/>
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AN25" s="52">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AO25" s="52">
         <f t="shared" si="9"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AP25" s="67"/>
       <c r="AQ25" s="67"/>
@@ -24657,8 +24847,8 @@
       <c r="W27" s="196" t="s">
         <v>47</v>
       </c>
-      <c r="X27" s="201" t="s">
-        <v>49</v>
+      <c r="X27" s="196" t="s">
+        <v>47</v>
       </c>
       <c r="Y27" s="201" t="s">
         <v>49</v>
@@ -24707,7 +24897,7 @@
       </c>
       <c r="AM27" s="51">
         <f t="shared" si="7"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AN27" s="52">
         <f t="shared" si="8"/>
@@ -24715,7 +24905,7 @@
       </c>
       <c r="AO27" s="52">
         <f t="shared" si="9"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AP27" s="67"/>
       <c r="AQ27" s="67"/>
@@ -27255,8 +27445,8 @@
       <c r="AA46" s="216" t="s">
         <v>47</v>
       </c>
-      <c r="AB46" s="220" t="s">
-        <v>47</v>
+      <c r="AB46" s="57" t="s">
+        <v>48</v>
       </c>
       <c r="AC46" s="221" t="s">
         <v>53</v>
@@ -27293,11 +27483,11 @@
       </c>
       <c r="AM46" s="51">
         <f t="shared" si="7"/>
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AN46" s="52">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO46" s="52">
         <f t="shared" si="9"/>
@@ -27596,11 +27786,11 @@
       </c>
       <c r="F50" s="237">
         <f t="shared" si="10"/>
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="G50" s="238">
         <f t="shared" si="10"/>
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H50" s="238">
         <f t="shared" si="10"/>
@@ -27608,7 +27798,7 @@
       </c>
       <c r="I50" s="238">
         <f t="shared" si="10"/>
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="J50" s="238">
         <f t="shared" si="10"/>
@@ -27636,7 +27826,7 @@
       </c>
       <c r="P50" s="238">
         <f t="shared" si="10"/>
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="Q50" s="238">
         <f t="shared" si="10"/>
@@ -27660,11 +27850,11 @@
       </c>
       <c r="V50" s="238">
         <f t="shared" si="10"/>
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="W50" s="238">
         <f t="shared" si="10"/>
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="X50" s="238">
         <f t="shared" si="10"/>
@@ -27684,7 +27874,7 @@
       </c>
       <c r="AB50" s="238">
         <f t="shared" si="10"/>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AC50" s="238">
         <f t="shared" si="10"/>
@@ -28280,7 +28470,7 @@
     <row r="55" ht="22.5" customHeight="1">
       <c r="A55" s="231"/>
       <c r="B55" s="236" t="s">
-        <v>273</v>
+        <v>53</v>
       </c>
       <c r="C55" s="139">
         <f t="shared" ref="C55:AF55" si="15">COUNTIF(C5:C45,"O")</f>
@@ -28476,11 +28666,11 @@
       </c>
       <c r="P56" s="140">
         <f t="shared" si="16"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q56" s="140">
         <f t="shared" si="16"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R56" s="140">
         <f t="shared" si="16"/>
@@ -28488,7 +28678,7 @@
       </c>
       <c r="S56" s="141">
         <f t="shared" si="16"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T56" s="139">
         <f t="shared" si="16"/>
@@ -28500,15 +28690,15 @@
       </c>
       <c r="V56" s="140">
         <f t="shared" si="16"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W56" s="140">
         <f t="shared" si="16"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X56" s="140">
         <f t="shared" si="16"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y56" s="140">
         <f t="shared" si="16"/>
@@ -28524,7 +28714,7 @@
       </c>
       <c r="AB56" s="140">
         <f t="shared" si="16"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AC56" s="140">
         <f t="shared" si="16"/>
@@ -28576,11 +28766,11 @@
       </c>
       <c r="F57" s="139">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G57" s="140">
         <f t="shared" si="17"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H57" s="140">
         <f t="shared" si="17"/>
@@ -28588,7 +28778,7 @@
       </c>
       <c r="I57" s="140">
         <f t="shared" si="17"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J57" s="140">
         <f t="shared" si="17"/>
@@ -28616,11 +28806,11 @@
       </c>
       <c r="P57" s="140">
         <f t="shared" si="17"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q57" s="140">
         <f t="shared" si="17"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R57" s="140">
         <f t="shared" si="17"/>
@@ -28628,7 +28818,7 @@
       </c>
       <c r="S57" s="141">
         <f t="shared" si="17"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T57" s="139">
         <f t="shared" si="17"/>
@@ -28644,11 +28834,11 @@
       </c>
       <c r="W57" s="140">
         <f t="shared" si="17"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X57" s="140">
         <f t="shared" si="17"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y57" s="140">
         <f t="shared" si="17"/>
@@ -28716,11 +28906,11 @@
       </c>
       <c r="F58" s="241">
         <f t="shared" si="18"/>
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="G58" s="242">
         <f t="shared" si="18"/>
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H58" s="242">
         <f t="shared" si="18"/>
@@ -28728,7 +28918,7 @@
       </c>
       <c r="I58" s="242">
         <f t="shared" si="18"/>
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="J58" s="242">
         <f t="shared" si="18"/>
@@ -28756,7 +28946,7 @@
       </c>
       <c r="P58" s="242">
         <f t="shared" si="18"/>
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="Q58" s="242">
         <f t="shared" si="18"/>
@@ -28780,11 +28970,11 @@
       </c>
       <c r="V58" s="242">
         <f t="shared" si="18"/>
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="W58" s="242">
         <f t="shared" si="18"/>
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="X58" s="242">
         <f t="shared" si="18"/>
@@ -28804,7 +28994,7 @@
       </c>
       <c r="AB58" s="242">
         <f t="shared" si="18"/>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AC58" s="242">
         <f t="shared" si="18"/>
@@ -40828,7 +41018,7 @@
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
   <cols>
     <col customWidth="1" min="1" max="1" width="8.25"/>
-    <col customWidth="1" min="2" max="2" width="3.88"/>
+    <col customWidth="1" min="2" max="2" width="5.38"/>
     <col customWidth="1" min="3" max="3" width="5.75"/>
     <col customWidth="1" min="4" max="34" width="4.25"/>
   </cols>
@@ -40847,92 +41037,92 @@
       <c r="D1" s="246" t="s">
         <v>9</v>
       </c>
-      <c r="E1" s="247" t="s">
+      <c r="E1" s="246" t="s">
         <v>10</v>
       </c>
-      <c r="F1" s="247" t="s">
+      <c r="F1" s="246" t="s">
         <v>11</v>
       </c>
-      <c r="G1" s="247" t="s">
+      <c r="G1" s="246" t="s">
         <v>12</v>
       </c>
-      <c r="H1" s="247" t="s">
+      <c r="H1" s="246" t="s">
         <v>13</v>
       </c>
-      <c r="I1" s="247" t="s">
+      <c r="I1" s="246" t="s">
         <v>7</v>
       </c>
-      <c r="J1" s="247" t="s">
+      <c r="J1" s="246" t="s">
         <v>8</v>
       </c>
-      <c r="K1" s="247" t="s">
+      <c r="K1" s="246" t="s">
         <v>9</v>
       </c>
-      <c r="L1" s="247" t="s">
+      <c r="L1" s="246" t="s">
         <v>10</v>
       </c>
-      <c r="M1" s="247" t="s">
+      <c r="M1" s="246" t="s">
         <v>11</v>
       </c>
-      <c r="N1" s="247" t="s">
+      <c r="N1" s="246" t="s">
         <v>12</v>
       </c>
-      <c r="O1" s="247" t="s">
+      <c r="O1" s="246" t="s">
         <v>13</v>
       </c>
-      <c r="P1" s="247" t="s">
+      <c r="P1" s="246" t="s">
         <v>7</v>
       </c>
-      <c r="Q1" s="247" t="s">
+      <c r="Q1" s="246" t="s">
         <v>8</v>
       </c>
-      <c r="R1" s="247" t="s">
+      <c r="R1" s="246" t="s">
         <v>9</v>
       </c>
-      <c r="S1" s="247" t="s">
+      <c r="S1" s="246" t="s">
         <v>10</v>
       </c>
-      <c r="T1" s="247" t="s">
+      <c r="T1" s="246" t="s">
         <v>11</v>
       </c>
-      <c r="U1" s="247" t="s">
+      <c r="U1" s="246" t="s">
         <v>12</v>
       </c>
-      <c r="V1" s="247" t="s">
+      <c r="V1" s="246" t="s">
         <v>13</v>
       </c>
-      <c r="W1" s="247" t="s">
+      <c r="W1" s="246" t="s">
         <v>7</v>
       </c>
-      <c r="X1" s="247" t="s">
+      <c r="X1" s="246" t="s">
         <v>8</v>
       </c>
-      <c r="Y1" s="247" t="s">
+      <c r="Y1" s="246" t="s">
         <v>9</v>
       </c>
-      <c r="Z1" s="247" t="s">
+      <c r="Z1" s="246" t="s">
         <v>10</v>
       </c>
-      <c r="AA1" s="247" t="s">
+      <c r="AA1" s="246" t="s">
         <v>11</v>
       </c>
-      <c r="AB1" s="247" t="s">
+      <c r="AB1" s="246" t="s">
         <v>12</v>
       </c>
-      <c r="AC1" s="247" t="s">
+      <c r="AC1" s="246" t="s">
         <v>13</v>
       </c>
-      <c r="AD1" s="247" t="s">
+      <c r="AD1" s="246" t="s">
         <v>7</v>
       </c>
-      <c r="AE1" s="247" t="s">
+      <c r="AE1" s="246" t="s">
         <v>8</v>
       </c>
-      <c r="AF1" s="247" t="s">
+      <c r="AF1" s="246" t="s">
         <v>9</v>
       </c>
-      <c r="AG1" s="248"/>
-      <c r="AH1" s="248"/>
+      <c r="AG1" s="247"/>
+      <c r="AH1" s="247"/>
     </row>
     <row r="2">
       <c r="A2" s="245"/>
@@ -40943,95 +41133,95 @@
       <c r="D2" s="246" t="s">
         <v>15</v>
       </c>
-      <c r="E2" s="247" t="s">
+      <c r="E2" s="246" t="s">
         <v>16</v>
       </c>
-      <c r="F2" s="247" t="s">
+      <c r="F2" s="246" t="s">
         <v>226</v>
       </c>
-      <c r="G2" s="247" t="s">
+      <c r="G2" s="246" t="s">
         <v>227</v>
       </c>
-      <c r="H2" s="247" t="s">
+      <c r="H2" s="246" t="s">
         <v>17</v>
       </c>
-      <c r="I2" s="247" t="s">
+      <c r="I2" s="246" t="s">
         <v>18</v>
       </c>
-      <c r="J2" s="247" t="s">
+      <c r="J2" s="246" t="s">
         <v>19</v>
       </c>
-      <c r="K2" s="247" t="s">
+      <c r="K2" s="246" t="s">
         <v>20</v>
       </c>
-      <c r="L2" s="247" t="s">
+      <c r="L2" s="246" t="s">
         <v>21</v>
       </c>
-      <c r="M2" s="247" t="s">
+      <c r="M2" s="246" t="s">
         <v>22</v>
       </c>
-      <c r="N2" s="247" t="s">
+      <c r="N2" s="246" t="s">
         <v>23</v>
       </c>
-      <c r="O2" s="247" t="s">
+      <c r="O2" s="246" t="s">
         <v>24</v>
       </c>
-      <c r="P2" s="247" t="s">
+      <c r="P2" s="246" t="s">
         <v>25</v>
       </c>
-      <c r="Q2" s="247" t="s">
+      <c r="Q2" s="246" t="s">
         <v>26</v>
       </c>
-      <c r="R2" s="247" t="s">
+      <c r="R2" s="246" t="s">
         <v>27</v>
       </c>
-      <c r="S2" s="247" t="s">
+      <c r="S2" s="246" t="s">
         <v>28</v>
       </c>
-      <c r="T2" s="247" t="s">
+      <c r="T2" s="246" t="s">
         <v>29</v>
       </c>
-      <c r="U2" s="247" t="s">
+      <c r="U2" s="246" t="s">
         <v>30</v>
       </c>
-      <c r="V2" s="247" t="s">
+      <c r="V2" s="246" t="s">
         <v>31</v>
       </c>
-      <c r="W2" s="247" t="s">
+      <c r="W2" s="246" t="s">
         <v>32</v>
       </c>
-      <c r="X2" s="247" t="s">
+      <c r="X2" s="246" t="s">
         <v>33</v>
       </c>
-      <c r="Y2" s="247" t="s">
+      <c r="Y2" s="246" t="s">
         <v>34</v>
       </c>
-      <c r="Z2" s="247" t="s">
+      <c r="Z2" s="246" t="s">
         <v>35</v>
       </c>
-      <c r="AA2" s="247" t="s">
+      <c r="AA2" s="246" t="s">
         <v>36</v>
       </c>
-      <c r="AB2" s="247" t="s">
+      <c r="AB2" s="246" t="s">
         <v>37</v>
       </c>
-      <c r="AC2" s="247" t="s">
+      <c r="AC2" s="246" t="s">
         <v>38</v>
       </c>
-      <c r="AD2" s="247" t="s">
+      <c r="AD2" s="246" t="s">
         <v>39</v>
       </c>
-      <c r="AE2" s="247" t="s">
+      <c r="AE2" s="246" t="s">
         <v>40</v>
       </c>
-      <c r="AF2" s="247" t="s">
+      <c r="AF2" s="246" t="s">
         <v>41</v>
       </c>
-      <c r="AG2" s="248"/>
-      <c r="AH2" s="248"/>
+      <c r="AG2" s="247"/>
+      <c r="AH2" s="247"/>
     </row>
     <row r="3">
-      <c r="A3" s="247" t="s">
+      <c r="A3" s="248" t="s">
         <v>228</v>
       </c>
       <c r="B3" s="246" t="s">
@@ -41095,13 +41285,13 @@
         <v>47</v>
       </c>
       <c r="V3" s="246" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="W3" s="246" t="s">
-        <v>47</v>
-      </c>
-      <c r="X3" s="245" t="s">
-        <v>47</v>
+        <v>48</v>
+      </c>
+      <c r="X3" s="246" t="s">
+        <v>48</v>
       </c>
       <c r="Y3" s="246" t="s">
         <v>53</v>
@@ -41131,7 +41321,7 @@
       <c r="AH3" s="245"/>
     </row>
     <row r="4">
-      <c r="A4" s="247" t="s">
+      <c r="A4" s="248" t="s">
         <v>229</v>
       </c>
       <c r="B4" s="246" t="s">
@@ -41231,7 +41421,7 @@
       <c r="AH4" s="245"/>
     </row>
     <row r="5">
-      <c r="A5" s="247" t="s">
+      <c r="A5" s="248" t="s">
         <v>230</v>
       </c>
       <c r="B5" s="246" t="s">
@@ -41331,7 +41521,7 @@
       <c r="AH5" s="245"/>
     </row>
     <row r="6">
-      <c r="A6" s="247" t="s">
+      <c r="A6" s="248" t="s">
         <v>231</v>
       </c>
       <c r="B6" s="246" t="s">
@@ -41431,7 +41621,7 @@
       <c r="AH6" s="245"/>
     </row>
     <row r="7">
-      <c r="A7" s="247" t="s">
+      <c r="A7" s="248" t="s">
         <v>232</v>
       </c>
       <c r="B7" s="246" t="s">
@@ -41447,10 +41637,10 @@
         <v>53</v>
       </c>
       <c r="F7" s="246" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G7" s="246" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="H7" s="246" t="s">
         <v>47</v>
@@ -41531,7 +41721,7 @@
       <c r="AH7" s="245"/>
     </row>
     <row r="8">
-      <c r="A8" s="247" t="s">
+      <c r="A8" s="248" t="s">
         <v>233</v>
       </c>
       <c r="B8" s="246" t="s">
@@ -41631,7 +41821,7 @@
       <c r="AH8" s="245"/>
     </row>
     <row r="9">
-      <c r="A9" s="247" t="s">
+      <c r="A9" s="248" t="s">
         <v>234</v>
       </c>
       <c r="B9" s="246" t="s">
@@ -41656,7 +41846,7 @@
         <v>47</v>
       </c>
       <c r="I9" s="246" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="J9" s="246" t="s">
         <v>49</v>
@@ -41680,7 +41870,7 @@
         <v>47</v>
       </c>
       <c r="Q9" s="246" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="R9" s="246" t="s">
         <v>53</v>
@@ -41731,7 +41921,7 @@
       <c r="AH9" s="245"/>
     </row>
     <row r="10">
-      <c r="A10" s="247" t="s">
+      <c r="A10" s="248" t="s">
         <v>235</v>
       </c>
       <c r="B10" s="246" t="s">
@@ -41831,7 +42021,7 @@
       <c r="AH10" s="245"/>
     </row>
     <row r="11">
-      <c r="A11" s="247" t="s">
+      <c r="A11" s="248" t="s">
         <v>236</v>
       </c>
       <c r="B11" s="246" t="s">
@@ -41931,7 +42121,7 @@
       <c r="AH11" s="245"/>
     </row>
     <row r="12">
-      <c r="A12" s="247" t="s">
+      <c r="A12" s="248" t="s">
         <v>237</v>
       </c>
       <c r="B12" s="246" t="s">
@@ -42031,7 +42221,7 @@
       <c r="AH12" s="245"/>
     </row>
     <row r="13">
-      <c r="A13" s="247" t="s">
+      <c r="A13" s="248" t="s">
         <v>238</v>
       </c>
       <c r="B13" s="246" t="s">
@@ -42131,7 +42321,7 @@
       <c r="AH13" s="245"/>
     </row>
     <row r="14">
-      <c r="A14" s="247" t="s">
+      <c r="A14" s="248" t="s">
         <v>239</v>
       </c>
       <c r="B14" s="246" t="s">
@@ -42231,7 +42421,7 @@
       <c r="AH14" s="245"/>
     </row>
     <row r="15">
-      <c r="A15" s="247" t="s">
+      <c r="A15" s="248" t="s">
         <v>240</v>
       </c>
       <c r="B15" s="246" t="s">
@@ -42313,7 +42503,7 @@
         <v>47</v>
       </c>
       <c r="AB15" s="246" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="AC15" s="246" t="s">
         <v>48</v>
@@ -42331,7 +42521,7 @@
       <c r="AH15" s="245"/>
     </row>
     <row r="16">
-      <c r="A16" s="247" t="s">
+      <c r="A16" s="248" t="s">
         <v>241</v>
       </c>
       <c r="B16" s="246" t="s">
@@ -42431,7 +42621,7 @@
       <c r="AH16" s="245"/>
     </row>
     <row r="17">
-      <c r="A17" s="247" t="s">
+      <c r="A17" s="248" t="s">
         <v>242</v>
       </c>
       <c r="B17" s="246" t="s">
@@ -42465,7 +42655,7 @@
         <v>53</v>
       </c>
       <c r="L17" s="246" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="M17" s="246" t="s">
         <v>47</v>
@@ -42531,7 +42721,7 @@
       <c r="AH17" s="245"/>
     </row>
     <row r="18">
-      <c r="A18" s="247" t="s">
+      <c r="A18" s="248" t="s">
         <v>243</v>
       </c>
       <c r="B18" s="246" t="s">
@@ -42631,7 +42821,7 @@
       <c r="AH18" s="245"/>
     </row>
     <row r="19">
-      <c r="A19" s="247" t="s">
+      <c r="A19" s="248" t="s">
         <v>244</v>
       </c>
       <c r="B19" s="246" t="s">
@@ -42731,7 +42921,7 @@
       <c r="AH19" s="245"/>
     </row>
     <row r="20">
-      <c r="A20" s="247" t="s">
+      <c r="A20" s="248" t="s">
         <v>245</v>
       </c>
       <c r="B20" s="246" t="s">
@@ -42831,7 +43021,7 @@
       <c r="AH20" s="245"/>
     </row>
     <row r="21">
-      <c r="A21" s="247" t="s">
+      <c r="A21" s="248" t="s">
         <v>246</v>
       </c>
       <c r="B21" s="246" t="s">
@@ -42876,8 +43066,8 @@
       <c r="O21" s="245" t="s">
         <v>47</v>
       </c>
-      <c r="P21" s="245" t="s">
-        <v>47</v>
+      <c r="P21" s="246" t="s">
+        <v>49</v>
       </c>
       <c r="Q21" s="246" t="s">
         <v>53</v>
@@ -42897,8 +43087,8 @@
       <c r="V21" s="245" t="s">
         <v>47</v>
       </c>
-      <c r="W21" s="245" t="s">
-        <v>47</v>
+      <c r="W21" s="246" t="s">
+        <v>49</v>
       </c>
       <c r="X21" s="246" t="s">
         <v>53</v>
@@ -42931,7 +43121,7 @@
       <c r="AH21" s="245"/>
     </row>
     <row r="22">
-      <c r="A22" s="247" t="s">
+      <c r="A22" s="248" t="s">
         <v>247</v>
       </c>
       <c r="B22" s="246" t="s">
@@ -43031,7 +43221,7 @@
       <c r="AH22" s="245"/>
     </row>
     <row r="23">
-      <c r="A23" s="247" t="s">
+      <c r="A23" s="248" t="s">
         <v>248</v>
       </c>
       <c r="B23" s="246" t="s">
@@ -43047,7 +43237,7 @@
         <v>49</v>
       </c>
       <c r="F23" s="246" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G23" s="246" t="s">
         <v>47</v>
@@ -43065,7 +43255,7 @@
         <v>53</v>
       </c>
       <c r="L23" s="246" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="M23" s="246" t="s">
         <v>47</v>
@@ -43077,7 +43267,7 @@
         <v>47</v>
       </c>
       <c r="P23" s="246" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="Q23" s="246" t="s">
         <v>53</v>
@@ -43086,7 +43276,7 @@
         <v>53</v>
       </c>
       <c r="S23" s="246" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="T23" s="246" t="s">
         <v>47</v>
@@ -43131,7 +43321,7 @@
       <c r="AH23" s="245"/>
     </row>
     <row r="24">
-      <c r="A24" s="247" t="s">
+      <c r="A24" s="248" t="s">
         <v>249</v>
       </c>
       <c r="B24" s="246" t="s">
@@ -43231,7 +43421,7 @@
       <c r="AH24" s="245"/>
     </row>
     <row r="25">
-      <c r="A25" s="247" t="s">
+      <c r="A25" s="248" t="s">
         <v>250</v>
       </c>
       <c r="B25" s="246" t="s">
@@ -43301,7 +43491,7 @@
         <v>47</v>
       </c>
       <c r="X25" s="246" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="Y25" s="246" t="s">
         <v>49</v>
@@ -43331,7 +43521,7 @@
       <c r="AH25" s="245"/>
     </row>
     <row r="26">
-      <c r="A26" s="247" t="s">
+      <c r="A26" s="248" t="s">
         <v>251</v>
       </c>
       <c r="B26" s="246" t="s">
@@ -43431,7 +43621,7 @@
       <c r="AH26" s="245"/>
     </row>
     <row r="27">
-      <c r="A27" s="247" t="s">
+      <c r="A27" s="248" t="s">
         <v>252</v>
       </c>
       <c r="B27" s="246" t="s">
@@ -43531,7 +43721,7 @@
       <c r="AH27" s="245"/>
     </row>
     <row r="28">
-      <c r="A28" s="247" t="s">
+      <c r="A28" s="248" t="s">
         <v>253</v>
       </c>
       <c r="B28" s="246" t="s">
@@ -43631,7 +43821,7 @@
       <c r="AH28" s="245"/>
     </row>
     <row r="29">
-      <c r="A29" s="247" t="s">
+      <c r="A29" s="248" t="s">
         <v>254</v>
       </c>
       <c r="B29" s="246" t="s">
@@ -43731,7 +43921,7 @@
       <c r="AH29" s="245"/>
     </row>
     <row r="30">
-      <c r="A30" s="247" t="s">
+      <c r="A30" s="248" t="s">
         <v>255</v>
       </c>
       <c r="B30" s="246" t="s">
@@ -43831,7 +44021,7 @@
       <c r="AH30" s="245"/>
     </row>
     <row r="31">
-      <c r="A31" s="247" t="s">
+      <c r="A31" s="248" t="s">
         <v>256</v>
       </c>
       <c r="B31" s="246" t="s">
@@ -43931,7 +44121,7 @@
       <c r="AH31" s="245"/>
     </row>
     <row r="32">
-      <c r="A32" s="247" t="s">
+      <c r="A32" s="248" t="s">
         <v>257</v>
       </c>
       <c r="B32" s="246" t="s">
@@ -44031,7 +44221,7 @@
       <c r="AH32" s="245"/>
     </row>
     <row r="33">
-      <c r="A33" s="247" t="s">
+      <c r="A33" s="248" t="s">
         <v>258</v>
       </c>
       <c r="B33" s="246" t="s">
@@ -44131,7 +44321,7 @@
       <c r="AH33" s="245"/>
     </row>
     <row r="34">
-      <c r="A34" s="247" t="s">
+      <c r="A34" s="248" t="s">
         <v>259</v>
       </c>
       <c r="B34" s="246" t="s">
@@ -44231,7 +44421,7 @@
       <c r="AH34" s="245"/>
     </row>
     <row r="35">
-      <c r="A35" s="247" t="s">
+      <c r="A35" s="248" t="s">
         <v>260</v>
       </c>
       <c r="B35" s="246" t="s">
@@ -44331,7 +44521,7 @@
       <c r="AH35" s="245"/>
     </row>
     <row r="36">
-      <c r="A36" s="247" t="s">
+      <c r="A36" s="248" t="s">
         <v>261</v>
       </c>
       <c r="B36" s="246" t="s">
@@ -44431,7 +44621,7 @@
       <c r="AH36" s="245"/>
     </row>
     <row r="37">
-      <c r="A37" s="247" t="s">
+      <c r="A37" s="248" t="s">
         <v>262</v>
       </c>
       <c r="B37" s="246" t="s">
@@ -44531,7 +44721,7 @@
       <c r="AH37" s="245"/>
     </row>
     <row r="38">
-      <c r="A38" s="247" t="s">
+      <c r="A38" s="248" t="s">
         <v>263</v>
       </c>
       <c r="B38" s="246" t="s">
@@ -44631,7 +44821,7 @@
       <c r="AH38" s="245"/>
     </row>
     <row r="39">
-      <c r="A39" s="247" t="s">
+      <c r="A39" s="248" t="s">
         <v>264</v>
       </c>
       <c r="B39" s="246" t="s">
@@ -44731,7 +44921,7 @@
       <c r="AH39" s="245"/>
     </row>
     <row r="40">
-      <c r="A40" s="247" t="s">
+      <c r="A40" s="248" t="s">
         <v>265</v>
       </c>
       <c r="B40" s="246" t="s">
@@ -44831,7 +45021,7 @@
       <c r="AH40" s="245"/>
     </row>
     <row r="41">
-      <c r="A41" s="247" t="s">
+      <c r="A41" s="248" t="s">
         <v>266</v>
       </c>
       <c r="B41" s="246" t="s">
@@ -44931,7 +45121,7 @@
       <c r="AH41" s="245"/>
     </row>
     <row r="42">
-      <c r="A42" s="247" t="s">
+      <c r="A42" s="248" t="s">
         <v>267</v>
       </c>
       <c r="B42" s="246" t="s">
@@ -45031,7 +45221,7 @@
       <c r="AH42" s="245"/>
     </row>
     <row r="43">
-      <c r="A43" s="248" t="s">
+      <c r="A43" s="247" t="s">
         <v>268</v>
       </c>
       <c r="B43" s="246" t="s">
@@ -45131,7 +45321,7 @@
       <c r="AH43" s="245"/>
     </row>
     <row r="44">
-      <c r="A44" s="248" t="s">
+      <c r="A44" s="247" t="s">
         <v>269</v>
       </c>
       <c r="B44" s="246" t="s">
@@ -45212,8 +45402,8 @@
       <c r="AA44" s="246" t="s">
         <v>47</v>
       </c>
-      <c r="AB44" s="245" t="s">
-        <v>47</v>
+      <c r="AB44" s="246" t="s">
+        <v>48</v>
       </c>
       <c r="AC44" s="246" t="s">
         <v>53</v>
@@ -50027,115 +50217,115 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="246" t="str">
+      <c r="A1" s="250" t="str">
         <f t="array" ref="A1:AE11">'ORIGIN MONTH 7'!B48:AF58</f>
         <v>Shift</v>
       </c>
-      <c r="B1" s="246" t="s">
+      <c r="B1" s="251" t="s">
         <v>8</v>
       </c>
-      <c r="C1" s="246" t="s">
+      <c r="C1" s="252" t="s">
         <v>9</v>
       </c>
-      <c r="D1" s="246" t="s">
+      <c r="D1" s="253" t="s">
         <v>10</v>
       </c>
-      <c r="E1" s="246" t="s">
+      <c r="E1" s="251" t="s">
         <v>11</v>
       </c>
-      <c r="F1" s="246" t="s">
+      <c r="F1" s="252" t="s">
         <v>12</v>
       </c>
-      <c r="G1" s="246" t="s">
+      <c r="G1" s="252" t="s">
         <v>13</v>
       </c>
-      <c r="H1" s="246" t="s">
+      <c r="H1" s="252" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="246" t="s">
+      <c r="I1" s="252" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="246" t="s">
+      <c r="J1" s="252" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="246" t="s">
+      <c r="K1" s="253" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="246" t="s">
+      <c r="L1" s="251" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="246" t="s">
+      <c r="M1" s="252" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="246" t="s">
+      <c r="N1" s="252" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="246" t="s">
+      <c r="O1" s="252" t="s">
         <v>7</v>
       </c>
-      <c r="P1" s="246" t="s">
+      <c r="P1" s="252" t="s">
         <v>8</v>
       </c>
-      <c r="Q1" s="246" t="s">
+      <c r="Q1" s="252" t="s">
         <v>9</v>
       </c>
-      <c r="R1" s="246" t="s">
+      <c r="R1" s="253" t="s">
         <v>10</v>
       </c>
-      <c r="S1" s="246" t="s">
+      <c r="S1" s="251" t="s">
         <v>11</v>
       </c>
-      <c r="T1" s="246" t="s">
+      <c r="T1" s="252" t="s">
         <v>12</v>
       </c>
-      <c r="U1" s="246" t="s">
+      <c r="U1" s="252" t="s">
         <v>13</v>
       </c>
-      <c r="V1" s="246" t="s">
+      <c r="V1" s="252" t="s">
         <v>7</v>
       </c>
-      <c r="W1" s="246" t="s">
+      <c r="W1" s="252" t="s">
         <v>8</v>
       </c>
-      <c r="X1" s="246" t="s">
+      <c r="X1" s="252" t="s">
         <v>9</v>
       </c>
-      <c r="Y1" s="246" t="s">
+      <c r="Y1" s="253" t="s">
         <v>10</v>
       </c>
-      <c r="Z1" s="246" t="s">
+      <c r="Z1" s="251" t="s">
         <v>11</v>
       </c>
-      <c r="AA1" s="246" t="s">
+      <c r="AA1" s="252" t="s">
         <v>12</v>
       </c>
-      <c r="AB1" s="246" t="s">
+      <c r="AB1" s="252" t="s">
         <v>13</v>
       </c>
-      <c r="AC1" s="246" t="s">
+      <c r="AC1" s="252" t="s">
         <v>7</v>
       </c>
-      <c r="AD1" s="246" t="s">
+      <c r="AD1" s="252" t="s">
         <v>8</v>
       </c>
-      <c r="AE1" s="246" t="s">
+      <c r="AE1" s="253" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="246" t="s">
+      <c r="A2" s="254" t="s">
         <v>272</v>
       </c>
-      <c r="B2" s="246" t="s">
+      <c r="B2" s="255" t="s">
         <v>14</v>
       </c>
       <c r="C2" s="246" t="s">
         <v>15</v>
       </c>
-      <c r="D2" s="246" t="s">
+      <c r="D2" s="256" t="s">
         <v>16</v>
       </c>
-      <c r="E2" s="246" t="s">
+      <c r="E2" s="255" t="s">
         <v>226</v>
       </c>
       <c r="F2" s="246" t="s">
@@ -50153,10 +50343,10 @@
       <c r="J2" s="246" t="s">
         <v>20</v>
       </c>
-      <c r="K2" s="246" t="s">
+      <c r="K2" s="256" t="s">
         <v>21</v>
       </c>
-      <c r="L2" s="246" t="s">
+      <c r="L2" s="255" t="s">
         <v>22</v>
       </c>
       <c r="M2" s="246" t="s">
@@ -50174,10 +50364,10 @@
       <c r="Q2" s="246" t="s">
         <v>27</v>
       </c>
-      <c r="R2" s="246" t="s">
+      <c r="R2" s="256" t="s">
         <v>28</v>
       </c>
-      <c r="S2" s="246" t="s">
+      <c r="S2" s="255" t="s">
         <v>29</v>
       </c>
       <c r="T2" s="246" t="s">
@@ -50195,10 +50385,10 @@
       <c r="X2" s="246" t="s">
         <v>34</v>
       </c>
-      <c r="Y2" s="246" t="s">
+      <c r="Y2" s="256" t="s">
         <v>35</v>
       </c>
-      <c r="Z2" s="246" t="s">
+      <c r="Z2" s="255" t="s">
         <v>36</v>
       </c>
       <c r="AA2" s="246" t="s">
@@ -50213,34 +50403,34 @@
       <c r="AD2" s="246" t="s">
         <v>40</v>
       </c>
-      <c r="AE2" s="246" t="s">
+      <c r="AE2" s="256" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="246" t="s">
-        <v>47</v>
-      </c>
-      <c r="B3" s="245">
+      <c r="A3" s="254" t="s">
+        <v>47</v>
+      </c>
+      <c r="B3" s="257">
         <v>26.0</v>
       </c>
       <c r="C3" s="245">
         <v>26.0</v>
       </c>
-      <c r="D3" s="245">
+      <c r="D3" s="258">
         <v>25.0</v>
       </c>
-      <c r="E3" s="245">
-        <v>27.0</v>
+      <c r="E3" s="257">
+        <v>25.0</v>
       </c>
       <c r="F3" s="245">
-        <v>26.0</v>
+        <v>25.0</v>
       </c>
       <c r="G3" s="245">
         <v>30.0</v>
       </c>
       <c r="H3" s="245">
-        <v>28.0</v>
+        <v>27.0</v>
       </c>
       <c r="I3" s="245">
         <v>26.0</v>
@@ -50248,10 +50438,10 @@
       <c r="J3" s="245">
         <v>26.0</v>
       </c>
-      <c r="K3" s="245">
+      <c r="K3" s="258">
         <v>25.0</v>
       </c>
-      <c r="L3" s="245">
+      <c r="L3" s="257">
         <v>25.0</v>
       </c>
       <c r="M3" s="245">
@@ -50261,7 +50451,7 @@
         <v>28.0</v>
       </c>
       <c r="O3" s="245">
-        <v>27.0</v>
+        <v>25.0</v>
       </c>
       <c r="P3" s="245">
         <v>26.0</v>
@@ -50269,20 +50459,20 @@
       <c r="Q3" s="245">
         <v>26.0</v>
       </c>
-      <c r="R3" s="245">
+      <c r="R3" s="258">
         <v>25.0</v>
       </c>
-      <c r="S3" s="245">
+      <c r="S3" s="257">
         <v>25.0</v>
       </c>
       <c r="T3" s="245">
         <v>25.0</v>
       </c>
       <c r="U3" s="245">
-        <v>27.0</v>
+        <v>26.0</v>
       </c>
       <c r="V3" s="245">
-        <v>28.0</v>
+        <v>26.0</v>
       </c>
       <c r="W3" s="245">
         <v>26.0</v>
@@ -50290,14 +50480,14 @@
       <c r="X3" s="245">
         <v>26.0</v>
       </c>
-      <c r="Y3" s="245">
+      <c r="Y3" s="258">
         <v>25.0</v>
       </c>
-      <c r="Z3" s="245">
+      <c r="Z3" s="257">
         <v>25.0</v>
       </c>
       <c r="AA3" s="245">
-        <v>25.0</v>
+        <v>26.0</v>
       </c>
       <c r="AB3" s="245">
         <v>27.0</v>
@@ -50308,24 +50498,24 @@
       <c r="AD3" s="245">
         <v>26.0</v>
       </c>
-      <c r="AE3" s="245">
+      <c r="AE3" s="258">
         <v>26.0</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="246" t="s">
+      <c r="A4" s="254" t="s">
         <v>46</v>
       </c>
-      <c r="B4" s="245">
+      <c r="B4" s="257">
         <v>0.0</v>
       </c>
       <c r="C4" s="245">
         <v>0.0</v>
       </c>
-      <c r="D4" s="245">
+      <c r="D4" s="258">
         <v>0.0</v>
       </c>
-      <c r="E4" s="245">
+      <c r="E4" s="257">
         <v>0.0</v>
       </c>
       <c r="F4" s="245">
@@ -50343,10 +50533,10 @@
       <c r="J4" s="245">
         <v>0.0</v>
       </c>
-      <c r="K4" s="245">
+      <c r="K4" s="258">
         <v>0.0</v>
       </c>
-      <c r="L4" s="245">
+      <c r="L4" s="257">
         <v>0.0</v>
       </c>
       <c r="M4" s="245">
@@ -50364,10 +50554,10 @@
       <c r="Q4" s="245">
         <v>0.0</v>
       </c>
-      <c r="R4" s="245">
+      <c r="R4" s="258">
         <v>0.0</v>
       </c>
-      <c r="S4" s="245">
+      <c r="S4" s="257">
         <v>0.0</v>
       </c>
       <c r="T4" s="245">
@@ -50385,10 +50575,10 @@
       <c r="X4" s="245">
         <v>0.0</v>
       </c>
-      <c r="Y4" s="245">
+      <c r="Y4" s="258">
         <v>0.0</v>
       </c>
-      <c r="Z4" s="245">
+      <c r="Z4" s="257">
         <v>0.0</v>
       </c>
       <c r="AA4" s="245">
@@ -50403,24 +50593,24 @@
       <c r="AD4" s="245">
         <v>0.0</v>
       </c>
-      <c r="AE4" s="245">
+      <c r="AE4" s="258">
         <v>0.0</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="246" t="s">
+      <c r="A5" s="254" t="s">
         <v>45</v>
       </c>
-      <c r="B5" s="245">
+      <c r="B5" s="257">
         <v>0.0</v>
       </c>
       <c r="C5" s="245">
         <v>0.0</v>
       </c>
-      <c r="D5" s="245">
+      <c r="D5" s="258">
         <v>0.0</v>
       </c>
-      <c r="E5" s="245">
+      <c r="E5" s="257">
         <v>0.0</v>
       </c>
       <c r="F5" s="245">
@@ -50438,10 +50628,10 @@
       <c r="J5" s="245">
         <v>0.0</v>
       </c>
-      <c r="K5" s="245">
+      <c r="K5" s="258">
         <v>0.0</v>
       </c>
-      <c r="L5" s="245">
+      <c r="L5" s="257">
         <v>0.0</v>
       </c>
       <c r="M5" s="245">
@@ -50459,10 +50649,10 @@
       <c r="Q5" s="245">
         <v>0.0</v>
       </c>
-      <c r="R5" s="245">
+      <c r="R5" s="258">
         <v>0.0</v>
       </c>
-      <c r="S5" s="245">
+      <c r="S5" s="257">
         <v>0.0</v>
       </c>
       <c r="T5" s="245">
@@ -50480,10 +50670,10 @@
       <c r="X5" s="245">
         <v>0.0</v>
       </c>
-      <c r="Y5" s="245">
+      <c r="Y5" s="258">
         <v>0.0</v>
       </c>
-      <c r="Z5" s="245">
+      <c r="Z5" s="257">
         <v>0.0</v>
       </c>
       <c r="AA5" s="245">
@@ -50498,24 +50688,24 @@
       <c r="AD5" s="245">
         <v>0.0</v>
       </c>
-      <c r="AE5" s="245">
+      <c r="AE5" s="258">
         <v>0.0</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="246" t="s">
+      <c r="A6" s="254" t="s">
         <v>44</v>
       </c>
-      <c r="B6" s="245">
+      <c r="B6" s="257">
         <v>0.0</v>
       </c>
       <c r="C6" s="245">
         <v>0.0</v>
       </c>
-      <c r="D6" s="245">
+      <c r="D6" s="258">
         <v>0.0</v>
       </c>
-      <c r="E6" s="245">
+      <c r="E6" s="257">
         <v>0.0</v>
       </c>
       <c r="F6" s="245">
@@ -50533,10 +50723,10 @@
       <c r="J6" s="245">
         <v>0.0</v>
       </c>
-      <c r="K6" s="245">
+      <c r="K6" s="258">
         <v>0.0</v>
       </c>
-      <c r="L6" s="245">
+      <c r="L6" s="257">
         <v>0.0</v>
       </c>
       <c r="M6" s="245">
@@ -50554,10 +50744,10 @@
       <c r="Q6" s="245">
         <v>0.0</v>
       </c>
-      <c r="R6" s="245">
+      <c r="R6" s="258">
         <v>0.0</v>
       </c>
-      <c r="S6" s="245">
+      <c r="S6" s="257">
         <v>0.0</v>
       </c>
       <c r="T6" s="245">
@@ -50575,10 +50765,10 @@
       <c r="X6" s="245">
         <v>0.0</v>
       </c>
-      <c r="Y6" s="245">
+      <c r="Y6" s="258">
         <v>0.0</v>
       </c>
-      <c r="Z6" s="245">
+      <c r="Z6" s="257">
         <v>0.0</v>
       </c>
       <c r="AA6" s="245">
@@ -50593,24 +50783,24 @@
       <c r="AD6" s="245">
         <v>0.0</v>
       </c>
-      <c r="AE6" s="245">
+      <c r="AE6" s="258">
         <v>0.0</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="246" t="s">
+      <c r="A7" s="254" t="s">
         <v>43</v>
       </c>
-      <c r="B7" s="245">
+      <c r="B7" s="257">
         <v>0.0</v>
       </c>
       <c r="C7" s="245">
         <v>0.0</v>
       </c>
-      <c r="D7" s="245">
+      <c r="D7" s="258">
         <v>0.0</v>
       </c>
-      <c r="E7" s="245">
+      <c r="E7" s="257">
         <v>0.0</v>
       </c>
       <c r="F7" s="245">
@@ -50628,10 +50818,10 @@
       <c r="J7" s="245">
         <v>0.0</v>
       </c>
-      <c r="K7" s="245">
+      <c r="K7" s="258">
         <v>0.0</v>
       </c>
-      <c r="L7" s="245">
+      <c r="L7" s="257">
         <v>0.0</v>
       </c>
       <c r="M7" s="245">
@@ -50649,10 +50839,10 @@
       <c r="Q7" s="245">
         <v>0.0</v>
       </c>
-      <c r="R7" s="245">
+      <c r="R7" s="258">
         <v>0.0</v>
       </c>
-      <c r="S7" s="245">
+      <c r="S7" s="257">
         <v>0.0</v>
       </c>
       <c r="T7" s="245">
@@ -50670,10 +50860,10 @@
       <c r="X7" s="245">
         <v>0.0</v>
       </c>
-      <c r="Y7" s="245">
+      <c r="Y7" s="258">
         <v>0.0</v>
       </c>
-      <c r="Z7" s="245">
+      <c r="Z7" s="257">
         <v>0.0</v>
       </c>
       <c r="AA7" s="245">
@@ -50688,24 +50878,24 @@
       <c r="AD7" s="245">
         <v>0.0</v>
       </c>
-      <c r="AE7" s="245">
+      <c r="AE7" s="258">
         <v>0.0</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="246" t="s">
-        <v>273</v>
-      </c>
-      <c r="B8" s="245">
+      <c r="A8" s="254" t="s">
+        <v>53</v>
+      </c>
+      <c r="B8" s="257">
         <v>12.0</v>
       </c>
       <c r="C8" s="245">
         <v>13.0</v>
       </c>
-      <c r="D8" s="245">
+      <c r="D8" s="258">
         <v>12.0</v>
       </c>
-      <c r="E8" s="245">
+      <c r="E8" s="257">
         <v>12.0</v>
       </c>
       <c r="F8" s="245">
@@ -50723,10 +50913,10 @@
       <c r="J8" s="245">
         <v>13.0</v>
       </c>
-      <c r="K8" s="245">
+      <c r="K8" s="258">
         <v>12.0</v>
       </c>
-      <c r="L8" s="245">
+      <c r="L8" s="257">
         <v>12.0</v>
       </c>
       <c r="M8" s="245">
@@ -50744,10 +50934,10 @@
       <c r="Q8" s="245">
         <v>13.0</v>
       </c>
-      <c r="R8" s="245">
+      <c r="R8" s="258">
         <v>12.0</v>
       </c>
-      <c r="S8" s="245">
+      <c r="S8" s="257">
         <v>12.0</v>
       </c>
       <c r="T8" s="245">
@@ -50765,10 +50955,10 @@
       <c r="X8" s="245">
         <v>13.0</v>
       </c>
-      <c r="Y8" s="245">
+      <c r="Y8" s="258">
         <v>12.0</v>
       </c>
-      <c r="Z8" s="245">
+      <c r="Z8" s="257">
         <v>12.0</v>
       </c>
       <c r="AA8" s="245">
@@ -50783,24 +50973,24 @@
       <c r="AD8" s="245">
         <v>12.0</v>
       </c>
-      <c r="AE8" s="245">
+      <c r="AE8" s="258">
         <v>13.0</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="246" t="s">
+      <c r="A9" s="254" t="s">
         <v>48</v>
       </c>
-      <c r="B9" s="245">
+      <c r="B9" s="257">
         <v>0.0</v>
       </c>
       <c r="C9" s="245">
         <v>0.0</v>
       </c>
-      <c r="D9" s="245">
+      <c r="D9" s="258">
         <v>0.0</v>
       </c>
-      <c r="E9" s="245">
+      <c r="E9" s="257">
         <v>2.0</v>
       </c>
       <c r="F9" s="245">
@@ -50818,10 +51008,10 @@
       <c r="J9" s="245">
         <v>2.0</v>
       </c>
-      <c r="K9" s="245">
+      <c r="K9" s="258">
         <v>2.0</v>
       </c>
-      <c r="L9" s="245">
+      <c r="L9" s="257">
         <v>2.0</v>
       </c>
       <c r="M9" s="245">
@@ -50831,43 +51021,43 @@
         <v>0.0</v>
       </c>
       <c r="O9" s="245">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="P9" s="245">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="Q9" s="245">
         <v>1.0</v>
       </c>
-      <c r="R9" s="245">
-        <v>1.0</v>
-      </c>
-      <c r="S9" s="245">
+      <c r="R9" s="258">
+        <v>2.0</v>
+      </c>
+      <c r="S9" s="257">
         <v>2.0</v>
       </c>
       <c r="T9" s="245">
         <v>1.0</v>
       </c>
       <c r="U9" s="245">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="V9" s="245">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="W9" s="245">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="X9" s="245">
         <v>1.0</v>
       </c>
-      <c r="Y9" s="245">
+      <c r="Y9" s="258">
         <v>2.0</v>
       </c>
-      <c r="Z9" s="245">
+      <c r="Z9" s="257">
         <v>2.0</v>
       </c>
       <c r="AA9" s="245">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="AB9" s="245">
         <v>4.0</v>
@@ -50878,34 +51068,34 @@
       <c r="AD9" s="245">
         <v>2.0</v>
       </c>
-      <c r="AE9" s="245">
+      <c r="AE9" s="258">
         <v>1.0</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="246" t="s">
+      <c r="A10" s="254" t="s">
         <v>49</v>
       </c>
-      <c r="B10" s="245">
+      <c r="B10" s="257">
         <v>3.0</v>
       </c>
       <c r="C10" s="245">
         <v>2.0</v>
       </c>
-      <c r="D10" s="245">
+      <c r="D10" s="258">
         <v>4.0</v>
       </c>
-      <c r="E10" s="245">
-        <v>0.0</v>
+      <c r="E10" s="257">
+        <v>2.0</v>
       </c>
       <c r="F10" s="245">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="G10" s="245">
         <v>0.0</v>
       </c>
       <c r="H10" s="245">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="I10" s="245">
         <v>1.0</v>
@@ -50913,10 +51103,10 @@
       <c r="J10" s="245">
         <v>0.0</v>
       </c>
-      <c r="K10" s="245">
+      <c r="K10" s="258">
         <v>2.0</v>
       </c>
-      <c r="L10" s="245">
+      <c r="L10" s="257">
         <v>2.0</v>
       </c>
       <c r="M10" s="245">
@@ -50926,18 +51116,18 @@
         <v>3.0</v>
       </c>
       <c r="O10" s="245">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="P10" s="245">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="Q10" s="245">
         <v>1.0</v>
       </c>
-      <c r="R10" s="245">
-        <v>3.0</v>
-      </c>
-      <c r="S10" s="245">
+      <c r="R10" s="258">
+        <v>2.0</v>
+      </c>
+      <c r="S10" s="257">
         <v>2.0</v>
       </c>
       <c r="T10" s="245">
@@ -50947,18 +51137,18 @@
         <v>4.0</v>
       </c>
       <c r="V10" s="245">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="W10" s="245">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="X10" s="245">
         <v>1.0</v>
       </c>
-      <c r="Y10" s="245">
+      <c r="Y10" s="258">
         <v>2.0</v>
       </c>
-      <c r="Z10" s="245">
+      <c r="Z10" s="257">
         <v>2.0</v>
       </c>
       <c r="AA10" s="245">
@@ -50973,102 +51163,102 @@
       <c r="AD10" s="245">
         <v>1.0</v>
       </c>
-      <c r="AE10" s="245">
+      <c r="AE10" s="258">
         <v>1.0</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="246" t="s">
+      <c r="A11" s="259" t="s">
         <v>183</v>
       </c>
-      <c r="B11" s="245">
+      <c r="B11" s="260">
         <v>26.0</v>
       </c>
-      <c r="C11" s="245">
+      <c r="C11" s="261">
         <v>26.0</v>
       </c>
-      <c r="D11" s="245">
+      <c r="D11" s="262">
         <v>25.0</v>
       </c>
-      <c r="E11" s="245">
+      <c r="E11" s="260">
+        <v>25.0</v>
+      </c>
+      <c r="F11" s="261">
+        <v>25.0</v>
+      </c>
+      <c r="G11" s="261">
+        <v>30.0</v>
+      </c>
+      <c r="H11" s="261">
         <v>27.0</v>
       </c>
-      <c r="F11" s="245">
+      <c r="I11" s="261">
         <v>26.0</v>
       </c>
-      <c r="G11" s="245">
-        <v>30.0</v>
-      </c>
-      <c r="H11" s="245">
+      <c r="J11" s="261">
+        <v>26.0</v>
+      </c>
+      <c r="K11" s="262">
+        <v>25.0</v>
+      </c>
+      <c r="L11" s="260">
+        <v>25.0</v>
+      </c>
+      <c r="M11" s="261">
+        <v>26.0</v>
+      </c>
+      <c r="N11" s="261">
         <v>28.0</v>
       </c>
-      <c r="I11" s="245">
+      <c r="O11" s="261">
+        <v>25.0</v>
+      </c>
+      <c r="P11" s="261">
         <v>26.0</v>
       </c>
-      <c r="J11" s="245">
+      <c r="Q11" s="261">
         <v>26.0</v>
       </c>
-      <c r="K11" s="245">
+      <c r="R11" s="262">
         <v>25.0</v>
       </c>
-      <c r="L11" s="245">
+      <c r="S11" s="260">
         <v>25.0</v>
       </c>
-      <c r="M11" s="245">
+      <c r="T11" s="261">
+        <v>25.0</v>
+      </c>
+      <c r="U11" s="261">
         <v>26.0</v>
       </c>
-      <c r="N11" s="245">
-        <v>28.0</v>
-      </c>
-      <c r="O11" s="245">
+      <c r="V11" s="261">
+        <v>26.0</v>
+      </c>
+      <c r="W11" s="261">
+        <v>26.0</v>
+      </c>
+      <c r="X11" s="261">
+        <v>26.0</v>
+      </c>
+      <c r="Y11" s="262">
+        <v>25.0</v>
+      </c>
+      <c r="Z11" s="260">
+        <v>25.0</v>
+      </c>
+      <c r="AA11" s="261">
+        <v>26.0</v>
+      </c>
+      <c r="AB11" s="261">
         <v>27.0</v>
       </c>
-      <c r="P11" s="245">
+      <c r="AC11" s="261">
+        <v>25.0</v>
+      </c>
+      <c r="AD11" s="261">
         <v>26.0</v>
       </c>
-      <c r="Q11" s="245">
-        <v>26.0</v>
-      </c>
-      <c r="R11" s="245">
-        <v>25.0</v>
-      </c>
-      <c r="S11" s="245">
-        <v>25.0</v>
-      </c>
-      <c r="T11" s="245">
-        <v>25.0</v>
-      </c>
-      <c r="U11" s="245">
-        <v>27.0</v>
-      </c>
-      <c r="V11" s="245">
-        <v>28.0</v>
-      </c>
-      <c r="W11" s="245">
-        <v>26.0</v>
-      </c>
-      <c r="X11" s="245">
-        <v>26.0</v>
-      </c>
-      <c r="Y11" s="245">
-        <v>25.0</v>
-      </c>
-      <c r="Z11" s="245">
-        <v>25.0</v>
-      </c>
-      <c r="AA11" s="245">
-        <v>25.0</v>
-      </c>
-      <c r="AB11" s="245">
-        <v>27.0</v>
-      </c>
-      <c r="AC11" s="245">
-        <v>25.0</v>
-      </c>
-      <c r="AD11" s="245">
-        <v>26.0</v>
-      </c>
-      <c r="AE11" s="245">
+      <c r="AE11" s="262">
         <v>26.0</v>
       </c>
     </row>
@@ -51085,11 +51275,11 @@
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
-      <c r="B1" s="250" t="s">
+      <c r="B1" s="263" t="s">
+        <v>273</v>
+      </c>
+      <c r="C1" s="263" t="s">
         <v>274</v>
-      </c>
-      <c r="C1" s="250" t="s">
-        <v>275</v>
       </c>
     </row>
     <row r="2">
@@ -51100,7 +51290,7 @@
         <v>46272.0</v>
       </c>
       <c r="C2" s="161" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
   </sheetData>

--- a/uploads/ORIGINAL7.xlsx
+++ b/uploads/ORIGINAL7.xlsx
@@ -24862,8 +24862,8 @@
       <c r="L17" s="223" t="s">
         <v>48</v>
       </c>
-      <c r="M17" s="208" t="s">
-        <v>47</v>
+      <c r="M17" s="203" t="s">
+        <v>45</v>
       </c>
       <c r="N17" s="206" t="s">
         <v>45</v>
@@ -24937,7 +24937,7 @@
       </c>
       <c r="AK17" s="49">
         <f t="shared" si="5"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AL17" s="50">
         <f t="shared" si="6"/>
@@ -24945,7 +24945,7 @@
       </c>
       <c r="AM17" s="51">
         <f t="shared" si="7"/>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AN17" s="52">
         <f t="shared" ref="AN17:AO17" si="19">COUNTIF($C17:$AF17,"PH")</f>
@@ -25951,7 +25951,7 @@
         <v>47</v>
       </c>
       <c r="M25" s="203" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="N25" s="206" t="s">
         <v>43</v>
@@ -26025,7 +26025,7 @@
       </c>
       <c r="AK25" s="49">
         <f t="shared" si="5"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL25" s="50">
         <f t="shared" si="6"/>
@@ -26033,7 +26033,7 @@
       </c>
       <c r="AM25" s="51">
         <f t="shared" si="7"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AN25" s="52">
         <f t="shared" ref="AN25:AO25" si="27">COUNTIF($C25:$AF25,"PH")</f>
@@ -42262,7 +42262,7 @@
         <v>48</v>
       </c>
       <c r="M15" s="288" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="N15" s="288" t="s">
         <v>45</v>
@@ -43062,7 +43062,7 @@
         <v>47</v>
       </c>
       <c r="M23" s="288" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="N23" s="288" t="s">
         <v>43</v>
@@ -51489,7 +51489,7 @@
         <v>48</v>
       </c>
       <c r="M15" s="288" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="N15" s="288" t="s">
         <v>45</v>
@@ -52289,7 +52289,7 @@
         <v>47</v>
       </c>
       <c r="M23" s="288" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="N23" s="288" t="s">
         <v>43</v>

--- a/uploads/ORIGINAL7.xlsx
+++ b/uploads/ORIGINAL7.xlsx
@@ -21602,7 +21602,7 @@
         <v>127</v>
       </c>
       <c r="B9" s="162">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="10">
@@ -21618,7 +21618,7 @@
         <v>136</v>
       </c>
       <c r="B11" s="162">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="12">
@@ -21626,7 +21626,7 @@
         <v>152</v>
       </c>
       <c r="B12" s="162">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="13">
@@ -21642,7 +21642,7 @@
         <v>167</v>
       </c>
       <c r="B14" s="162">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="15">
@@ -21650,7 +21650,7 @@
         <v>164</v>
       </c>
       <c r="B15" s="162">
-        <v>1.0</v>
+        <v>5.0</v>
       </c>
     </row>
   </sheetData>
@@ -23243,7 +23243,7 @@
         <v>45</v>
       </c>
       <c r="Q5" s="199" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="R5" s="196" t="s">
         <v>53</v>
@@ -23297,11 +23297,11 @@
       </c>
       <c r="AI5" s="48">
         <f t="shared" ref="AI5:AI46" si="3">COUNTIF($C5:$AF5,"D5")</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AJ5" s="48">
         <f t="shared" ref="AJ5:AJ46" si="4">COUNTIF($C5:$AF5,"C6")</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AK5" s="49">
         <f t="shared" ref="AK5:AK46" si="5">COUNTIF($C5:$AF5,"B5")</f>
@@ -23337,7 +23337,7 @@
         <v>62</v>
       </c>
       <c r="C6" s="203" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D6" s="58" t="s">
         <v>53</v>
@@ -23379,7 +23379,7 @@
         <v>45</v>
       </c>
       <c r="Q6" s="206" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="R6" s="58" t="s">
         <v>53</v>
@@ -23387,14 +23387,14 @@
       <c r="S6" s="204" t="s">
         <v>53</v>
       </c>
-      <c r="T6" s="208" t="s">
-        <v>47</v>
+      <c r="T6" s="203" t="s">
+        <v>46</v>
       </c>
       <c r="U6" s="206" t="s">
         <v>46</v>
       </c>
       <c r="V6" s="206" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="W6" s="206" t="s">
         <v>44</v>
@@ -23429,15 +23429,15 @@
       <c r="AG6" s="25"/>
       <c r="AH6" s="47">
         <f t="shared" si="2"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AI6" s="48">
         <f t="shared" si="3"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AJ6" s="48">
         <f t="shared" si="4"/>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AK6" s="49">
         <f t="shared" si="5"/>
@@ -23449,7 +23449,7 @@
       </c>
       <c r="AM6" s="51">
         <f t="shared" si="7"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AN6" s="52">
         <f t="shared" ref="AN6:AO6" si="8">COUNTIF($C6:$AF6,"PH")</f>
@@ -23553,11 +23553,11 @@
       <c r="AC7" s="213" t="s">
         <v>49</v>
       </c>
-      <c r="AD7" s="81" t="s">
-        <v>47</v>
-      </c>
-      <c r="AE7" s="206" t="s">
-        <v>43</v>
+      <c r="AD7" s="57" t="s">
+        <v>48</v>
+      </c>
+      <c r="AE7" s="57" t="s">
+        <v>48</v>
       </c>
       <c r="AF7" s="214" t="s">
         <v>43</v>
@@ -23565,11 +23565,11 @@
       <c r="AG7" s="25"/>
       <c r="AH7" s="47">
         <f t="shared" si="2"/>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AI7" s="48">
         <f t="shared" si="3"/>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AJ7" s="48">
         <f t="shared" si="4"/>
@@ -23585,7 +23585,7 @@
       </c>
       <c r="AM7" s="51">
         <f t="shared" si="7"/>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AN7" s="52">
         <f t="shared" ref="AN7:AO7" si="9">COUNTIF($C7:$AF7,"PH")</f>
@@ -23778,7 +23778,7 @@
         <v>44</v>
       </c>
       <c r="N9" s="206" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="O9" s="57" t="s">
         <v>48</v>
@@ -23825,8 +23825,8 @@
       <c r="AC9" s="57" t="s">
         <v>48</v>
       </c>
-      <c r="AD9" s="81" t="s">
-        <v>47</v>
+      <c r="AD9" s="206" t="s">
+        <v>45</v>
       </c>
       <c r="AE9" s="207" t="s">
         <v>45</v>
@@ -23841,15 +23841,15 @@
       </c>
       <c r="AI9" s="48">
         <f t="shared" si="3"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AJ9" s="48">
         <f t="shared" si="4"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AK9" s="49">
         <f t="shared" si="5"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AL9" s="50">
         <f t="shared" si="6"/>
@@ -23857,7 +23857,7 @@
       </c>
       <c r="AM9" s="51">
         <f t="shared" si="7"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AN9" s="52">
         <f t="shared" ref="AN9:AO9" si="11">COUNTIF($C9:$AF9,"PH")</f>
@@ -23881,7 +23881,7 @@
         <v>74</v>
       </c>
       <c r="C10" s="221" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="D10" s="206" t="s">
         <v>43</v>
@@ -23920,13 +23920,13 @@
         <v>49</v>
       </c>
       <c r="P10" s="206" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="Q10" s="206" t="s">
+        <v>47</v>
+      </c>
+      <c r="R10" s="206" t="s">
         <v>44</v>
-      </c>
-      <c r="R10" s="206" t="s">
-        <v>43</v>
       </c>
       <c r="S10" s="204" t="s">
         <v>53</v>
@@ -23944,7 +23944,7 @@
         <v>45</v>
       </c>
       <c r="X10" s="206" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="Y10" s="206" t="s">
         <v>44</v>
@@ -23962,10 +23962,10 @@
         <v>49</v>
       </c>
       <c r="AD10" s="206" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="AE10" s="206" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="AF10" s="222" t="s">
         <v>49</v>
@@ -23973,27 +23973,27 @@
       <c r="AG10" s="25"/>
       <c r="AH10" s="47">
         <f t="shared" si="2"/>
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AI10" s="48">
         <f t="shared" si="3"/>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AJ10" s="48">
         <f t="shared" si="4"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AK10" s="49">
         <f t="shared" si="5"/>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AL10" s="50">
         <f t="shared" si="6"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AM10" s="51">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AN10" s="52">
         <f t="shared" ref="AN10:AO10" si="12">COUNTIF($C10:$AF10,"PH")</f>
@@ -24050,7 +24050,7 @@
         <v>47</v>
       </c>
       <c r="N11" s="206" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="O11" s="206" t="s">
         <v>45</v>
@@ -24101,7 +24101,7 @@
         <v>45</v>
       </c>
       <c r="AE11" s="206" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="AF11" s="204" t="s">
         <v>53</v>
@@ -24113,15 +24113,15 @@
       </c>
       <c r="AI11" s="48">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AJ11" s="48">
         <f t="shared" si="4"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AK11" s="49">
         <f t="shared" si="5"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AL11" s="50">
         <f t="shared" si="6"/>
@@ -24129,7 +24129,7 @@
       </c>
       <c r="AM11" s="51">
         <f t="shared" si="7"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AN11" s="52">
         <f t="shared" ref="AN11:AO11" si="13">COUNTIF($C11:$AF11,"PH")</f>
@@ -24425,7 +24425,7 @@
         <v>86</v>
       </c>
       <c r="C14" s="203" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D14" s="206" t="s">
         <v>43</v>
@@ -24446,7 +24446,7 @@
         <v>48</v>
       </c>
       <c r="J14" s="206" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="K14" s="206" t="s">
         <v>43</v>
@@ -24482,7 +24482,7 @@
         <v>47</v>
       </c>
       <c r="V14" s="206" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="W14" s="206" t="s">
         <v>45</v>
@@ -24506,7 +24506,7 @@
         <v>47</v>
       </c>
       <c r="AD14" s="206" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="AE14" s="57" t="s">
         <v>48</v>
@@ -24517,7 +24517,7 @@
       <c r="AG14" s="25"/>
       <c r="AH14" s="47">
         <f t="shared" si="2"/>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AI14" s="48">
         <f t="shared" si="3"/>
@@ -24525,19 +24525,19 @@
       </c>
       <c r="AJ14" s="48">
         <f t="shared" si="4"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AK14" s="49">
         <f t="shared" si="5"/>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AL14" s="50">
         <f t="shared" si="6"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM14" s="51">
         <f t="shared" si="7"/>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AN14" s="52">
         <f t="shared" ref="AN14:AO14" si="16">COUNTIF($C14:$AF14,"PH")</f>
@@ -24984,7 +24984,7 @@
         <v>47</v>
       </c>
       <c r="H18" s="206" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I18" s="206" t="s">
         <v>44</v>
@@ -25005,7 +25005,7 @@
         <v>47</v>
       </c>
       <c r="O18" s="206" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="P18" s="206" t="s">
         <v>45</v>
@@ -25077,11 +25077,11 @@
       </c>
       <c r="AL18" s="50">
         <f t="shared" si="6"/>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AM18" s="51">
         <f t="shared" si="7"/>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AN18" s="52">
         <f t="shared" ref="AN18:AO18" si="20">COUNTIF($C18:$AF18,"PH")</f>
@@ -25111,7 +25111,7 @@
         <v>53</v>
       </c>
       <c r="E19" s="214" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F19" s="203" t="s">
         <v>47</v>
@@ -25138,7 +25138,7 @@
         <v>47</v>
       </c>
       <c r="N19" s="206" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="O19" s="206" t="s">
         <v>43</v>
@@ -25156,10 +25156,10 @@
         <v>47</v>
       </c>
       <c r="T19" s="203" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="U19" s="206" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="V19" s="206" t="s">
         <v>43</v>
@@ -25197,7 +25197,7 @@
       <c r="AG19" s="25"/>
       <c r="AH19" s="47">
         <f t="shared" si="2"/>
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AI19" s="48">
         <f t="shared" si="3"/>
@@ -25205,19 +25205,19 @@
       </c>
       <c r="AJ19" s="48">
         <f t="shared" si="4"/>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AK19" s="49">
         <f t="shared" si="5"/>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AL19" s="50">
         <f t="shared" si="6"/>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AM19" s="51">
         <f t="shared" si="7"/>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AN19" s="52">
         <f t="shared" ref="AN19:AO19" si="21">COUNTIF($C19:$AF19,"PH")</f>
@@ -25309,8 +25309,8 @@
       <c r="Y20" s="81" t="s">
         <v>47</v>
       </c>
-      <c r="Z20" s="226" t="s">
-        <v>47</v>
+      <c r="Z20" s="214" t="s">
+        <v>46</v>
       </c>
       <c r="AA20" s="203" t="s">
         <v>46</v>
@@ -25349,11 +25349,11 @@
       </c>
       <c r="AL20" s="50">
         <f t="shared" si="6"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AM20" s="51">
         <f t="shared" si="7"/>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AN20" s="52">
         <f t="shared" ref="AN20:AO20" si="22">COUNTIF($C20:$AF20,"PH")</f>
@@ -25824,7 +25824,7 @@
         <v>53</v>
       </c>
       <c r="P24" s="206" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="Q24" s="206" t="s">
         <v>45</v>
@@ -25889,11 +25889,11 @@
       </c>
       <c r="AK24" s="49">
         <f t="shared" si="5"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AL24" s="50">
         <f t="shared" si="6"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AM24" s="51">
         <f t="shared" si="7"/>
@@ -26098,8 +26098,8 @@
       <c r="P26" s="81" t="s">
         <v>47</v>
       </c>
-      <c r="Q26" s="81" t="s">
-        <v>47</v>
+      <c r="Q26" s="206" t="s">
+        <v>45</v>
       </c>
       <c r="R26" s="206" t="s">
         <v>43</v>
@@ -26161,7 +26161,7 @@
       </c>
       <c r="AK26" s="49">
         <f t="shared" si="5"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AL26" s="50">
         <f t="shared" si="6"/>
@@ -26169,7 +26169,7 @@
       </c>
       <c r="AM26" s="51">
         <f t="shared" si="7"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AN26" s="52">
         <f t="shared" ref="AN26:AO26" si="28">COUNTIF($C26:$AF26,"PH")</f>
@@ -26199,7 +26199,7 @@
         <v>45</v>
       </c>
       <c r="E27" s="224" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F27" s="230" t="s">
         <v>43</v>
@@ -26220,7 +26220,7 @@
         <v>45</v>
       </c>
       <c r="L27" s="224" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="M27" s="230" t="s">
         <v>43</v>
@@ -26232,13 +26232,13 @@
         <v>53</v>
       </c>
       <c r="P27" s="206" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="Q27" s="207" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="R27" s="207" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="S27" s="214" t="s">
         <v>44</v>
@@ -26285,27 +26285,27 @@
       <c r="AG27" s="25"/>
       <c r="AH27" s="47">
         <f t="shared" si="2"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AI27" s="48">
         <f t="shared" si="3"/>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AJ27" s="48">
         <f t="shared" si="4"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AK27" s="49">
         <f t="shared" si="5"/>
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AL27" s="50">
         <f t="shared" si="6"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AM27" s="51">
         <f t="shared" si="7"/>
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AN27" s="52">
         <f t="shared" ref="AN27:AO27" si="29">COUNTIF($C27:$AF27,"PH")</f>
@@ -26358,8 +26358,8 @@
       <c r="L28" s="226" t="s">
         <v>47</v>
       </c>
-      <c r="M28" s="203" t="s">
-        <v>45</v>
+      <c r="M28" s="213" t="s">
+        <v>49</v>
       </c>
       <c r="N28" s="213" t="s">
         <v>49</v>
@@ -26433,7 +26433,7 @@
       </c>
       <c r="AK28" s="49">
         <f t="shared" si="5"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AL28" s="50">
         <f t="shared" si="6"/>
@@ -26445,11 +26445,11 @@
       </c>
       <c r="AN28" s="52">
         <f t="shared" ref="AN28:AO28" si="30">COUNTIF($C28:$AF28,"PH")</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AO28" s="52">
         <f t="shared" si="30"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AP28" s="67"/>
       <c r="AQ28" s="67"/>
@@ -26486,7 +26486,7 @@
         <v>45</v>
       </c>
       <c r="J29" s="206" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="K29" s="206" t="s">
         <v>44</v>
@@ -26513,7 +26513,7 @@
         <v>45</v>
       </c>
       <c r="S29" s="224" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="T29" s="212" t="s">
         <v>53</v>
@@ -26521,8 +26521,8 @@
       <c r="U29" s="58" t="s">
         <v>53</v>
       </c>
-      <c r="V29" s="206" t="s">
-        <v>45</v>
+      <c r="V29" s="213" t="s">
+        <v>49</v>
       </c>
       <c r="W29" s="206" t="s">
         <v>45</v>
@@ -26557,15 +26557,15 @@
       <c r="AG29" s="25"/>
       <c r="AH29" s="47">
         <f t="shared" si="2"/>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AI29" s="48">
         <f t="shared" si="3"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AJ29" s="48">
         <f t="shared" si="4"/>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AK29" s="49">
         <f t="shared" si="5"/>
@@ -26581,11 +26581,11 @@
       </c>
       <c r="AN29" s="52">
         <f t="shared" ref="AN29:AO29" si="31">COUNTIF($C29:$AF29,"PH")</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AO29" s="52">
         <f t="shared" si="31"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AP29" s="67"/>
       <c r="AQ29" s="67"/>
@@ -26613,7 +26613,7 @@
         <v>47</v>
       </c>
       <c r="G30" s="206" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="H30" s="57" t="s">
         <v>48</v>
@@ -26658,10 +26658,10 @@
         <v>46</v>
       </c>
       <c r="V30" s="206" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="W30" s="206" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="X30" s="206" t="s">
         <v>43</v>
@@ -26681,11 +26681,11 @@
       <c r="AC30" s="206" t="s">
         <v>44</v>
       </c>
-      <c r="AD30" s="57" t="s">
-        <v>48</v>
-      </c>
-      <c r="AE30" s="57" t="s">
-        <v>48</v>
+      <c r="AD30" s="206" t="s">
+        <v>43</v>
+      </c>
+      <c r="AE30" s="206" t="s">
+        <v>43</v>
       </c>
       <c r="AF30" s="204" t="s">
         <v>53</v>
@@ -26693,23 +26693,23 @@
       <c r="AG30" s="25"/>
       <c r="AH30" s="47">
         <f t="shared" si="2"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AI30" s="48">
         <f t="shared" si="3"/>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AJ30" s="48">
         <f t="shared" si="4"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AK30" s="49">
         <f t="shared" si="5"/>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AL30" s="50">
         <f t="shared" si="6"/>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AM30" s="51">
         <f t="shared" si="7"/>
@@ -26751,8 +26751,8 @@
       <c r="G31" s="58" t="s">
         <v>53</v>
       </c>
-      <c r="H31" s="206" t="s">
-        <v>45</v>
+      <c r="H31" s="213" t="s">
+        <v>49</v>
       </c>
       <c r="I31" s="206" t="s">
         <v>45</v>
@@ -26800,7 +26800,7 @@
         <v>45</v>
       </c>
       <c r="X31" s="206" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="Y31" s="213" t="s">
         <v>49</v>
@@ -26808,8 +26808,8 @@
       <c r="Z31" s="222" t="s">
         <v>49</v>
       </c>
-      <c r="AA31" s="205" t="s">
-        <v>49</v>
+      <c r="AA31" s="58" t="s">
+        <v>53</v>
       </c>
       <c r="AB31" s="58" t="s">
         <v>53</v>
@@ -26829,7 +26829,7 @@
       <c r="AG31" s="25"/>
       <c r="AH31" s="47">
         <f t="shared" si="2"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AI31" s="48">
         <f t="shared" si="3"/>
@@ -26837,11 +26837,11 @@
       </c>
       <c r="AJ31" s="48">
         <f t="shared" si="4"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AK31" s="49">
         <f t="shared" si="5"/>
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AL31" s="50">
         <f t="shared" si="6"/>
@@ -26900,7 +26900,7 @@
         <v>45</v>
       </c>
       <c r="L32" s="214" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="M32" s="212" t="s">
         <v>53</v>
@@ -26921,7 +26921,7 @@
         <v>44</v>
       </c>
       <c r="S32" s="214" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="T32" s="212" t="s">
         <v>53</v>
@@ -26929,17 +26929,17 @@
       <c r="U32" s="58" t="s">
         <v>53</v>
       </c>
-      <c r="V32" s="81" t="s">
-        <v>47</v>
+      <c r="V32" s="206" t="s">
+        <v>46</v>
       </c>
       <c r="W32" s="206" t="s">
         <v>46</v>
       </c>
       <c r="X32" s="206" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="Y32" s="206" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="Z32" s="214" t="s">
         <v>43</v>
@@ -26957,7 +26957,7 @@
         <v>46</v>
       </c>
       <c r="AE32" s="206" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="AF32" s="214" t="s">
         <v>44</v>
@@ -26965,11 +26965,11 @@
       <c r="AG32" s="25"/>
       <c r="AH32" s="47">
         <f t="shared" si="2"/>
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AI32" s="48">
         <f t="shared" si="3"/>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AJ32" s="48">
         <f t="shared" si="4"/>
@@ -26981,11 +26981,11 @@
       </c>
       <c r="AL32" s="50">
         <f t="shared" si="6"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AM32" s="51">
         <f t="shared" si="7"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AN32" s="52">
         <f t="shared" ref="AN32:AO32" si="34">COUNTIF($C32:$AF32,"PH")</f>
@@ -27178,7 +27178,7 @@
         <v>45</v>
       </c>
       <c r="N34" s="206" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="O34" s="206" t="s">
         <v>44</v>
@@ -27199,7 +27199,7 @@
         <v>45</v>
       </c>
       <c r="U34" s="206" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="V34" s="206" t="s">
         <v>44</v>
@@ -27214,7 +27214,7 @@
         <v>47</v>
       </c>
       <c r="Z34" s="214" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="AA34" s="203" t="s">
         <v>44</v>
@@ -27223,7 +27223,7 @@
         <v>43</v>
       </c>
       <c r="AC34" s="206" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="AD34" s="58" t="s">
         <v>53</v>
@@ -27239,23 +27239,23 @@
       </c>
       <c r="AH34" s="47">
         <f t="shared" si="2"/>
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AI34" s="48">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AJ34" s="48">
         <f t="shared" si="4"/>
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AK34" s="49">
         <f t="shared" si="5"/>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AL34" s="50">
         <f t="shared" si="6"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AM34" s="51">
         <f t="shared" si="7"/>
@@ -27325,10 +27325,10 @@
         <v>48</v>
       </c>
       <c r="Q35" s="206" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="R35" s="206" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="S35" s="214" t="s">
         <v>45</v>
@@ -27346,7 +27346,7 @@
         <v>47</v>
       </c>
       <c r="X35" s="206" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="Y35" s="206" t="s">
         <v>45</v>
@@ -27366,8 +27366,8 @@
       <c r="AD35" s="57" t="s">
         <v>48</v>
       </c>
-      <c r="AE35" s="81" t="s">
-        <v>47</v>
+      <c r="AE35" s="206" t="s">
+        <v>45</v>
       </c>
       <c r="AF35" s="214" t="s">
         <v>45</v>
@@ -27387,7 +27387,7 @@
       </c>
       <c r="AK35" s="49">
         <f t="shared" si="5"/>
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="AL35" s="50">
         <f t="shared" si="6"/>
@@ -27395,7 +27395,7 @@
       </c>
       <c r="AM35" s="51">
         <f t="shared" si="7"/>
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="AN35" s="52">
         <f t="shared" ref="AN35:AO35" si="37">COUNTIF($C35:$AF35,"PH")</f>
@@ -27418,11 +27418,11 @@
       <c r="B36" s="202" t="s">
         <v>153</v>
       </c>
-      <c r="C36" s="234" t="s">
-        <v>47</v>
+      <c r="C36" s="221" t="s">
+        <v>45</v>
       </c>
       <c r="D36" s="219" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E36" s="214" t="s">
         <v>44</v>
@@ -27439,8 +27439,8 @@
       <c r="I36" s="213" t="s">
         <v>49</v>
       </c>
-      <c r="J36" s="219" t="s">
-        <v>47</v>
+      <c r="J36" s="213" t="s">
+        <v>49</v>
       </c>
       <c r="K36" s="206" t="s">
         <v>45</v>
@@ -27448,8 +27448,8 @@
       <c r="L36" s="214" t="s">
         <v>44</v>
       </c>
-      <c r="M36" s="203" t="s">
-        <v>43</v>
+      <c r="M36" s="213" t="s">
+        <v>49</v>
       </c>
       <c r="N36" s="58" t="s">
         <v>53</v>
@@ -27460,8 +27460,8 @@
       <c r="P36" s="217" t="s">
         <v>47</v>
       </c>
-      <c r="Q36" s="219" t="s">
-        <v>46</v>
+      <c r="Q36" s="217" t="s">
+        <v>47</v>
       </c>
       <c r="R36" s="206" t="s">
         <v>45</v>
@@ -27499,7 +27499,7 @@
       <c r="AC36" s="58" t="s">
         <v>53</v>
       </c>
-      <c r="AD36" s="217" t="s">
+      <c r="AD36" s="81" t="s">
         <v>47</v>
       </c>
       <c r="AE36" s="219" t="s">
@@ -27511,11 +27511,11 @@
       <c r="AG36" s="25"/>
       <c r="AH36" s="47">
         <f t="shared" si="2"/>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AI36" s="48">
         <f t="shared" si="3"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AJ36" s="48">
         <f t="shared" si="4"/>
@@ -27523,23 +27523,23 @@
       </c>
       <c r="AK36" s="49">
         <f t="shared" si="5"/>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AL36" s="50">
         <f t="shared" si="6"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AM36" s="51">
         <f t="shared" si="7"/>
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AN36" s="52">
         <f t="shared" ref="AN36:AO36" si="38">COUNTIF($C36:$AF36,"PH")</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AO36" s="52">
         <f t="shared" si="38"/>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AP36" s="67"/>
       <c r="AQ36" s="67"/>
@@ -27554,8 +27554,8 @@
       <c r="B37" s="202" t="s">
         <v>156</v>
       </c>
-      <c r="C37" s="208" t="s">
-        <v>47</v>
+      <c r="C37" s="203" t="s">
+        <v>43</v>
       </c>
       <c r="D37" s="206" t="s">
         <v>43</v>
@@ -27647,11 +27647,11 @@
       <c r="AG37" s="25"/>
       <c r="AH37" s="47">
         <f t="shared" si="2"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AI37" s="48">
         <f t="shared" si="3"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AJ37" s="48">
         <f t="shared" si="4"/>
@@ -27667,7 +27667,7 @@
       </c>
       <c r="AM37" s="51">
         <f t="shared" si="7"/>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AN37" s="52">
         <f t="shared" ref="AN37:AO37" si="39">COUNTIF($C37:$AF37,"PH")</f>
@@ -27697,7 +27697,7 @@
         <v>46</v>
       </c>
       <c r="E38" s="214" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F38" s="203" t="s">
         <v>43</v>
@@ -27745,7 +27745,7 @@
         <v>44</v>
       </c>
       <c r="U38" s="206" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="V38" s="58" t="s">
         <v>53</v>
@@ -27787,11 +27787,11 @@
       </c>
       <c r="AI38" s="48">
         <f t="shared" si="3"/>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AJ38" s="48">
         <f t="shared" si="4"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AK38" s="49">
         <f t="shared" si="5"/>
@@ -27827,7 +27827,7 @@
         <v>162</v>
       </c>
       <c r="C39" s="203" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D39" s="207" t="s">
         <v>43</v>
@@ -27841,14 +27841,14 @@
       <c r="G39" s="58" t="s">
         <v>53</v>
       </c>
-      <c r="H39" s="81" t="s">
-        <v>47</v>
+      <c r="H39" s="206" t="s">
+        <v>46</v>
       </c>
       <c r="I39" s="206" t="s">
         <v>45</v>
       </c>
       <c r="J39" s="206" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="K39" s="206" t="s">
         <v>44</v>
@@ -27862,11 +27862,11 @@
       <c r="N39" s="58" t="s">
         <v>53</v>
       </c>
-      <c r="O39" s="81" t="s">
-        <v>47</v>
-      </c>
-      <c r="P39" s="81" t="s">
-        <v>47</v>
+      <c r="O39" s="206" t="s">
+        <v>46</v>
+      </c>
+      <c r="P39" s="206" t="s">
+        <v>46</v>
       </c>
       <c r="Q39" s="206" t="s">
         <v>46</v>
@@ -27887,7 +27887,7 @@
         <v>49</v>
       </c>
       <c r="W39" s="206" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="X39" s="206" t="s">
         <v>45</v>
@@ -27908,7 +27908,7 @@
         <v>46</v>
       </c>
       <c r="AD39" s="206" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="AE39" s="206" t="s">
         <v>43</v>
@@ -27919,15 +27919,15 @@
       <c r="AG39" s="25"/>
       <c r="AH39" s="47">
         <f t="shared" si="2"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AI39" s="48">
         <f t="shared" si="3"/>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AJ39" s="48">
         <f t="shared" si="4"/>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AK39" s="49">
         <f t="shared" si="5"/>
@@ -27935,11 +27935,11 @@
       </c>
       <c r="AL39" s="50">
         <f t="shared" si="6"/>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AM39" s="51">
         <f t="shared" si="7"/>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AN39" s="52">
         <f t="shared" ref="AN39:AO39" si="41">COUNTIF($C39:$AF39,"PH")</f>
@@ -27983,8 +27983,8 @@
       <c r="I40" s="58" t="s">
         <v>53</v>
       </c>
-      <c r="J40" s="213" t="s">
-        <v>49</v>
+      <c r="J40" s="206" t="s">
+        <v>45</v>
       </c>
       <c r="K40" s="206" t="s">
         <v>45</v>
@@ -27992,11 +27992,11 @@
       <c r="L40" s="214" t="s">
         <v>45</v>
       </c>
-      <c r="M40" s="205" t="s">
-        <v>49</v>
-      </c>
-      <c r="N40" s="213" t="s">
-        <v>49</v>
+      <c r="M40" s="206" t="s">
+        <v>45</v>
+      </c>
+      <c r="N40" s="206" t="s">
+        <v>43</v>
       </c>
       <c r="O40" s="58" t="s">
         <v>53</v>
@@ -28004,11 +28004,11 @@
       <c r="P40" s="58" t="s">
         <v>53</v>
       </c>
-      <c r="Q40" s="213" t="s">
-        <v>49</v>
+      <c r="Q40" s="206" t="s">
+        <v>46</v>
       </c>
       <c r="R40" s="206" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="S40" s="222" t="s">
         <v>49</v>
@@ -28055,23 +28055,23 @@
       <c r="AG40" s="25"/>
       <c r="AH40" s="47">
         <f t="shared" si="2"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AI40" s="48">
         <f t="shared" si="3"/>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AJ40" s="48">
         <f t="shared" si="4"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AK40" s="49">
         <f t="shared" si="5"/>
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AL40" s="50">
         <f t="shared" si="6"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AM40" s="51">
         <f t="shared" si="7"/>
@@ -28079,11 +28079,11 @@
       </c>
       <c r="AN40" s="52">
         <f t="shared" ref="AN40:AO40" si="42">COUNTIF($C40:$AF40,"PH")</f>
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AO40" s="52">
         <f t="shared" si="42"/>
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AP40" s="67"/>
       <c r="AQ40" s="67"/>
@@ -28104,8 +28104,8 @@
       <c r="D41" s="58" t="s">
         <v>53</v>
       </c>
-      <c r="E41" s="226" t="s">
-        <v>47</v>
+      <c r="E41" s="214" t="s">
+        <v>46</v>
       </c>
       <c r="F41" s="203" t="s">
         <v>45</v>
@@ -28113,8 +28113,8 @@
       <c r="G41" s="206" t="s">
         <v>43</v>
       </c>
-      <c r="H41" s="213" t="s">
-        <v>49</v>
+      <c r="H41" s="206" t="s">
+        <v>43</v>
       </c>
       <c r="I41" s="206" t="s">
         <v>43</v>
@@ -28125,11 +28125,11 @@
       <c r="K41" s="58" t="s">
         <v>53</v>
       </c>
-      <c r="L41" s="226" t="s">
-        <v>47</v>
-      </c>
-      <c r="M41" s="205" t="s">
-        <v>49</v>
+      <c r="L41" s="214" t="s">
+        <v>46</v>
+      </c>
+      <c r="M41" s="206" t="s">
+        <v>45</v>
       </c>
       <c r="N41" s="206" t="s">
         <v>45</v>
@@ -28146,8 +28146,8 @@
       <c r="R41" s="58" t="s">
         <v>53</v>
       </c>
-      <c r="S41" s="226" t="s">
-        <v>47</v>
+      <c r="S41" s="214" t="s">
+        <v>46</v>
       </c>
       <c r="T41" s="203" t="s">
         <v>45</v>
@@ -28155,8 +28155,8 @@
       <c r="U41" s="206" t="s">
         <v>45</v>
       </c>
-      <c r="V41" s="213" t="s">
-        <v>49</v>
+      <c r="V41" s="206" t="s">
+        <v>45</v>
       </c>
       <c r="W41" s="206" t="s">
         <v>43</v>
@@ -28191,11 +28191,11 @@
       <c r="AG41" s="25"/>
       <c r="AH41" s="47">
         <f t="shared" si="2"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AI41" s="48">
         <f t="shared" si="3"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AJ41" s="48">
         <f t="shared" si="4"/>
@@ -28203,23 +28203,23 @@
       </c>
       <c r="AK41" s="49">
         <f t="shared" si="5"/>
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AL41" s="50">
         <f t="shared" si="6"/>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AM41" s="51">
         <f t="shared" si="7"/>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AN41" s="52">
         <f t="shared" ref="AN41:AO41" si="43">COUNTIF($C41:$AF41,"PH")</f>
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AO41" s="52">
         <f t="shared" si="43"/>
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AP41" s="67"/>
       <c r="AQ41" s="67"/>
@@ -28268,7 +28268,7 @@
         <v>45</v>
       </c>
       <c r="N42" s="237" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="O42" s="237" t="s">
         <v>43</v>
@@ -28327,7 +28327,7 @@
       <c r="AG42" s="25"/>
       <c r="AH42" s="47">
         <f t="shared" si="2"/>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AI42" s="48">
         <f t="shared" si="3"/>
@@ -28335,11 +28335,11 @@
       </c>
       <c r="AJ42" s="48">
         <f t="shared" si="4"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AK42" s="49">
         <f t="shared" si="5"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AL42" s="50">
         <f t="shared" si="6"/>
@@ -28401,7 +28401,7 @@
         <v>45</v>
       </c>
       <c r="M43" s="203" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="N43" s="206" t="s">
         <v>43</v>
@@ -28463,7 +28463,7 @@
       <c r="AG43" s="25"/>
       <c r="AH43" s="47">
         <f t="shared" si="2"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AI43" s="48">
         <f t="shared" si="3"/>
@@ -28471,11 +28471,11 @@
       </c>
       <c r="AJ43" s="48">
         <f t="shared" si="4"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AK43" s="49">
         <f t="shared" si="5"/>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AL43" s="50">
         <f t="shared" si="6"/>
@@ -28506,11 +28506,11 @@
       <c r="B44" s="228" t="s">
         <v>177</v>
       </c>
-      <c r="C44" s="203" t="s">
-        <v>45</v>
+      <c r="C44" s="221" t="s">
+        <v>47</v>
       </c>
       <c r="D44" s="206" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E44" s="214" t="s">
         <v>45</v>
@@ -28573,7 +28573,7 @@
         <v>46</v>
       </c>
       <c r="Y44" s="207" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="Z44" s="223" t="s">
         <v>48</v>
@@ -28599,7 +28599,7 @@
       <c r="AG44" s="25"/>
       <c r="AH44" s="47">
         <f t="shared" si="2"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AI44" s="48">
         <f t="shared" si="3"/>
@@ -28607,11 +28607,11 @@
       </c>
       <c r="AJ44" s="48">
         <f t="shared" si="4"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AK44" s="49">
         <f t="shared" si="5"/>
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="AL44" s="50">
         <f t="shared" si="6"/>
@@ -28619,7 +28619,7 @@
       </c>
       <c r="AM44" s="51">
         <f t="shared" si="7"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AN44" s="52">
         <f t="shared" ref="AN44:AO44" si="46">COUNTIF($C44:$AF44,"PH")</f>
@@ -28655,7 +28655,7 @@
         <v>49</v>
       </c>
       <c r="G45" s="237" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="H45" s="237" t="s">
         <v>43</v>
@@ -28670,7 +28670,7 @@
         <v>47</v>
       </c>
       <c r="L45" s="238" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="M45" s="203" t="s">
         <v>45</v>
@@ -28691,13 +28691,13 @@
         <v>47</v>
       </c>
       <c r="S45" s="238" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="T45" s="236" t="s">
         <v>45</v>
       </c>
       <c r="U45" s="206" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="V45" s="206" t="s">
         <v>43</v>
@@ -28712,7 +28712,7 @@
         <v>47</v>
       </c>
       <c r="Z45" s="214" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="AA45" s="203" t="s">
         <v>45</v>
@@ -28721,7 +28721,7 @@
         <v>44</v>
       </c>
       <c r="AC45" s="206" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="AD45" s="58" t="s">
         <v>53</v>
@@ -28735,27 +28735,27 @@
       <c r="AG45" s="112"/>
       <c r="AH45" s="47">
         <f t="shared" si="2"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AI45" s="48">
         <f t="shared" si="3"/>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AJ45" s="48">
         <f t="shared" si="4"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AK45" s="49">
         <f t="shared" si="5"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AL45" s="50">
         <f t="shared" si="6"/>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AM45" s="51">
         <f t="shared" si="7"/>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AN45" s="52">
         <f t="shared" ref="AN45:AO45" si="47">COUNTIF($C45:$AF45,"PH")</f>
@@ -28809,7 +28809,7 @@
         <v>45</v>
       </c>
       <c r="M46" s="245" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="N46" s="246" t="s">
         <v>43</v>
@@ -28875,11 +28875,11 @@
       </c>
       <c r="AI46" s="48">
         <f t="shared" si="3"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AJ46" s="48">
         <f t="shared" si="4"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AK46" s="49">
         <f t="shared" si="5"/>
@@ -29226,7 +29226,7 @@
       </c>
       <c r="N50" s="272">
         <f t="shared" si="48"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O50" s="272">
         <f t="shared" si="48"/>
@@ -29238,7 +29238,7 @@
       </c>
       <c r="Q50" s="272">
         <f t="shared" si="49"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="R50" s="272">
         <f t="shared" si="49"/>
@@ -29482,7 +29482,7 @@
       </c>
       <c r="H52" s="143">
         <f t="shared" si="55"/>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I52" s="143">
         <f t="shared" si="55"/>
@@ -29658,7 +29658,7 @@
       </c>
       <c r="Q53" s="140">
         <f t="shared" si="56"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R53" s="140">
         <f t="shared" si="56"/>
@@ -29762,7 +29762,7 @@
       </c>
       <c r="H54" s="140">
         <f t="shared" si="57"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I54" s="140">
         <f t="shared" si="57"/>
@@ -29798,7 +29798,7 @@
       </c>
       <c r="Q54" s="140">
         <f t="shared" si="57"/>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="R54" s="140">
         <f t="shared" si="57"/>
@@ -29978,7 +29978,7 @@
       </c>
       <c r="AA55" s="275">
         <f t="shared" si="58"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AB55" s="140">
         <f t="shared" si="58"/>
@@ -30206,7 +30206,7 @@
       </c>
       <c r="N57" s="140">
         <f t="shared" si="60"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O57" s="140">
         <f t="shared" si="60"/>
@@ -30218,7 +30218,7 @@
       </c>
       <c r="Q57" s="140">
         <f t="shared" si="60"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R57" s="140">
         <f t="shared" si="60"/>
@@ -30258,7 +30258,7 @@
       </c>
       <c r="AA57" s="275">
         <f t="shared" si="60"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AB57" s="140">
         <f t="shared" si="60"/>
@@ -30346,7 +30346,7 @@
       </c>
       <c r="N58" s="285">
         <f t="shared" si="61"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="O58" s="285">
         <f t="shared" si="61"/>
@@ -30358,7 +30358,7 @@
       </c>
       <c r="Q58" s="281">
         <f t="shared" si="61"/>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="R58" s="281">
         <f t="shared" si="61"/>
@@ -41074,7 +41074,7 @@
         <v>45</v>
       </c>
       <c r="Q3" s="288" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="R3" s="288" t="s">
         <v>53</v>
@@ -41132,7 +41132,7 @@
         <v>62</v>
       </c>
       <c r="C4" s="288" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D4" s="288" t="s">
         <v>53</v>
@@ -41174,7 +41174,7 @@
         <v>45</v>
       </c>
       <c r="Q4" s="288" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="R4" s="288" t="s">
         <v>53</v>
@@ -41183,13 +41183,13 @@
         <v>53</v>
       </c>
       <c r="T4" s="288" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="U4" s="288" t="s">
         <v>46</v>
       </c>
       <c r="V4" s="288" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="W4" s="288" t="s">
         <v>44</v>
@@ -41313,10 +41313,10 @@
         <v>49</v>
       </c>
       <c r="AD5" s="288" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="AE5" s="288" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="AF5" s="288" t="s">
         <v>43</v>
@@ -41465,7 +41465,7 @@
         <v>44</v>
       </c>
       <c r="N7" s="288" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="O7" s="288" t="s">
         <v>48</v>
@@ -41513,7 +41513,7 @@
         <v>48</v>
       </c>
       <c r="AD7" s="288" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="AE7" s="287" t="s">
         <v>45</v>
@@ -41532,7 +41532,7 @@
         <v>74</v>
       </c>
       <c r="C8" s="288" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="D8" s="288" t="s">
         <v>43</v>
@@ -41571,13 +41571,13 @@
         <v>49</v>
       </c>
       <c r="P8" s="288" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="Q8" s="288" t="s">
+        <v>47</v>
+      </c>
+      <c r="R8" s="288" t="s">
         <v>44</v>
-      </c>
-      <c r="R8" s="288" t="s">
-        <v>43</v>
       </c>
       <c r="S8" s="288" t="s">
         <v>53</v>
@@ -41595,7 +41595,7 @@
         <v>45</v>
       </c>
       <c r="X8" s="288" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="Y8" s="288" t="s">
         <v>44</v>
@@ -41613,10 +41613,10 @@
         <v>49</v>
       </c>
       <c r="AD8" s="288" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="AE8" s="288" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="AF8" s="288" t="s">
         <v>49</v>
@@ -41665,7 +41665,7 @@
         <v>47</v>
       </c>
       <c r="N9" s="288" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="O9" s="288" t="s">
         <v>45</v>
@@ -41716,7 +41716,7 @@
         <v>45</v>
       </c>
       <c r="AE9" s="288" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="AF9" s="288" t="s">
         <v>53</v>
@@ -41932,7 +41932,7 @@
         <v>86</v>
       </c>
       <c r="C12" s="288" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D12" s="288" t="s">
         <v>43</v>
@@ -41953,7 +41953,7 @@
         <v>48</v>
       </c>
       <c r="J12" s="288" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="K12" s="288" t="s">
         <v>43</v>
@@ -41989,7 +41989,7 @@
         <v>47</v>
       </c>
       <c r="V12" s="288" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="W12" s="288" t="s">
         <v>45</v>
@@ -42013,7 +42013,7 @@
         <v>47</v>
       </c>
       <c r="AD12" s="288" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="AE12" s="288" t="s">
         <v>48</v>
@@ -42347,7 +42347,7 @@
         <v>47</v>
       </c>
       <c r="H16" s="288" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I16" s="288" t="s">
         <v>44</v>
@@ -42368,7 +42368,7 @@
         <v>47</v>
       </c>
       <c r="O16" s="288" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="P16" s="288" t="s">
         <v>45</v>
@@ -42438,7 +42438,7 @@
         <v>53</v>
       </c>
       <c r="E17" s="288" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F17" s="288" t="s">
         <v>47</v>
@@ -42465,7 +42465,7 @@
         <v>47</v>
       </c>
       <c r="N17" s="288" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="O17" s="288" t="s">
         <v>43</v>
@@ -42483,10 +42483,10 @@
         <v>47</v>
       </c>
       <c r="T17" s="288" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="U17" s="288" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="V17" s="288" t="s">
         <v>43</v>
@@ -42601,7 +42601,7 @@
         <v>47</v>
       </c>
       <c r="Z18" s="288" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="AA18" s="288" t="s">
         <v>46</v>
@@ -42971,7 +42971,7 @@
         <v>53</v>
       </c>
       <c r="P22" s="288" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="Q22" s="288" t="s">
         <v>45</v>
@@ -43174,7 +43174,7 @@
         <v>47</v>
       </c>
       <c r="Q24" s="288" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="R24" s="288" t="s">
         <v>43</v>
@@ -43238,7 +43238,7 @@
         <v>45</v>
       </c>
       <c r="E25" s="287" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F25" s="287" t="s">
         <v>43</v>
@@ -43259,7 +43259,7 @@
         <v>45</v>
       </c>
       <c r="L25" s="287" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="M25" s="287" t="s">
         <v>43</v>
@@ -43271,13 +43271,13 @@
         <v>53</v>
       </c>
       <c r="P25" s="288" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="Q25" s="287" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="R25" s="287" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="S25" s="288" t="s">
         <v>44</v>
@@ -43362,7 +43362,7 @@
         <v>47</v>
       </c>
       <c r="M26" s="288" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="N26" s="288" t="s">
         <v>49</v>
@@ -43453,7 +43453,7 @@
         <v>45</v>
       </c>
       <c r="J27" s="288" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="K27" s="288" t="s">
         <v>44</v>
@@ -43480,7 +43480,7 @@
         <v>45</v>
       </c>
       <c r="S27" s="287" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="T27" s="288" t="s">
         <v>53</v>
@@ -43489,7 +43489,7 @@
         <v>53</v>
       </c>
       <c r="V27" s="288" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="W27" s="288" t="s">
         <v>45</v>
@@ -43544,7 +43544,7 @@
         <v>47</v>
       </c>
       <c r="G28" s="288" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="H28" s="288" t="s">
         <v>48</v>
@@ -43589,10 +43589,10 @@
         <v>46</v>
       </c>
       <c r="V28" s="288" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="W28" s="288" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="X28" s="288" t="s">
         <v>43</v>
@@ -43613,10 +43613,10 @@
         <v>44</v>
       </c>
       <c r="AD28" s="288" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="AE28" s="288" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="AF28" s="288" t="s">
         <v>53</v>
@@ -43647,7 +43647,7 @@
         <v>53</v>
       </c>
       <c r="H29" s="288" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="I29" s="288" t="s">
         <v>45</v>
@@ -43695,7 +43695,7 @@
         <v>45</v>
       </c>
       <c r="X29" s="288" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="Y29" s="288" t="s">
         <v>49</v>
@@ -43704,7 +43704,7 @@
         <v>49</v>
       </c>
       <c r="AA29" s="288" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="AB29" s="288" t="s">
         <v>53</v>
@@ -43759,7 +43759,7 @@
         <v>45</v>
       </c>
       <c r="L30" s="288" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="M30" s="288" t="s">
         <v>53</v>
@@ -43780,7 +43780,7 @@
         <v>44</v>
       </c>
       <c r="S30" s="288" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="T30" s="288" t="s">
         <v>53</v>
@@ -43789,16 +43789,16 @@
         <v>53</v>
       </c>
       <c r="V30" s="288" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="W30" s="288" t="s">
         <v>46</v>
       </c>
       <c r="X30" s="288" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="Y30" s="288" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="Z30" s="288" t="s">
         <v>43</v>
@@ -43816,7 +43816,7 @@
         <v>46</v>
       </c>
       <c r="AE30" s="288" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="AF30" s="288" t="s">
         <v>44</v>
@@ -43965,7 +43965,7 @@
         <v>45</v>
       </c>
       <c r="N32" s="288" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="O32" s="288" t="s">
         <v>44</v>
@@ -43986,7 +43986,7 @@
         <v>45</v>
       </c>
       <c r="U32" s="288" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="V32" s="288" t="s">
         <v>44</v>
@@ -44001,7 +44001,7 @@
         <v>47</v>
       </c>
       <c r="Z32" s="288" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="AA32" s="288" t="s">
         <v>44</v>
@@ -44010,7 +44010,7 @@
         <v>43</v>
       </c>
       <c r="AC32" s="288" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="AD32" s="288" t="s">
         <v>53</v>
@@ -44074,10 +44074,10 @@
         <v>48</v>
       </c>
       <c r="Q33" s="288" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="R33" s="288" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="S33" s="288" t="s">
         <v>45</v>
@@ -44095,7 +44095,7 @@
         <v>47</v>
       </c>
       <c r="X33" s="288" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="Y33" s="288" t="s">
         <v>45</v>
@@ -44116,7 +44116,7 @@
         <v>48</v>
       </c>
       <c r="AE33" s="288" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="AF33" s="288" t="s">
         <v>45</v>
@@ -44132,10 +44132,10 @@
         <v>153</v>
       </c>
       <c r="C34" s="288" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D34" s="288" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E34" s="288" t="s">
         <v>44</v>
@@ -44153,7 +44153,7 @@
         <v>49</v>
       </c>
       <c r="J34" s="288" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="K34" s="288" t="s">
         <v>45</v>
@@ -44162,7 +44162,7 @@
         <v>44</v>
       </c>
       <c r="M34" s="288" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="N34" s="288" t="s">
         <v>53</v>
@@ -44174,7 +44174,7 @@
         <v>47</v>
       </c>
       <c r="Q34" s="288" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="R34" s="288" t="s">
         <v>45</v>
@@ -44232,7 +44232,7 @@
         <v>156</v>
       </c>
       <c r="C35" s="288" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="D35" s="288" t="s">
         <v>43</v>
@@ -44338,7 +44338,7 @@
         <v>46</v>
       </c>
       <c r="E36" s="288" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F36" s="288" t="s">
         <v>43</v>
@@ -44386,7 +44386,7 @@
         <v>44</v>
       </c>
       <c r="U36" s="288" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="V36" s="288" t="s">
         <v>53</v>
@@ -44432,7 +44432,7 @@
         <v>162</v>
       </c>
       <c r="C37" s="288" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D37" s="287" t="s">
         <v>43</v>
@@ -44447,13 +44447,13 @@
         <v>53</v>
       </c>
       <c r="H37" s="288" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="I37" s="288" t="s">
         <v>45</v>
       </c>
       <c r="J37" s="288" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="K37" s="288" t="s">
         <v>44</v>
@@ -44468,10 +44468,10 @@
         <v>53</v>
       </c>
       <c r="O37" s="288" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="P37" s="288" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="Q37" s="288" t="s">
         <v>46</v>
@@ -44492,7 +44492,7 @@
         <v>49</v>
       </c>
       <c r="W37" s="288" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="X37" s="288" t="s">
         <v>45</v>
@@ -44513,7 +44513,7 @@
         <v>46</v>
       </c>
       <c r="AD37" s="288" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="AE37" s="288" t="s">
         <v>43</v>
@@ -44553,7 +44553,7 @@
         <v>53</v>
       </c>
       <c r="J38" s="288" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="K38" s="288" t="s">
         <v>45</v>
@@ -44562,10 +44562,10 @@
         <v>45</v>
       </c>
       <c r="M38" s="288" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="N38" s="288" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="O38" s="288" t="s">
         <v>53</v>
@@ -44574,10 +44574,10 @@
         <v>53</v>
       </c>
       <c r="Q38" s="288" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="R38" s="288" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="S38" s="288" t="s">
         <v>49</v>
@@ -44638,7 +44638,7 @@
         <v>53</v>
       </c>
       <c r="E39" s="288" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F39" s="288" t="s">
         <v>45</v>
@@ -44647,7 +44647,7 @@
         <v>43</v>
       </c>
       <c r="H39" s="288" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="I39" s="288" t="s">
         <v>43</v>
@@ -44659,10 +44659,10 @@
         <v>53</v>
       </c>
       <c r="L39" s="288" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="M39" s="288" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="N39" s="288" t="s">
         <v>45</v>
@@ -44680,7 +44680,7 @@
         <v>53</v>
       </c>
       <c r="S39" s="288" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="T39" s="288" t="s">
         <v>45</v>
@@ -44689,7 +44689,7 @@
         <v>45</v>
       </c>
       <c r="V39" s="288" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="W39" s="288" t="s">
         <v>43</v>
@@ -44765,7 +44765,7 @@
         <v>45</v>
       </c>
       <c r="N40" s="287" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="O40" s="287" t="s">
         <v>43</v>
@@ -44862,7 +44862,7 @@
         <v>45</v>
       </c>
       <c r="M41" s="288" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="N41" s="288" t="s">
         <v>43</v>
@@ -44932,10 +44932,10 @@
         <v>177</v>
       </c>
       <c r="C42" s="288" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D42" s="288" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E42" s="288" t="s">
         <v>45</v>
@@ -44998,7 +44998,7 @@
         <v>46</v>
       </c>
       <c r="Y42" s="287" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="Z42" s="288" t="s">
         <v>48</v>
@@ -45044,7 +45044,7 @@
         <v>49</v>
       </c>
       <c r="G43" s="287" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="H43" s="287" t="s">
         <v>43</v>
@@ -45059,7 +45059,7 @@
         <v>47</v>
       </c>
       <c r="L43" s="287" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="M43" s="288" t="s">
         <v>45</v>
@@ -45080,13 +45080,13 @@
         <v>47</v>
       </c>
       <c r="S43" s="287" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="T43" s="287" t="s">
         <v>45</v>
       </c>
       <c r="U43" s="288" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="V43" s="288" t="s">
         <v>43</v>
@@ -45101,7 +45101,7 @@
         <v>47</v>
       </c>
       <c r="Z43" s="288" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="AA43" s="288" t="s">
         <v>45</v>
@@ -45110,7 +45110,7 @@
         <v>44</v>
       </c>
       <c r="AC43" s="288" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="AD43" s="288" t="s">
         <v>53</v>
@@ -45162,7 +45162,7 @@
         <v>45</v>
       </c>
       <c r="M44" s="287" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="N44" s="287" t="s">
         <v>43</v>
@@ -47225,7 +47225,7 @@
         <v>5.0</v>
       </c>
       <c r="M3" s="287">
-        <v>5.0</v>
+        <v>6.0</v>
       </c>
       <c r="N3" s="287">
         <v>5.0</v>
@@ -47234,7 +47234,7 @@
         <v>5.0</v>
       </c>
       <c r="P3" s="287">
-        <v>5.0</v>
+        <v>6.0</v>
       </c>
       <c r="Q3" s="287">
         <v>6.0</v>
@@ -47397,7 +47397,7 @@
         <v>7.0</v>
       </c>
       <c r="G5" s="287">
-        <v>7.0</v>
+        <v>6.0</v>
       </c>
       <c r="H5" s="287">
         <v>6.0</v>
@@ -47519,7 +47519,7 @@
         <v>3.0</v>
       </c>
       <c r="P6" s="287">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="Q6" s="287">
         <v>3.0</v>
@@ -47587,7 +47587,7 @@
         <v>6.0</v>
       </c>
       <c r="G7" s="287">
-        <v>6.0</v>
+        <v>7.0</v>
       </c>
       <c r="H7" s="287">
         <v>7.0</v>
@@ -47614,7 +47614,7 @@
         <v>6.0</v>
       </c>
       <c r="P7" s="287">
-        <v>7.0</v>
+        <v>6.0</v>
       </c>
       <c r="Q7" s="287">
         <v>6.0</v>
@@ -47739,7 +47739,7 @@
         <v>12.0</v>
       </c>
       <c r="Z8" s="298">
-        <v>11.0</v>
+        <v>12.0</v>
       </c>
       <c r="AA8" s="287">
         <v>13.0</v>
@@ -47890,7 +47890,7 @@
         <v>5.0</v>
       </c>
       <c r="M10" s="287">
-        <v>5.0</v>
+        <v>4.0</v>
       </c>
       <c r="N10" s="287">
         <v>6.0</v>
@@ -47899,7 +47899,7 @@
         <v>4.0</v>
       </c>
       <c r="P10" s="287">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="Q10" s="287">
         <v>1.0</v>
@@ -47929,7 +47929,7 @@
         <v>3.0</v>
       </c>
       <c r="Z10" s="298">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
       <c r="AA10" s="287">
         <v>2.0</v>
@@ -47985,7 +47985,7 @@
         <v>24.0</v>
       </c>
       <c r="M11" s="305">
-        <v>24.0</v>
+        <v>25.0</v>
       </c>
       <c r="N11" s="305">
         <v>24.0</v>
@@ -47994,7 +47994,7 @@
         <v>24.0</v>
       </c>
       <c r="P11" s="302">
-        <v>25.0</v>
+        <v>26.0</v>
       </c>
       <c r="Q11" s="302">
         <v>25.0</v>
@@ -50301,7 +50301,7 @@
         <v>45</v>
       </c>
       <c r="Q3" s="288" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="R3" s="288" t="s">
         <v>53</v>
@@ -50359,7 +50359,7 @@
         <v>62</v>
       </c>
       <c r="C4" s="288" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D4" s="288" t="s">
         <v>53</v>
@@ -50401,7 +50401,7 @@
         <v>45</v>
       </c>
       <c r="Q4" s="288" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="R4" s="288" t="s">
         <v>53</v>
@@ -50410,13 +50410,13 @@
         <v>53</v>
       </c>
       <c r="T4" s="288" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="U4" s="288" t="s">
         <v>46</v>
       </c>
       <c r="V4" s="288" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="W4" s="288" t="s">
         <v>44</v>
@@ -50540,10 +50540,10 @@
         <v>49</v>
       </c>
       <c r="AD5" s="288" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="AE5" s="288" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="AF5" s="288" t="s">
         <v>43</v>
@@ -50692,7 +50692,7 @@
         <v>44</v>
       </c>
       <c r="N7" s="288" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="O7" s="288" t="s">
         <v>48</v>
@@ -50740,7 +50740,7 @@
         <v>48</v>
       </c>
       <c r="AD7" s="288" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="AE7" s="287" t="s">
         <v>45</v>
@@ -50759,7 +50759,7 @@
         <v>74</v>
       </c>
       <c r="C8" s="288" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="D8" s="288" t="s">
         <v>43</v>
@@ -50798,13 +50798,13 @@
         <v>49</v>
       </c>
       <c r="P8" s="288" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="Q8" s="288" t="s">
+        <v>47</v>
+      </c>
+      <c r="R8" s="288" t="s">
         <v>44</v>
-      </c>
-      <c r="R8" s="288" t="s">
-        <v>43</v>
       </c>
       <c r="S8" s="288" t="s">
         <v>53</v>
@@ -50822,7 +50822,7 @@
         <v>45</v>
       </c>
       <c r="X8" s="288" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="Y8" s="288" t="s">
         <v>44</v>
@@ -50840,10 +50840,10 @@
         <v>49</v>
       </c>
       <c r="AD8" s="288" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="AE8" s="288" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="AF8" s="288" t="s">
         <v>49</v>
@@ -50892,7 +50892,7 @@
         <v>47</v>
       </c>
       <c r="N9" s="288" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="O9" s="288" t="s">
         <v>45</v>
@@ -50943,7 +50943,7 @@
         <v>45</v>
       </c>
       <c r="AE9" s="288" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="AF9" s="288" t="s">
         <v>53</v>
@@ -51159,7 +51159,7 @@
         <v>86</v>
       </c>
       <c r="C12" s="288" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D12" s="288" t="s">
         <v>43</v>
@@ -51180,7 +51180,7 @@
         <v>48</v>
       </c>
       <c r="J12" s="288" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="K12" s="288" t="s">
         <v>43</v>
@@ -51216,7 +51216,7 @@
         <v>47</v>
       </c>
       <c r="V12" s="288" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="W12" s="288" t="s">
         <v>45</v>
@@ -51240,7 +51240,7 @@
         <v>47</v>
       </c>
       <c r="AD12" s="288" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="AE12" s="288" t="s">
         <v>48</v>
@@ -51574,7 +51574,7 @@
         <v>47</v>
       </c>
       <c r="H16" s="288" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I16" s="288" t="s">
         <v>44</v>
@@ -51595,7 +51595,7 @@
         <v>47</v>
       </c>
       <c r="O16" s="288" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="P16" s="288" t="s">
         <v>45</v>
@@ -51665,7 +51665,7 @@
         <v>53</v>
       </c>
       <c r="E17" s="288" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F17" s="288" t="s">
         <v>47</v>
@@ -51692,7 +51692,7 @@
         <v>47</v>
       </c>
       <c r="N17" s="288" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="O17" s="288" t="s">
         <v>43</v>
@@ -51710,10 +51710,10 @@
         <v>47</v>
       </c>
       <c r="T17" s="288" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="U17" s="288" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="V17" s="288" t="s">
         <v>43</v>
@@ -51828,7 +51828,7 @@
         <v>47</v>
       </c>
       <c r="Z18" s="288" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="AA18" s="288" t="s">
         <v>46</v>
@@ -52198,7 +52198,7 @@
         <v>53</v>
       </c>
       <c r="P22" s="288" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="Q22" s="288" t="s">
         <v>45</v>
@@ -52401,7 +52401,7 @@
         <v>47</v>
       </c>
       <c r="Q24" s="288" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="R24" s="288" t="s">
         <v>43</v>
@@ -52465,7 +52465,7 @@
         <v>45</v>
       </c>
       <c r="E25" s="287" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F25" s="287" t="s">
         <v>43</v>
@@ -52486,7 +52486,7 @@
         <v>45</v>
       </c>
       <c r="L25" s="287" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="M25" s="287" t="s">
         <v>43</v>
@@ -52498,13 +52498,13 @@
         <v>53</v>
       </c>
       <c r="P25" s="288" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="Q25" s="287" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="R25" s="287" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="S25" s="288" t="s">
         <v>44</v>
@@ -52589,7 +52589,7 @@
         <v>47</v>
       </c>
       <c r="M26" s="288" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="N26" s="288" t="s">
         <v>49</v>
@@ -52680,7 +52680,7 @@
         <v>45</v>
       </c>
       <c r="J27" s="288" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="K27" s="288" t="s">
         <v>44</v>
@@ -52707,7 +52707,7 @@
         <v>45</v>
       </c>
       <c r="S27" s="287" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="T27" s="288" t="s">
         <v>53</v>
@@ -52716,7 +52716,7 @@
         <v>53</v>
       </c>
       <c r="V27" s="288" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="W27" s="288" t="s">
         <v>45</v>
@@ -52771,7 +52771,7 @@
         <v>47</v>
       </c>
       <c r="G28" s="288" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="H28" s="288" t="s">
         <v>48</v>
@@ -52816,10 +52816,10 @@
         <v>46</v>
       </c>
       <c r="V28" s="288" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="W28" s="288" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="X28" s="288" t="s">
         <v>43</v>
@@ -52840,10 +52840,10 @@
         <v>44</v>
       </c>
       <c r="AD28" s="288" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="AE28" s="288" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="AF28" s="288" t="s">
         <v>53</v>
@@ -52874,7 +52874,7 @@
         <v>53</v>
       </c>
       <c r="H29" s="288" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="I29" s="288" t="s">
         <v>45</v>
@@ -52922,7 +52922,7 @@
         <v>45</v>
       </c>
       <c r="X29" s="288" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="Y29" s="288" t="s">
         <v>49</v>
@@ -52931,7 +52931,7 @@
         <v>49</v>
       </c>
       <c r="AA29" s="288" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="AB29" s="288" t="s">
         <v>53</v>
@@ -52986,7 +52986,7 @@
         <v>45</v>
       </c>
       <c r="L30" s="288" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="M30" s="288" t="s">
         <v>53</v>
@@ -53007,7 +53007,7 @@
         <v>44</v>
       </c>
       <c r="S30" s="288" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="T30" s="288" t="s">
         <v>53</v>
@@ -53016,16 +53016,16 @@
         <v>53</v>
       </c>
       <c r="V30" s="288" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="W30" s="288" t="s">
         <v>46</v>
       </c>
       <c r="X30" s="288" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="Y30" s="288" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="Z30" s="288" t="s">
         <v>43</v>
@@ -53043,7 +53043,7 @@
         <v>46</v>
       </c>
       <c r="AE30" s="288" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="AF30" s="288" t="s">
         <v>44</v>
@@ -53192,7 +53192,7 @@
         <v>45</v>
       </c>
       <c r="N32" s="288" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="O32" s="288" t="s">
         <v>44</v>
@@ -53213,7 +53213,7 @@
         <v>45</v>
       </c>
       <c r="U32" s="288" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="V32" s="288" t="s">
         <v>44</v>
@@ -53228,7 +53228,7 @@
         <v>47</v>
       </c>
       <c r="Z32" s="288" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="AA32" s="288" t="s">
         <v>44</v>
@@ -53237,7 +53237,7 @@
         <v>43</v>
       </c>
       <c r="AC32" s="288" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="AD32" s="288" t="s">
         <v>53</v>
@@ -53301,10 +53301,10 @@
         <v>48</v>
       </c>
       <c r="Q33" s="288" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="R33" s="288" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="S33" s="288" t="s">
         <v>45</v>
@@ -53322,7 +53322,7 @@
         <v>47</v>
       </c>
       <c r="X33" s="288" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="Y33" s="288" t="s">
         <v>45</v>
@@ -53343,7 +53343,7 @@
         <v>48</v>
       </c>
       <c r="AE33" s="288" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="AF33" s="288" t="s">
         <v>45</v>
@@ -53359,10 +53359,10 @@
         <v>153</v>
       </c>
       <c r="C34" s="288" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D34" s="288" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E34" s="288" t="s">
         <v>44</v>
@@ -53380,7 +53380,7 @@
         <v>49</v>
       </c>
       <c r="J34" s="288" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="K34" s="288" t="s">
         <v>45</v>
@@ -53389,7 +53389,7 @@
         <v>44</v>
       </c>
       <c r="M34" s="288" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="N34" s="288" t="s">
         <v>53</v>
@@ -53401,7 +53401,7 @@
         <v>47</v>
       </c>
       <c r="Q34" s="288" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="R34" s="288" t="s">
         <v>45</v>
@@ -53459,7 +53459,7 @@
         <v>156</v>
       </c>
       <c r="C35" s="288" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="D35" s="288" t="s">
         <v>43</v>
@@ -53565,7 +53565,7 @@
         <v>46</v>
       </c>
       <c r="E36" s="288" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F36" s="288" t="s">
         <v>43</v>
@@ -53613,7 +53613,7 @@
         <v>44</v>
       </c>
       <c r="U36" s="288" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="V36" s="288" t="s">
         <v>53</v>
@@ -53659,7 +53659,7 @@
         <v>162</v>
       </c>
       <c r="C37" s="288" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D37" s="287" t="s">
         <v>43</v>
@@ -53674,13 +53674,13 @@
         <v>53</v>
       </c>
       <c r="H37" s="288" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="I37" s="288" t="s">
         <v>45</v>
       </c>
       <c r="J37" s="288" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="K37" s="288" t="s">
         <v>44</v>
@@ -53695,10 +53695,10 @@
         <v>53</v>
       </c>
       <c r="O37" s="288" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="P37" s="288" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="Q37" s="288" t="s">
         <v>46</v>
@@ -53719,7 +53719,7 @@
         <v>49</v>
       </c>
       <c r="W37" s="288" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="X37" s="288" t="s">
         <v>45</v>
@@ -53740,7 +53740,7 @@
         <v>46</v>
       </c>
       <c r="AD37" s="288" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="AE37" s="288" t="s">
         <v>43</v>
@@ -53780,7 +53780,7 @@
         <v>53</v>
       </c>
       <c r="J38" s="288" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="K38" s="288" t="s">
         <v>45</v>
@@ -53789,10 +53789,10 @@
         <v>45</v>
       </c>
       <c r="M38" s="288" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="N38" s="288" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="O38" s="288" t="s">
         <v>53</v>
@@ -53801,10 +53801,10 @@
         <v>53</v>
       </c>
       <c r="Q38" s="288" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="R38" s="288" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="S38" s="288" t="s">
         <v>49</v>
@@ -53865,7 +53865,7 @@
         <v>53</v>
       </c>
       <c r="E39" s="288" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F39" s="288" t="s">
         <v>45</v>
@@ -53874,7 +53874,7 @@
         <v>43</v>
       </c>
       <c r="H39" s="288" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="I39" s="288" t="s">
         <v>43</v>
@@ -53886,10 +53886,10 @@
         <v>53</v>
       </c>
       <c r="L39" s="288" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="M39" s="288" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="N39" s="288" t="s">
         <v>45</v>
@@ -53907,7 +53907,7 @@
         <v>53</v>
       </c>
       <c r="S39" s="288" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="T39" s="288" t="s">
         <v>45</v>
@@ -53916,7 +53916,7 @@
         <v>45</v>
       </c>
       <c r="V39" s="288" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="W39" s="288" t="s">
         <v>43</v>
@@ -53992,7 +53992,7 @@
         <v>45</v>
       </c>
       <c r="N40" s="287" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="O40" s="287" t="s">
         <v>43</v>
@@ -54089,7 +54089,7 @@
         <v>45</v>
       </c>
       <c r="M41" s="288" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="N41" s="288" t="s">
         <v>43</v>
@@ -54159,10 +54159,10 @@
         <v>177</v>
       </c>
       <c r="C42" s="288" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D42" s="288" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E42" s="288" t="s">
         <v>45</v>
@@ -54225,7 +54225,7 @@
         <v>46</v>
       </c>
       <c r="Y42" s="287" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="Z42" s="288" t="s">
         <v>48</v>
@@ -54271,7 +54271,7 @@
         <v>49</v>
       </c>
       <c r="G43" s="287" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="H43" s="287" t="s">
         <v>43</v>
@@ -54286,7 +54286,7 @@
         <v>47</v>
       </c>
       <c r="L43" s="287" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="M43" s="288" t="s">
         <v>45</v>
@@ -54307,13 +54307,13 @@
         <v>47</v>
       </c>
       <c r="S43" s="287" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="T43" s="287" t="s">
         <v>45</v>
       </c>
       <c r="U43" s="288" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="V43" s="288" t="s">
         <v>43</v>
@@ -54328,7 +54328,7 @@
         <v>47</v>
       </c>
       <c r="Z43" s="288" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="AA43" s="288" t="s">
         <v>45</v>
@@ -54337,7 +54337,7 @@
         <v>44</v>
       </c>
       <c r="AC43" s="288" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="AD43" s="288" t="s">
         <v>53</v>
@@ -54389,7 +54389,7 @@
         <v>45</v>
       </c>
       <c r="M44" s="287" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="N44" s="287" t="s">
         <v>43</v>

--- a/uploads/ORIGINAL7.xlsx
+++ b/uploads/ORIGINAL7.xlsx
@@ -25270,8 +25270,8 @@
       <c r="L20" s="226" t="s">
         <v>47</v>
       </c>
-      <c r="M20" s="205" t="s">
-        <v>49</v>
+      <c r="M20" s="57" t="s">
+        <v>48</v>
       </c>
       <c r="N20" s="206" t="s">
         <v>46</v>
@@ -25291,8 +25291,8 @@
       <c r="S20" s="214" t="s">
         <v>46</v>
       </c>
-      <c r="T20" s="205" t="s">
-        <v>49</v>
+      <c r="T20" s="57" t="s">
+        <v>48</v>
       </c>
       <c r="U20" s="206" t="s">
         <v>45</v>
@@ -25357,11 +25357,11 @@
       </c>
       <c r="AN20" s="52">
         <f t="shared" ref="AN20:AO20" si="22">COUNTIF($C20:$AF20,"PH")</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AO20" s="52">
         <f t="shared" si="22"/>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AP20" s="67"/>
       <c r="AQ20" s="67"/>
@@ -30062,7 +30062,7 @@
       </c>
       <c r="M56" s="275">
         <f t="shared" si="59"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N56" s="140">
         <f t="shared" si="59"/>
@@ -30090,7 +30090,7 @@
       </c>
       <c r="T56" s="275">
         <f t="shared" si="59"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U56" s="140">
         <f t="shared" si="59"/>
@@ -30202,7 +30202,7 @@
       </c>
       <c r="M57" s="275">
         <f t="shared" si="60"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N57" s="140">
         <f t="shared" si="60"/>
@@ -30230,7 +30230,7 @@
       </c>
       <c r="T57" s="275">
         <f t="shared" si="60"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="U57" s="140">
         <f t="shared" si="60"/>
@@ -42562,7 +42562,7 @@
         <v>47</v>
       </c>
       <c r="M18" s="288" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="N18" s="288" t="s">
         <v>46</v>
@@ -42583,7 +42583,7 @@
         <v>46</v>
       </c>
       <c r="T18" s="288" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="U18" s="288" t="s">
         <v>45</v>
@@ -47792,7 +47792,7 @@
         <v>4.0</v>
       </c>
       <c r="L9" s="298">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="M9" s="287">
         <v>0.0</v>
@@ -47813,7 +47813,7 @@
         <v>2.0</v>
       </c>
       <c r="S9" s="298">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="T9" s="287">
         <v>0.0</v>
@@ -47887,7 +47887,7 @@
         <v>2.0</v>
       </c>
       <c r="L10" s="298">
-        <v>5.0</v>
+        <v>4.0</v>
       </c>
       <c r="M10" s="287">
         <v>4.0</v>
@@ -47908,7 +47908,7 @@
         <v>3.0</v>
       </c>
       <c r="S10" s="298">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
       <c r="T10" s="287">
         <v>5.0</v>
@@ -51789,7 +51789,7 @@
         <v>47</v>
       </c>
       <c r="M18" s="288" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="N18" s="288" t="s">
         <v>46</v>
@@ -51810,7 +51810,7 @@
         <v>46</v>
       </c>
       <c r="T18" s="288" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="U18" s="288" t="s">
         <v>45</v>

--- a/uploads/ORIGINAL7.xlsx
+++ b/uploads/ORIGINAL7.xlsx
@@ -23306,7 +23306,7 @@
         <v>53</v>
       </c>
       <c r="AA5" s="195" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="AB5" s="199" t="s">
         <v>45</v>
@@ -23338,7 +23338,7 @@
       </c>
       <c r="AK5" s="49">
         <f t="shared" ref="AK5:AK46" si="5">COUNTIF($C5:$AF5,"B5")</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AL5" s="50">
         <f t="shared" ref="AL5:AL46" si="6">COUNTIF($C5:$AF5,"A8")</f>
@@ -23346,7 +23346,7 @@
       </c>
       <c r="AM5" s="51">
         <f t="shared" ref="AM5:AM46" si="7">COUNTIF($C5:$AF5,"A2")</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AN5" s="52">
         <f t="shared" ref="AN5:AO5" si="1">COUNTIF($C5:$AF5,"PH")</f>
@@ -24122,7 +24122,7 @@
         <v>53</v>
       </c>
       <c r="AA11" s="203" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="AB11" s="207" t="s">
         <v>43</v>
@@ -24154,7 +24154,7 @@
       </c>
       <c r="AK11" s="49">
         <f t="shared" si="5"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AL11" s="50">
         <f t="shared" si="6"/>
@@ -24162,7 +24162,7 @@
       </c>
       <c r="AM11" s="51">
         <f t="shared" si="7"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AN11" s="52">
         <f t="shared" ref="AN11:AO11" si="13">COUNTIF($C11:$AF11,"PH")</f>
@@ -42621,7 +42621,7 @@
         <v>53</v>
       </c>
       <c r="AA3" s="293" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="AB3" s="293" t="s">
         <v>45</v>
@@ -43221,7 +43221,7 @@
         <v>53</v>
       </c>
       <c r="AA9" s="293" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="AB9" s="293" t="s">
         <v>43</v>
@@ -51848,7 +51848,7 @@
         <v>53</v>
       </c>
       <c r="AA3" s="293" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="AB3" s="293" t="s">
         <v>45</v>
@@ -52448,7 +52448,7 @@
         <v>53</v>
       </c>
       <c r="AA9" s="293" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="AB9" s="293" t="s">
         <v>43</v>

--- a/uploads/ORIGINAL7.xlsx
+++ b/uploads/ORIGINAL7.xlsx
@@ -27264,8 +27264,8 @@
       <c r="AE34" s="204" t="s">
         <v>53</v>
       </c>
-      <c r="AF34" s="229" t="s">
-        <v>47</v>
+      <c r="AF34" s="217" t="s">
+        <v>45</v>
       </c>
       <c r="AG34" s="25" t="s">
         <v>148</v>
@@ -27284,7 +27284,7 @@
       </c>
       <c r="AK34" s="49">
         <f t="shared" si="5"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AL34" s="50">
         <f t="shared" si="6"/>
@@ -27292,7 +27292,7 @@
       </c>
       <c r="AM34" s="51">
         <f t="shared" si="7"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AN34" s="52">
         <f t="shared" ref="AN34:AO34" si="36">COUNTIF($C34:$AF34,"PH")</f>
@@ -27811,7 +27811,7 @@
         <v>46</v>
       </c>
       <c r="AF38" s="217" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="AG38" s="25"/>
       <c r="AH38" s="47">
@@ -27828,7 +27828,7 @@
       </c>
       <c r="AK38" s="49">
         <f t="shared" si="5"/>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AL38" s="50">
         <f t="shared" si="6"/>
@@ -27836,7 +27836,7 @@
       </c>
       <c r="AM38" s="51">
         <f t="shared" si="7"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AN38" s="52">
         <f t="shared" ref="AN38:AO38" si="40">COUNTIF($C38:$AF38,"PH")</f>
@@ -45536,7 +45536,7 @@
         <v>53</v>
       </c>
       <c r="AF32" s="293" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="AG32" s="292"/>
       <c r="AH32" s="292"/>
@@ -45936,7 +45936,7 @@
         <v>46</v>
       </c>
       <c r="AF36" s="293" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="AG36" s="292"/>
       <c r="AH36" s="292"/>
@@ -54763,7 +54763,7 @@
         <v>53</v>
       </c>
       <c r="AF32" s="293" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="AG32" s="292"/>
       <c r="AH32" s="292"/>
@@ -55163,7 +55163,7 @@
         <v>46</v>
       </c>
       <c r="AF36" s="293" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="AG36" s="292"/>
       <c r="AH36" s="292"/>

--- a/uploads/ORIGINAL7.xlsx
+++ b/uploads/ORIGINAL7.xlsx
@@ -11,12 +11,13 @@
     <sheet state="visible" name="ManPower7" sheetId="6" r:id="rId9"/>
     <sheet state="visible" name="Sumary" sheetId="7" r:id="rId10"/>
     <sheet state="visible" name="Month7" sheetId="8" r:id="rId11"/>
+    <sheet state="visible" name="Misa" sheetId="9" r:id="rId12"/>
   </sheets>
   <definedNames/>
   <calcPr/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId12" roundtripDataChecksum="jwnbD1D1BQbYqkMU5VJHG9U16VcRqwuE91dMP79Ic80="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId13" roundtripDataChecksum="0VxZszcf/fp25O03JlP+IL9HkfyaL5msI0EdXtLjS3s="/>
     </ext>
   </extLst>
 </workbook>
@@ -3213,6 +3214,10 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
 </file>
 
+<file path=xl/drawings/drawing9.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
   <a:themeElements>
@@ -26636,8 +26641,8 @@
       <c r="L28" s="255" t="s">
         <v>47</v>
       </c>
-      <c r="M28" s="226" t="s">
-        <v>49</v>
+      <c r="M28" s="231" t="s">
+        <v>47</v>
       </c>
       <c r="N28" s="237" t="s">
         <v>49</v>
@@ -26719,15 +26724,15 @@
       </c>
       <c r="AM28" s="51">
         <f t="shared" si="7"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AN28" s="52">
         <f t="shared" ref="AN28:AO28" si="30">COUNTIF($C28:$AF28,"PH")</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AO28" s="52">
         <f t="shared" si="30"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AP28" s="67"/>
       <c r="AQ28" s="67"/>
@@ -27220,7 +27225,7 @@
         <v>45</v>
       </c>
       <c r="Z32" s="239" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="AA32" s="235" t="s">
         <v>53</v>
@@ -27243,11 +27248,11 @@
       <c r="AG32" s="25"/>
       <c r="AH32" s="47">
         <f t="shared" si="2"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AI32" s="48">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ32" s="48">
         <f t="shared" si="4"/>
@@ -27255,7 +27260,7 @@
       </c>
       <c r="AK32" s="49">
         <f t="shared" si="5"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AL32" s="50">
         <f t="shared" si="6"/>
@@ -28718,7 +28723,7 @@
         <v>45</v>
       </c>
       <c r="Z43" s="239" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="AA43" s="231" t="s">
         <v>43</v>
@@ -28741,11 +28746,11 @@
       <c r="AG43" s="25"/>
       <c r="AH43" s="47">
         <f t="shared" si="2"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AI43" s="48">
         <f t="shared" si="3"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AJ43" s="48">
         <f t="shared" si="4"/>
@@ -28753,7 +28758,7 @@
       </c>
       <c r="AK43" s="49">
         <f t="shared" si="5"/>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AL43" s="50">
         <f t="shared" si="6"/>
@@ -29500,7 +29505,7 @@
       </c>
       <c r="M50" s="322">
         <f t="shared" si="48"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N50" s="323">
         <f t="shared" si="48"/>
@@ -30480,7 +30485,7 @@
       </c>
       <c r="M57" s="326">
         <f t="shared" si="60"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N57" s="140">
         <f t="shared" si="60"/>
@@ -30620,7 +30625,7 @@
       </c>
       <c r="M58" s="334">
         <f t="shared" si="61"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="N58" s="336">
         <f t="shared" si="61"/>
@@ -45126,7 +45131,7 @@
         <v>47</v>
       </c>
       <c r="M26" s="340" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="N26" s="340" t="s">
         <v>49</v>
@@ -45565,7 +45570,7 @@
         <v>45</v>
       </c>
       <c r="Z30" s="340" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="AA30" s="340" t="s">
         <v>53</v>
@@ -46665,7 +46670,7 @@
         <v>45</v>
       </c>
       <c r="Z41" s="340" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="AA41" s="340" t="s">
         <v>43</v>
@@ -48987,7 +48992,7 @@
         <v>5.0</v>
       </c>
       <c r="L3" s="350">
-        <v>5.0</v>
+        <v>6.0</v>
       </c>
       <c r="M3" s="339">
         <v>6.0</v>
@@ -49652,7 +49657,7 @@
         <v>2.0</v>
       </c>
       <c r="L10" s="350">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
       <c r="M10" s="339">
         <v>4.0</v>
@@ -49747,7 +49752,7 @@
         <v>24.0</v>
       </c>
       <c r="L11" s="356">
-        <v>24.0</v>
+        <v>25.0</v>
       </c>
       <c r="M11" s="357">
         <v>25.0</v>
@@ -54357,7 +54362,7 @@
         <v>47</v>
       </c>
       <c r="M26" s="340" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="N26" s="340" t="s">
         <v>49</v>
@@ -54796,7 +54801,7 @@
         <v>45</v>
       </c>
       <c r="Z30" s="340" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="AA30" s="340" t="s">
         <v>53</v>
@@ -55896,7 +55901,7 @@
         <v>45</v>
       </c>
       <c r="Z41" s="340" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="AA41" s="340" t="s">
         <v>43</v>
@@ -57978,4 +57983,15 @@
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
+  <sheetData/>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>
--- a/uploads/ORIGINAL7.xlsx
+++ b/uploads/ORIGINAL7.xlsx
@@ -26409,7 +26409,7 @@
         <v>48</v>
       </c>
       <c r="Z26" s="239" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="AA26" s="231" t="s">
         <v>44</v>
@@ -26432,7 +26432,7 @@
       <c r="AG26" s="25"/>
       <c r="AH26" s="47">
         <f t="shared" si="2"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AI26" s="48">
         <f t="shared" si="3"/>
@@ -26440,11 +26440,11 @@
       </c>
       <c r="AJ26" s="48">
         <f t="shared" si="4"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AK26" s="49">
         <f t="shared" si="5"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AL26" s="50">
         <f t="shared" si="6"/>
@@ -27635,7 +27635,7 @@
         <v>45</v>
       </c>
       <c r="Z35" s="239" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AA35" s="231" t="s">
         <v>43</v>
@@ -27658,7 +27658,7 @@
       <c r="AG35" s="25"/>
       <c r="AH35" s="47">
         <f t="shared" si="2"/>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AI35" s="48">
         <f t="shared" si="3"/>
@@ -27666,11 +27666,11 @@
       </c>
       <c r="AJ35" s="48">
         <f t="shared" si="4"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AK35" s="49">
         <f t="shared" si="5"/>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AL35" s="50">
         <f t="shared" si="6"/>
@@ -44970,7 +44970,7 @@
         <v>48</v>
       </c>
       <c r="Z24" s="340" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="AA24" s="340" t="s">
         <v>44</v>
@@ -45870,7 +45870,7 @@
         <v>45</v>
       </c>
       <c r="Z33" s="340" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AA33" s="340" t="s">
         <v>43</v>
@@ -54201,7 +54201,7 @@
         <v>48</v>
       </c>
       <c r="Z24" s="340" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="AA24" s="340" t="s">
         <v>44</v>
@@ -55101,7 +55101,7 @@
         <v>45</v>
       </c>
       <c r="Z33" s="340" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AA33" s="340" t="s">
         <v>43</v>

--- a/uploads/ORIGINAL7.xlsx
+++ b/uploads/ORIGINAL7.xlsx
@@ -23843,7 +23843,7 @@
         <v>48</v>
       </c>
       <c r="AF7" s="239" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="AG7" s="25"/>
       <c r="AH7" s="47">
@@ -23852,11 +23852,11 @@
       </c>
       <c r="AI7" s="48">
         <f t="shared" si="3"/>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AJ7" s="48">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK7" s="49">
         <f t="shared" si="5"/>
@@ -26563,7 +26563,7 @@
         <v>45</v>
       </c>
       <c r="AF27" s="239" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="AG27" s="25"/>
       <c r="AH27" s="47">
@@ -26572,11 +26572,11 @@
       </c>
       <c r="AI27" s="48">
         <f t="shared" si="3"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AJ27" s="48">
         <f t="shared" si="4"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AK27" s="49">
         <f t="shared" si="5"/>
@@ -43088,7 +43088,7 @@
         <v>48</v>
       </c>
       <c r="AF5" s="340" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="AG5" s="339"/>
       <c r="AH5" s="339"/>
@@ -45088,7 +45088,7 @@
         <v>45</v>
       </c>
       <c r="AF25" s="340" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="AG25" s="339"/>
       <c r="AH25" s="339"/>
@@ -52319,7 +52319,7 @@
         <v>48</v>
       </c>
       <c r="AF5" s="340" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="AG5" s="339"/>
       <c r="AH5" s="339"/>
@@ -54319,7 +54319,7 @@
         <v>45</v>
       </c>
       <c r="AF25" s="340" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="AG25" s="339"/>
       <c r="AH25" s="339"/>

--- a/uploads/ORIGINAL7.xlsx
+++ b/uploads/ORIGINAL7.xlsx
@@ -701,7 +701,7 @@
     <t>29/6  1,2/7</t>
   </si>
   <si>
-    <t>MONTH 7</t>
+    <t>MONTH 7/2026</t>
   </si>
   <si>
     <t>GA MONTHLY ROSTER</t>
@@ -1069,7 +1069,7 @@
     <font>
       <b/>
       <u/>
-      <sz val="12.0"/>
+      <sz val="11.0"/>
       <color theme="1"/>
       <name val="Arial"/>
     </font>
@@ -25270,7 +25270,7 @@
         <v>47</v>
       </c>
       <c r="I18" s="227" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="J18" s="227" t="s">
         <v>44</v>
@@ -25344,7 +25344,7 @@
       <c r="AG18" s="25"/>
       <c r="AH18" s="47">
         <f t="shared" si="2"/>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AI18" s="48">
         <f t="shared" si="3"/>
@@ -25352,11 +25352,11 @@
       </c>
       <c r="AJ18" s="48">
         <f t="shared" si="4"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AK18" s="49">
         <f t="shared" si="5"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AL18" s="50">
         <f t="shared" si="6"/>
@@ -26630,7 +26630,7 @@
         <v>47</v>
       </c>
       <c r="I28" s="227" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="J28" s="224" t="s">
         <v>53</v>
@@ -26704,7 +26704,7 @@
       <c r="AG28" s="25"/>
       <c r="AH28" s="47">
         <f t="shared" si="2"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AI28" s="48">
         <f t="shared" si="3"/>
@@ -26712,11 +26712,11 @@
       </c>
       <c r="AJ28" s="48">
         <f t="shared" si="4"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AK28" s="49">
         <f t="shared" si="5"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AL28" s="50">
         <f t="shared" si="6"/>
@@ -44119,7 +44119,7 @@
         <v>47</v>
       </c>
       <c r="I16" s="340" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="J16" s="340" t="s">
         <v>44</v>
@@ -45119,7 +45119,7 @@
         <v>47</v>
       </c>
       <c r="I26" s="340" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="J26" s="340" t="s">
         <v>53</v>
@@ -53350,7 +53350,7 @@
         <v>47</v>
       </c>
       <c r="I16" s="340" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="J16" s="340" t="s">
         <v>44</v>
@@ -54350,7 +54350,7 @@
         <v>47</v>
       </c>
       <c r="I26" s="340" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="J26" s="340" t="s">
         <v>53</v>

--- a/uploads/ORIGINAL7.xlsx
+++ b/uploads/ORIGINAL7.xlsx
@@ -12,19 +12,20 @@
     <sheet state="visible" name="Sumary" sheetId="7" r:id="rId10"/>
     <sheet state="visible" name="Month7" sheetId="8" r:id="rId11"/>
     <sheet state="visible" name="Misa" sheetId="9" r:id="rId12"/>
+    <sheet state="visible" name="PH ROSTER 7" sheetId="10" r:id="rId13"/>
   </sheets>
   <definedNames/>
   <calcPr/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId13" roundtripDataChecksum="0VxZszcf/fp25O03JlP+IL9HkfyaL5msI0EdXtLjS3s="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId14" roundtripDataChecksum="m42vob0gntZtE2/vhUs5LTYLgkDTbyhzpbhz8UNYXXw="/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5909" uniqueCount="281">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5910" uniqueCount="282">
   <si>
     <t xml:space="preserve"> GA  MONTHLY ROSTER</t>
   </si>
@@ -868,6 +869,9 @@
   <si>
     <t>10,11/7</t>
   </si>
+  <si>
+    <t>PH LIST OF GAME AMBASSADOR</t>
+  </si>
 </sst>
 </file>
 
@@ -876,7 +880,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="m/d"/>
   </numFmts>
-  <fonts count="54">
+  <fonts count="55">
     <font>
       <sz val="11.0"/>
       <color theme="1"/>
@@ -1185,6 +1189,12 @@
       <b/>
       <color theme="8"/>
       <name val="Arial"/>
+    </font>
+    <font>
+      <b/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="17">
@@ -2095,7 +2105,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="360">
+  <cellXfs count="362">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -2781,9 +2791,6 @@
     <xf borderId="11" fillId="3" fontId="29" numFmtId="49" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="19" fillId="2" fontId="29" numFmtId="49" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
-    </xf>
     <xf borderId="61" fillId="2" fontId="42" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
@@ -2805,14 +2812,14 @@
     <xf borderId="61" fillId="2" fontId="43" numFmtId="49" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
-    <xf borderId="19" fillId="0" fontId="29" numFmtId="49" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf borderId="61" fillId="0" fontId="29" numFmtId="49" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf borderId="18" fillId="4" fontId="29" numFmtId="49" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf borderId="19" fillId="2" fontId="29" numFmtId="49" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
     <xf borderId="19" fillId="3" fontId="29" numFmtId="49" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2870,6 +2877,9 @@
     </xf>
     <xf borderId="18" fillId="2" fontId="42" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
+    </xf>
+    <xf borderId="19" fillId="0" fontId="29" numFmtId="49" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf borderId="18" fillId="2" fontId="29" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
@@ -3136,11 +3146,17 @@
     <xf borderId="0" fillId="16" fontId="53" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf borderId="0" fillId="0" fontId="54" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" textRotation="0" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="54" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment shrinkToFit="0" textRotation="0" wrapText="0"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle xfId="0" name="Normal" builtinId="0"/>
   </cellStyles>
-  <dxfs count="4">
+  <dxfs count="5">
     <dxf>
       <font/>
       <fill>
@@ -3178,11 +3194,25 @@
       </fill>
       <border/>
     </dxf>
+    <dxf>
+      <font/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFB7E1CD"/>
+          <bgColor rgb="FFB7E1CD"/>
+        </patternFill>
+      </fill>
+      <border/>
+    </dxf>
   </dxfs>
 </styleSheet>
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/drawings/drawing10.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
 </file>
 
@@ -21801,6 +21831,30 @@
   <colBreaks count="1" manualBreakCount="1">
     <brk id="32" man="1"/>
   </colBreaks>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="B1" s="360" t="s">
+        <v>281</v>
+      </c>
+      <c r="C1" s="361"/>
+      <c r="D1" s="361"/>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="B1:D1">
+    <cfRule type="notContainsBlanks" dxfId="4" priority="1">
+      <formula>LEN(TRIM(B1))&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
@@ -23842,13 +23896,13 @@
       <c r="AE7" s="238" t="s">
         <v>48</v>
       </c>
-      <c r="AF7" s="239" t="s">
-        <v>44</v>
+      <c r="AF7" s="238" t="s">
+        <v>48</v>
       </c>
       <c r="AG7" s="25"/>
       <c r="AH7" s="47">
         <f t="shared" si="2"/>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AI7" s="48">
         <f t="shared" si="3"/>
@@ -23856,7 +23910,7 @@
       </c>
       <c r="AJ7" s="48">
         <f t="shared" si="4"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK7" s="49">
         <f t="shared" si="5"/>
@@ -23891,10 +23945,10 @@
       <c r="B8" s="222" t="s">
         <v>68</v>
       </c>
-      <c r="C8" s="240" t="s">
+      <c r="C8" s="239" t="s">
         <v>46</v>
       </c>
-      <c r="D8" s="241" t="s">
+      <c r="D8" s="240" t="s">
         <v>46</v>
       </c>
       <c r="E8" s="225" t="s">
@@ -23903,19 +23957,19 @@
       <c r="F8" s="235" t="s">
         <v>53</v>
       </c>
-      <c r="G8" s="242" t="s">
-        <v>47</v>
-      </c>
-      <c r="H8" s="243" t="s">
-        <v>47</v>
-      </c>
-      <c r="I8" s="243" t="s">
-        <v>47</v>
-      </c>
-      <c r="J8" s="242" t="s">
-        <v>47</v>
-      </c>
-      <c r="K8" s="244" t="s">
+      <c r="G8" s="241" t="s">
+        <v>47</v>
+      </c>
+      <c r="H8" s="242" t="s">
+        <v>47</v>
+      </c>
+      <c r="I8" s="242" t="s">
+        <v>47</v>
+      </c>
+      <c r="J8" s="241" t="s">
+        <v>47</v>
+      </c>
+      <c r="K8" s="243" t="s">
         <v>46</v>
       </c>
       <c r="L8" s="229" t="s">
@@ -23924,10 +23978,10 @@
       <c r="M8" s="235" t="s">
         <v>53</v>
       </c>
-      <c r="N8" s="242" t="s">
-        <v>47</v>
-      </c>
-      <c r="O8" s="244" t="s">
+      <c r="N8" s="241" t="s">
+        <v>47</v>
+      </c>
+      <c r="O8" s="243" t="s">
         <v>46</v>
       </c>
       <c r="P8" s="237" t="s">
@@ -23945,19 +23999,19 @@
       <c r="T8" s="235" t="s">
         <v>53</v>
       </c>
-      <c r="U8" s="242" t="s">
-        <v>47</v>
-      </c>
-      <c r="V8" s="242" t="s">
-        <v>47</v>
-      </c>
-      <c r="W8" s="244" t="s">
+      <c r="U8" s="241" t="s">
+        <v>47</v>
+      </c>
+      <c r="V8" s="241" t="s">
+        <v>47</v>
+      </c>
+      <c r="W8" s="243" t="s">
         <v>46</v>
       </c>
-      <c r="X8" s="244" t="s">
+      <c r="X8" s="243" t="s">
         <v>46</v>
       </c>
-      <c r="Y8" s="244" t="s">
+      <c r="Y8" s="243" t="s">
         <v>46</v>
       </c>
       <c r="Z8" s="229" t="s">
@@ -23966,19 +24020,19 @@
       <c r="AA8" s="235" t="s">
         <v>53</v>
       </c>
-      <c r="AB8" s="242" t="s">
-        <v>47</v>
-      </c>
-      <c r="AC8" s="244" t="s">
+      <c r="AB8" s="241" t="s">
+        <v>47</v>
+      </c>
+      <c r="AC8" s="243" t="s">
         <v>46</v>
       </c>
-      <c r="AD8" s="244" t="s">
+      <c r="AD8" s="243" t="s">
         <v>46</v>
       </c>
-      <c r="AE8" s="244" t="s">
+      <c r="AE8" s="243" t="s">
         <v>46</v>
       </c>
-      <c r="AF8" s="245" t="s">
+      <c r="AF8" s="244" t="s">
         <v>46</v>
       </c>
       <c r="AG8" s="25"/>
@@ -24163,7 +24217,7 @@
       <c r="B10" s="222" t="s">
         <v>74</v>
       </c>
-      <c r="C10" s="246" t="s">
+      <c r="C10" s="245" t="s">
         <v>47</v>
       </c>
       <c r="D10" s="227" t="s">
@@ -24250,13 +24304,13 @@
       <c r="AE10" s="227" t="s">
         <v>44</v>
       </c>
-      <c r="AF10" s="247" t="s">
-        <v>49</v>
+      <c r="AF10" s="227" t="s">
+        <v>44</v>
       </c>
       <c r="AG10" s="25"/>
       <c r="AH10" s="47">
         <f t="shared" si="2"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AI10" s="48">
         <f t="shared" si="3"/>
@@ -24264,7 +24318,7 @@
       </c>
       <c r="AJ10" s="48">
         <f t="shared" si="4"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AK10" s="49">
         <f t="shared" si="5"/>
@@ -24280,11 +24334,11 @@
       </c>
       <c r="AN10" s="52">
         <f t="shared" ref="AN10:AO10" si="12">COUNTIF($C10:$AF10,"PH")</f>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AO10" s="52">
         <f t="shared" si="12"/>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AP10" s="67"/>
       <c r="AQ10" s="67"/>
@@ -24299,7 +24353,7 @@
       <c r="B11" s="222" t="s">
         <v>77</v>
       </c>
-      <c r="C11" s="248" t="s">
+      <c r="C11" s="246" t="s">
         <v>49</v>
       </c>
       <c r="D11" s="224" t="s">
@@ -24435,7 +24489,7 @@
       <c r="B12" s="222" t="s">
         <v>80</v>
       </c>
-      <c r="C12" s="248" t="s">
+      <c r="C12" s="246" t="s">
         <v>49</v>
       </c>
       <c r="D12" s="227" t="s">
@@ -24465,7 +24519,7 @@
       <c r="L12" s="229" t="s">
         <v>53</v>
       </c>
-      <c r="M12" s="249" t="s">
+      <c r="M12" s="247" t="s">
         <v>53</v>
       </c>
       <c r="N12" s="227" t="s">
@@ -24522,7 +24576,7 @@
       <c r="AE12" s="227" t="s">
         <v>43</v>
       </c>
-      <c r="AF12" s="239" t="s">
+      <c r="AF12" s="248" t="s">
         <v>43</v>
       </c>
       <c r="AG12" s="25"/>
@@ -24794,7 +24848,7 @@
       <c r="AE14" s="238" t="s">
         <v>48</v>
       </c>
-      <c r="AF14" s="250" t="s">
+      <c r="AF14" s="249" t="s">
         <v>48</v>
       </c>
       <c r="AG14" s="25"/>
@@ -24849,7 +24903,7 @@
       <c r="D15" s="227" t="s">
         <v>44</v>
       </c>
-      <c r="E15" s="251" t="s">
+      <c r="E15" s="250" t="s">
         <v>43</v>
       </c>
       <c r="F15" s="235" t="s">
@@ -24870,7 +24924,7 @@
       <c r="K15" s="238" t="s">
         <v>48</v>
       </c>
-      <c r="L15" s="250" t="s">
+      <c r="L15" s="249" t="s">
         <v>48</v>
       </c>
       <c r="M15" s="235" t="s">
@@ -24891,7 +24945,7 @@
       <c r="R15" s="227" t="s">
         <v>44</v>
       </c>
-      <c r="S15" s="239" t="s">
+      <c r="S15" s="248" t="s">
         <v>43</v>
       </c>
       <c r="T15" s="235" t="s">
@@ -24912,7 +24966,7 @@
       <c r="Y15" s="227" t="s">
         <v>43</v>
       </c>
-      <c r="Z15" s="252" t="s">
+      <c r="Z15" s="251" t="s">
         <v>43</v>
       </c>
       <c r="AA15" s="235" t="s">
@@ -24930,7 +24984,7 @@
       <c r="AE15" s="227" t="s">
         <v>45</v>
       </c>
-      <c r="AF15" s="239" t="s">
+      <c r="AF15" s="248" t="s">
         <v>45</v>
       </c>
       <c r="AG15" s="25"/>
@@ -24979,13 +25033,13 @@
       <c r="B16" s="222" t="s">
         <v>92</v>
       </c>
-      <c r="C16" s="248" t="s">
+      <c r="C16" s="246" t="s">
         <v>49</v>
       </c>
       <c r="D16" s="237" t="s">
         <v>49</v>
       </c>
-      <c r="E16" s="253" t="s">
+      <c r="E16" s="252" t="s">
         <v>49</v>
       </c>
       <c r="F16" s="226" t="s">
@@ -25006,7 +25060,7 @@
       <c r="K16" s="227" t="s">
         <v>46</v>
       </c>
-      <c r="L16" s="239" t="s">
+      <c r="L16" s="248" t="s">
         <v>45</v>
       </c>
       <c r="M16" s="231" t="s">
@@ -25027,7 +25081,7 @@
       <c r="R16" s="227" t="s">
         <v>46</v>
       </c>
-      <c r="S16" s="239" t="s">
+      <c r="S16" s="248" t="s">
         <v>45</v>
       </c>
       <c r="T16" s="231" t="s">
@@ -25048,13 +25102,13 @@
       <c r="Y16" s="236" t="s">
         <v>47</v>
       </c>
-      <c r="Z16" s="239" t="s">
+      <c r="Z16" s="248" t="s">
         <v>44</v>
       </c>
       <c r="AA16" s="226" t="s">
         <v>49</v>
       </c>
-      <c r="AB16" s="254" t="s">
+      <c r="AB16" s="253" t="s">
         <v>43</v>
       </c>
       <c r="AC16" s="224" t="s">
@@ -25066,7 +25120,7 @@
       <c r="AE16" s="236" t="s">
         <v>47</v>
       </c>
-      <c r="AF16" s="255" t="s">
+      <c r="AF16" s="254" t="s">
         <v>47</v>
       </c>
       <c r="AG16" s="25"/>
@@ -25115,13 +25169,13 @@
       <c r="B17" s="222" t="s">
         <v>95</v>
       </c>
-      <c r="C17" s="256" t="s">
+      <c r="C17" s="255" t="s">
         <v>53</v>
       </c>
       <c r="D17" s="224" t="s">
         <v>53</v>
       </c>
-      <c r="E17" s="257" t="s">
+      <c r="E17" s="256" t="s">
         <v>47</v>
       </c>
       <c r="F17" s="231" t="s">
@@ -25142,7 +25196,7 @@
       <c r="K17" s="224" t="s">
         <v>53</v>
       </c>
-      <c r="L17" s="250" t="s">
+      <c r="L17" s="249" t="s">
         <v>48</v>
       </c>
       <c r="M17" s="231" t="s">
@@ -25163,7 +25217,7 @@
       <c r="R17" s="224" t="s">
         <v>53</v>
       </c>
-      <c r="S17" s="250" t="s">
+      <c r="S17" s="249" t="s">
         <v>48</v>
       </c>
       <c r="T17" s="230" t="s">
@@ -25184,13 +25238,13 @@
       <c r="Y17" s="224" t="s">
         <v>53</v>
       </c>
-      <c r="Z17" s="255" t="s">
+      <c r="Z17" s="254" t="s">
         <v>47</v>
       </c>
       <c r="AA17" s="231" t="s">
         <v>47</v>
       </c>
-      <c r="AB17" s="242" t="s">
+      <c r="AB17" s="241" t="s">
         <v>47</v>
       </c>
       <c r="AC17" s="238" t="s">
@@ -25263,7 +25317,7 @@
       <c r="F18" s="235" t="s">
         <v>53</v>
       </c>
-      <c r="G18" s="258" t="s">
+      <c r="G18" s="257" t="s">
         <v>47</v>
       </c>
       <c r="H18" s="227" t="s">
@@ -25338,7 +25392,7 @@
       <c r="AE18" s="227" t="s">
         <v>44</v>
       </c>
-      <c r="AF18" s="239" t="s">
+      <c r="AF18" s="248" t="s">
         <v>43</v>
       </c>
       <c r="AG18" s="25"/>
@@ -25387,13 +25441,13 @@
       <c r="B19" s="222" t="s">
         <v>101</v>
       </c>
-      <c r="C19" s="256" t="s">
+      <c r="C19" s="255" t="s">
         <v>53</v>
       </c>
       <c r="D19" s="224" t="s">
         <v>53</v>
       </c>
-      <c r="E19" s="251" t="s">
+      <c r="E19" s="250" t="s">
         <v>47</v>
       </c>
       <c r="F19" s="231" t="s">
@@ -25402,7 +25456,7 @@
       <c r="G19" s="227" t="s">
         <v>45</v>
       </c>
-      <c r="H19" s="259" t="s">
+      <c r="H19" s="258" t="s">
         <v>45</v>
       </c>
       <c r="I19" s="238" t="s">
@@ -25414,7 +25468,7 @@
       <c r="K19" s="224" t="s">
         <v>53</v>
       </c>
-      <c r="L19" s="250" t="s">
+      <c r="L19" s="249" t="s">
         <v>48</v>
       </c>
       <c r="M19" s="230" t="s">
@@ -25435,7 +25489,7 @@
       <c r="R19" s="224" t="s">
         <v>53</v>
       </c>
-      <c r="S19" s="255" t="s">
+      <c r="S19" s="254" t="s">
         <v>47</v>
       </c>
       <c r="T19" s="231" t="s">
@@ -25456,7 +25510,7 @@
       <c r="Y19" s="224" t="s">
         <v>53</v>
       </c>
-      <c r="Z19" s="250" t="s">
+      <c r="Z19" s="249" t="s">
         <v>48</v>
       </c>
       <c r="AA19" s="230" t="s">
@@ -25523,13 +25577,13 @@
       <c r="B20" s="222" t="s">
         <v>104</v>
       </c>
-      <c r="C20" s="256" t="s">
+      <c r="C20" s="255" t="s">
         <v>53</v>
       </c>
       <c r="D20" s="236" t="s">
         <v>47</v>
       </c>
-      <c r="E20" s="257" t="s">
+      <c r="E20" s="256" t="s">
         <v>47</v>
       </c>
       <c r="F20" s="231" t="s">
@@ -25550,10 +25604,10 @@
       <c r="K20" s="236" t="s">
         <v>47</v>
       </c>
-      <c r="L20" s="255" t="s">
-        <v>47</v>
-      </c>
-      <c r="M20" s="260" t="s">
+      <c r="L20" s="254" t="s">
+        <v>47</v>
+      </c>
+      <c r="M20" s="259" t="s">
         <v>48</v>
       </c>
       <c r="N20" s="227" t="s">
@@ -25571,10 +25625,10 @@
       <c r="R20" s="236" t="s">
         <v>47</v>
       </c>
-      <c r="S20" s="239" t="s">
+      <c r="S20" s="248" t="s">
         <v>46</v>
       </c>
-      <c r="T20" s="260" t="s">
+      <c r="T20" s="259" t="s">
         <v>48</v>
       </c>
       <c r="U20" s="227" t="s">
@@ -25592,7 +25646,7 @@
       <c r="Y20" s="236" t="s">
         <v>47</v>
       </c>
-      <c r="Z20" s="239" t="s">
+      <c r="Z20" s="248" t="s">
         <v>46</v>
       </c>
       <c r="AA20" s="231" t="s">
@@ -25610,7 +25664,7 @@
       <c r="AE20" s="224" t="s">
         <v>53</v>
       </c>
-      <c r="AF20" s="261" t="s">
+      <c r="AF20" s="260" t="s">
         <v>47</v>
       </c>
       <c r="AG20" s="25"/>
@@ -25656,94 +25710,94 @@
       <c r="A21" s="221" t="s">
         <v>249</v>
       </c>
-      <c r="B21" s="262" t="s">
+      <c r="B21" s="261" t="s">
         <v>107</v>
       </c>
-      <c r="C21" s="263" t="s">
+      <c r="C21" s="262" t="s">
         <v>43</v>
       </c>
       <c r="D21" s="224" t="s">
         <v>53</v>
       </c>
-      <c r="E21" s="264" t="s">
-        <v>43</v>
-      </c>
-      <c r="F21" s="265" t="s">
-        <v>43</v>
-      </c>
-      <c r="G21" s="266" t="s">
-        <v>53</v>
-      </c>
-      <c r="H21" s="244" t="s">
-        <v>43</v>
-      </c>
-      <c r="I21" s="244" t="s">
-        <v>43</v>
-      </c>
-      <c r="J21" s="244" t="s">
+      <c r="E21" s="263" t="s">
+        <v>43</v>
+      </c>
+      <c r="F21" s="264" t="s">
+        <v>43</v>
+      </c>
+      <c r="G21" s="265" t="s">
+        <v>53</v>
+      </c>
+      <c r="H21" s="243" t="s">
+        <v>43</v>
+      </c>
+      <c r="I21" s="243" t="s">
+        <v>43</v>
+      </c>
+      <c r="J21" s="243" t="s">
         <v>43</v>
       </c>
       <c r="K21" s="224" t="s">
         <v>53</v>
       </c>
-      <c r="L21" s="267" t="s">
-        <v>43</v>
-      </c>
-      <c r="M21" s="268" t="s">
+      <c r="L21" s="266" t="s">
+        <v>43</v>
+      </c>
+      <c r="M21" s="267" t="s">
         <v>43</v>
       </c>
       <c r="N21" s="224" t="s">
         <v>53</v>
       </c>
-      <c r="O21" s="244" t="s">
-        <v>43</v>
-      </c>
-      <c r="P21" s="244" t="s">
-        <v>43</v>
-      </c>
-      <c r="Q21" s="244" t="s">
+      <c r="O21" s="243" t="s">
+        <v>43</v>
+      </c>
+      <c r="P21" s="243" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q21" s="243" t="s">
         <v>43</v>
       </c>
       <c r="R21" s="224" t="s">
         <v>53</v>
       </c>
-      <c r="S21" s="245" t="s">
-        <v>43</v>
-      </c>
-      <c r="T21" s="265" t="s">
+      <c r="S21" s="244" t="s">
+        <v>43</v>
+      </c>
+      <c r="T21" s="264" t="s">
         <v>43</v>
       </c>
       <c r="U21" s="224" t="s">
         <v>53</v>
       </c>
-      <c r="V21" s="244" t="s">
-        <v>43</v>
-      </c>
-      <c r="W21" s="244" t="s">
-        <v>43</v>
-      </c>
-      <c r="X21" s="244" t="s">
+      <c r="V21" s="243" t="s">
+        <v>43</v>
+      </c>
+      <c r="W21" s="243" t="s">
+        <v>43</v>
+      </c>
+      <c r="X21" s="243" t="s">
         <v>43</v>
       </c>
       <c r="Y21" s="224" t="s">
         <v>53</v>
       </c>
-      <c r="Z21" s="245" t="s">
-        <v>43</v>
-      </c>
-      <c r="AA21" s="265" t="s">
+      <c r="Z21" s="244" t="s">
+        <v>43</v>
+      </c>
+      <c r="AA21" s="264" t="s">
         <v>43</v>
       </c>
       <c r="AB21" s="224" t="s">
         <v>53</v>
       </c>
-      <c r="AC21" s="244" t="s">
-        <v>43</v>
-      </c>
-      <c r="AD21" s="244" t="s">
-        <v>43</v>
-      </c>
-      <c r="AE21" s="244" t="s">
+      <c r="AC21" s="243" t="s">
+        <v>43</v>
+      </c>
+      <c r="AD21" s="243" t="s">
+        <v>43</v>
+      </c>
+      <c r="AE21" s="243" t="s">
         <v>43</v>
       </c>
       <c r="AF21" s="229" t="s">
@@ -25795,13 +25849,13 @@
       <c r="B22" s="222" t="s">
         <v>110</v>
       </c>
-      <c r="C22" s="256" t="s">
+      <c r="C22" s="255" t="s">
         <v>53</v>
       </c>
       <c r="D22" s="237" t="s">
         <v>49</v>
       </c>
-      <c r="E22" s="257" t="s">
+      <c r="E22" s="256" t="s">
         <v>47</v>
       </c>
       <c r="F22" s="231" t="s">
@@ -25822,7 +25876,7 @@
       <c r="K22" s="236" t="s">
         <v>47</v>
       </c>
-      <c r="L22" s="239" t="s">
+      <c r="L22" s="248" t="s">
         <v>46</v>
       </c>
       <c r="M22" s="231" t="s">
@@ -25843,7 +25897,7 @@
       <c r="R22" s="236" t="s">
         <v>47</v>
       </c>
-      <c r="S22" s="239" t="s">
+      <c r="S22" s="248" t="s">
         <v>46</v>
       </c>
       <c r="T22" s="231" t="s">
@@ -25864,7 +25918,7 @@
       <c r="Y22" s="236" t="s">
         <v>47</v>
       </c>
-      <c r="Z22" s="239" t="s">
+      <c r="Z22" s="248" t="s">
         <v>46</v>
       </c>
       <c r="AA22" s="231" t="s">
@@ -25882,7 +25936,7 @@
       <c r="AE22" s="224" t="s">
         <v>53</v>
       </c>
-      <c r="AF22" s="252" t="s">
+      <c r="AF22" s="251" t="s">
         <v>46</v>
       </c>
       <c r="AG22" s="25"/>
@@ -25931,13 +25985,13 @@
       <c r="B23" s="222" t="s">
         <v>113</v>
       </c>
-      <c r="C23" s="256" t="s">
+      <c r="C23" s="255" t="s">
         <v>53</v>
       </c>
       <c r="D23" s="224" t="s">
         <v>53</v>
       </c>
-      <c r="E23" s="253" t="s">
+      <c r="E23" s="252" t="s">
         <v>49</v>
       </c>
       <c r="F23" s="231" t="s">
@@ -25958,7 +26012,7 @@
       <c r="K23" s="224" t="s">
         <v>53</v>
       </c>
-      <c r="L23" s="247" t="s">
+      <c r="L23" s="268" t="s">
         <v>49</v>
       </c>
       <c r="M23" s="269" t="s">
@@ -25979,7 +26033,7 @@
       <c r="R23" s="224" t="s">
         <v>53</v>
       </c>
-      <c r="S23" s="261" t="s">
+      <c r="S23" s="260" t="s">
         <v>47</v>
       </c>
       <c r="T23" s="270" t="s">
@@ -26000,7 +26054,7 @@
       <c r="Y23" s="224" t="s">
         <v>53</v>
       </c>
-      <c r="Z23" s="261" t="s">
+      <c r="Z23" s="260" t="s">
         <v>47</v>
       </c>
       <c r="AA23" s="231" t="s">
@@ -26094,7 +26148,7 @@
       <c r="K24" s="237" t="s">
         <v>49</v>
       </c>
-      <c r="L24" s="247" t="s">
+      <c r="L24" s="268" t="s">
         <v>49</v>
       </c>
       <c r="M24" s="226" t="s">
@@ -26115,7 +26169,7 @@
       <c r="R24" s="227" t="s">
         <v>45</v>
       </c>
-      <c r="S24" s="239" t="s">
+      <c r="S24" s="248" t="s">
         <v>44</v>
       </c>
       <c r="T24" s="231" t="s">
@@ -26136,7 +26190,7 @@
       <c r="Y24" s="227" t="s">
         <v>45</v>
       </c>
-      <c r="Z24" s="239" t="s">
+      <c r="Z24" s="248" t="s">
         <v>43</v>
       </c>
       <c r="AA24" s="231" t="s">
@@ -26154,7 +26208,7 @@
       <c r="AE24" s="236" t="s">
         <v>47</v>
       </c>
-      <c r="AF24" s="239" t="s">
+      <c r="AF24" s="248" t="s">
         <v>46</v>
       </c>
       <c r="AG24" s="25"/>
@@ -26203,13 +26257,13 @@
       <c r="B25" s="222" t="s">
         <v>119</v>
       </c>
-      <c r="C25" s="256" t="s">
+      <c r="C25" s="255" t="s">
         <v>53</v>
       </c>
       <c r="D25" s="224" t="s">
         <v>53</v>
       </c>
-      <c r="E25" s="253" t="s">
+      <c r="E25" s="252" t="s">
         <v>49</v>
       </c>
       <c r="F25" s="226" t="s">
@@ -26230,7 +26284,7 @@
       <c r="K25" s="224" t="s">
         <v>53</v>
       </c>
-      <c r="L25" s="255" t="s">
+      <c r="L25" s="254" t="s">
         <v>47</v>
       </c>
       <c r="M25" s="231" t="s">
@@ -26251,7 +26305,7 @@
       <c r="R25" s="224" t="s">
         <v>53</v>
       </c>
-      <c r="S25" s="250" t="s">
+      <c r="S25" s="249" t="s">
         <v>48</v>
       </c>
       <c r="T25" s="230" t="s">
@@ -26272,7 +26326,7 @@
       <c r="Y25" s="224" t="s">
         <v>53</v>
       </c>
-      <c r="Z25" s="255" t="s">
+      <c r="Z25" s="254" t="s">
         <v>47</v>
       </c>
       <c r="AA25" s="230" t="s">
@@ -26351,7 +26405,7 @@
       <c r="F26" s="231" t="s">
         <v>44</v>
       </c>
-      <c r="G26" s="266" t="s">
+      <c r="G26" s="265" t="s">
         <v>53</v>
       </c>
       <c r="H26" s="224" t="s">
@@ -26366,7 +26420,7 @@
       <c r="K26" s="228" t="s">
         <v>47</v>
       </c>
-      <c r="L26" s="239" t="s">
+      <c r="L26" s="248" t="s">
         <v>44</v>
       </c>
       <c r="M26" s="231" t="s">
@@ -26387,10 +26441,10 @@
       <c r="R26" s="227" t="s">
         <v>45</v>
       </c>
-      <c r="S26" s="239" t="s">
-        <v>45</v>
-      </c>
-      <c r="T26" s="260" t="s">
+      <c r="S26" s="248" t="s">
+        <v>45</v>
+      </c>
+      <c r="T26" s="259" t="s">
         <v>48</v>
       </c>
       <c r="U26" s="224" t="s">
@@ -26408,7 +26462,7 @@
       <c r="Y26" s="238" t="s">
         <v>48</v>
       </c>
-      <c r="Z26" s="239" t="s">
+      <c r="Z26" s="248" t="s">
         <v>44</v>
       </c>
       <c r="AA26" s="231" t="s">
@@ -26426,7 +26480,7 @@
       <c r="AE26" s="238" t="s">
         <v>48</v>
       </c>
-      <c r="AF26" s="255" t="s">
+      <c r="AF26" s="254" t="s">
         <v>47</v>
       </c>
       <c r="AG26" s="25"/>
@@ -26472,7 +26526,7 @@
       <c r="A27" s="232" t="s">
         <v>255</v>
       </c>
-      <c r="B27" s="262" t="s">
+      <c r="B27" s="261" t="s">
         <v>125</v>
       </c>
       <c r="C27" s="272" t="s">
@@ -26502,7 +26556,7 @@
       <c r="K27" s="228" t="s">
         <v>45</v>
       </c>
-      <c r="L27" s="252" t="s">
+      <c r="L27" s="251" t="s">
         <v>43</v>
       </c>
       <c r="M27" s="269" t="s">
@@ -26523,7 +26577,7 @@
       <c r="R27" s="228" t="s">
         <v>47</v>
       </c>
-      <c r="S27" s="239" t="s">
+      <c r="S27" s="248" t="s">
         <v>44</v>
       </c>
       <c r="T27" s="231" t="s">
@@ -26544,7 +26598,7 @@
       <c r="Y27" s="236" t="s">
         <v>47</v>
       </c>
-      <c r="Z27" s="239" t="s">
+      <c r="Z27" s="248" t="s">
         <v>45</v>
       </c>
       <c r="AA27" s="226" t="s">
@@ -26562,7 +26616,7 @@
       <c r="AE27" s="227" t="s">
         <v>45</v>
       </c>
-      <c r="AF27" s="239" t="s">
+      <c r="AF27" s="248" t="s">
         <v>43</v>
       </c>
       <c r="AG27" s="25"/>
@@ -26611,13 +26665,13 @@
       <c r="B28" s="222" t="s">
         <v>128</v>
       </c>
-      <c r="C28" s="256" t="s">
+      <c r="C28" s="255" t="s">
         <v>53</v>
       </c>
       <c r="D28" s="224" t="s">
         <v>53</v>
       </c>
-      <c r="E28" s="251" t="s">
+      <c r="E28" s="250" t="s">
         <v>46</v>
       </c>
       <c r="F28" s="231" t="s">
@@ -26638,7 +26692,7 @@
       <c r="K28" s="224" t="s">
         <v>53</v>
       </c>
-      <c r="L28" s="255" t="s">
+      <c r="L28" s="254" t="s">
         <v>47</v>
       </c>
       <c r="M28" s="231" t="s">
@@ -26659,7 +26713,7 @@
       <c r="R28" s="224" t="s">
         <v>53</v>
       </c>
-      <c r="S28" s="255" t="s">
+      <c r="S28" s="254" t="s">
         <v>47</v>
       </c>
       <c r="T28" s="231" t="s">
@@ -26680,7 +26734,7 @@
       <c r="Y28" s="224" t="s">
         <v>53</v>
       </c>
-      <c r="Z28" s="255" t="s">
+      <c r="Z28" s="254" t="s">
         <v>47</v>
       </c>
       <c r="AA28" s="269" t="s">
@@ -26753,7 +26807,7 @@
       <c r="D29" s="227" t="s">
         <v>44</v>
       </c>
-      <c r="E29" s="251" t="s">
+      <c r="E29" s="250" t="s">
         <v>43</v>
       </c>
       <c r="F29" s="235" t="s">
@@ -26774,7 +26828,7 @@
       <c r="K29" s="227" t="s">
         <v>44</v>
       </c>
-      <c r="L29" s="239" t="s">
+      <c r="L29" s="248" t="s">
         <v>43</v>
       </c>
       <c r="M29" s="235" t="s">
@@ -26795,7 +26849,7 @@
       <c r="R29" s="227" t="s">
         <v>45</v>
       </c>
-      <c r="S29" s="252" t="s">
+      <c r="S29" s="251" t="s">
         <v>43</v>
       </c>
       <c r="T29" s="235" t="s">
@@ -26816,7 +26870,7 @@
       <c r="Y29" s="237" t="s">
         <v>49</v>
       </c>
-      <c r="Z29" s="247" t="s">
+      <c r="Z29" s="268" t="s">
         <v>49</v>
       </c>
       <c r="AA29" s="235" t="s">
@@ -26834,7 +26888,7 @@
       <c r="AE29" s="227" t="s">
         <v>45</v>
       </c>
-      <c r="AF29" s="239" t="s">
+      <c r="AF29" s="248" t="s">
         <v>43</v>
       </c>
       <c r="AG29" s="25"/>
@@ -26883,7 +26937,7 @@
       <c r="B30" s="222" t="s">
         <v>134</v>
       </c>
-      <c r="C30" s="248" t="s">
+      <c r="C30" s="246" t="s">
         <v>49</v>
       </c>
       <c r="D30" s="224" t="s">
@@ -27025,7 +27079,7 @@
       <c r="D31" s="227" t="s">
         <v>44</v>
       </c>
-      <c r="E31" s="251" t="s">
+      <c r="E31" s="250" t="s">
         <v>43</v>
       </c>
       <c r="F31" s="235" t="s">
@@ -27046,7 +27100,7 @@
       <c r="K31" s="227" t="s">
         <v>44</v>
       </c>
-      <c r="L31" s="239" t="s">
+      <c r="L31" s="248" t="s">
         <v>43</v>
       </c>
       <c r="M31" s="235" t="s">
@@ -27067,7 +27121,7 @@
       <c r="R31" s="227" t="s">
         <v>45</v>
       </c>
-      <c r="S31" s="252" t="s">
+      <c r="S31" s="251" t="s">
         <v>43</v>
       </c>
       <c r="T31" s="235" t="s">
@@ -27088,7 +27142,7 @@
       <c r="Y31" s="237" t="s">
         <v>49</v>
       </c>
-      <c r="Z31" s="247" t="s">
+      <c r="Z31" s="268" t="s">
         <v>49</v>
       </c>
       <c r="AA31" s="235" t="s">
@@ -27106,7 +27160,7 @@
       <c r="AE31" s="227" t="s">
         <v>45</v>
       </c>
-      <c r="AF31" s="239" t="s">
+      <c r="AF31" s="248" t="s">
         <v>44</v>
       </c>
       <c r="AG31" s="25"/>
@@ -27161,7 +27215,7 @@
       <c r="D32" s="227" t="s">
         <v>47</v>
       </c>
-      <c r="E32" s="251" t="s">
+      <c r="E32" s="250" t="s">
         <v>45</v>
       </c>
       <c r="F32" s="235" t="s">
@@ -27182,7 +27236,7 @@
       <c r="K32" s="227" t="s">
         <v>45</v>
       </c>
-      <c r="L32" s="239" t="s">
+      <c r="L32" s="248" t="s">
         <v>45</v>
       </c>
       <c r="M32" s="235" t="s">
@@ -27203,7 +27257,7 @@
       <c r="R32" s="227" t="s">
         <v>44</v>
       </c>
-      <c r="S32" s="239" t="s">
+      <c r="S32" s="248" t="s">
         <v>44</v>
       </c>
       <c r="T32" s="235" t="s">
@@ -27224,7 +27278,7 @@
       <c r="Y32" s="227" t="s">
         <v>45</v>
       </c>
-      <c r="Z32" s="239" t="s">
+      <c r="Z32" s="248" t="s">
         <v>45</v>
       </c>
       <c r="AA32" s="235" t="s">
@@ -27242,7 +27296,7 @@
       <c r="AE32" s="227" t="s">
         <v>47</v>
       </c>
-      <c r="AF32" s="239" t="s">
+      <c r="AF32" s="248" t="s">
         <v>45</v>
       </c>
       <c r="AG32" s="25"/>
@@ -27291,16 +27345,16 @@
       <c r="B33" s="222" t="s">
         <v>143</v>
       </c>
-      <c r="C33" s="248" t="s">
+      <c r="C33" s="246" t="s">
         <v>49</v>
       </c>
       <c r="D33" s="237" t="s">
         <v>49</v>
       </c>
-      <c r="E33" s="253" t="s">
+      <c r="E33" s="252" t="s">
         <v>49</v>
       </c>
-      <c r="F33" s="260" t="s">
+      <c r="F33" s="259" t="s">
         <v>48</v>
       </c>
       <c r="G33" s="224" t="s">
@@ -27318,10 +27372,10 @@
       <c r="K33" s="238" t="s">
         <v>48</v>
       </c>
-      <c r="L33" s="250" t="s">
+      <c r="L33" s="249" t="s">
         <v>48</v>
       </c>
-      <c r="M33" s="260" t="s">
+      <c r="M33" s="259" t="s">
         <v>48</v>
       </c>
       <c r="N33" s="224" t="s">
@@ -27330,13 +27384,13 @@
       <c r="O33" s="224" t="s">
         <v>53</v>
       </c>
-      <c r="P33" s="242" t="s">
-        <v>47</v>
-      </c>
-      <c r="Q33" s="242" t="s">
-        <v>47</v>
-      </c>
-      <c r="R33" s="242" t="s">
+      <c r="P33" s="241" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q33" s="241" t="s">
+        <v>47</v>
+      </c>
+      <c r="R33" s="241" t="s">
         <v>47</v>
       </c>
       <c r="S33" s="273" t="s">
@@ -27351,13 +27405,13 @@
       <c r="V33" s="224" t="s">
         <v>53</v>
       </c>
-      <c r="W33" s="242" t="s">
-        <v>47</v>
-      </c>
-      <c r="X33" s="242" t="s">
-        <v>47</v>
-      </c>
-      <c r="Y33" s="242" t="s">
+      <c r="W33" s="241" t="s">
+        <v>47</v>
+      </c>
+      <c r="X33" s="241" t="s">
+        <v>47</v>
+      </c>
+      <c r="Y33" s="241" t="s">
         <v>47</v>
       </c>
       <c r="Z33" s="273" t="s">
@@ -27372,10 +27426,10 @@
       <c r="AC33" s="224" t="s">
         <v>53</v>
       </c>
-      <c r="AD33" s="242" t="s">
-        <v>47</v>
-      </c>
-      <c r="AE33" s="242" t="s">
+      <c r="AD33" s="241" t="s">
+        <v>47</v>
+      </c>
+      <c r="AE33" s="241" t="s">
         <v>47</v>
       </c>
       <c r="AF33" s="273" t="s">
@@ -27427,13 +27481,13 @@
       <c r="B34" s="222" t="s">
         <v>146</v>
       </c>
-      <c r="C34" s="256" t="s">
+      <c r="C34" s="255" t="s">
         <v>53</v>
       </c>
       <c r="D34" s="227" t="s">
         <v>46</v>
       </c>
-      <c r="E34" s="251" t="s">
+      <c r="E34" s="250" t="s">
         <v>45</v>
       </c>
       <c r="F34" s="231" t="s">
@@ -27454,7 +27508,7 @@
       <c r="K34" s="236" t="s">
         <v>47</v>
       </c>
-      <c r="L34" s="239" t="s">
+      <c r="L34" s="248" t="s">
         <v>46</v>
       </c>
       <c r="M34" s="231" t="s">
@@ -27475,7 +27529,7 @@
       <c r="R34" s="236" t="s">
         <v>47</v>
       </c>
-      <c r="S34" s="239" t="s">
+      <c r="S34" s="248" t="s">
         <v>47</v>
       </c>
       <c r="T34" s="231" t="s">
@@ -27496,7 +27550,7 @@
       <c r="Y34" s="236" t="s">
         <v>47</v>
       </c>
-      <c r="Z34" s="239" t="s">
+      <c r="Z34" s="248" t="s">
         <v>45</v>
       </c>
       <c r="AA34" s="231" t="s">
@@ -27514,7 +27568,7 @@
       <c r="AE34" s="224" t="s">
         <v>53</v>
       </c>
-      <c r="AF34" s="239" t="s">
+      <c r="AF34" s="248" t="s">
         <v>45</v>
       </c>
       <c r="AG34" s="25" t="s">
@@ -27592,7 +27646,7 @@
       <c r="K35" s="227" t="s">
         <v>45</v>
       </c>
-      <c r="L35" s="239" t="s">
+      <c r="L35" s="248" t="s">
         <v>45</v>
       </c>
       <c r="M35" s="231" t="s">
@@ -27613,7 +27667,7 @@
       <c r="R35" s="227" t="s">
         <v>45</v>
       </c>
-      <c r="S35" s="239" t="s">
+      <c r="S35" s="248" t="s">
         <v>45</v>
       </c>
       <c r="T35" s="231" t="s">
@@ -27634,7 +27688,7 @@
       <c r="Y35" s="227" t="s">
         <v>45</v>
       </c>
-      <c r="Z35" s="239" t="s">
+      <c r="Z35" s="248" t="s">
         <v>45</v>
       </c>
       <c r="AA35" s="231" t="s">
@@ -27652,7 +27706,7 @@
       <c r="AE35" s="227" t="s">
         <v>45</v>
       </c>
-      <c r="AF35" s="239" t="s">
+      <c r="AF35" s="248" t="s">
         <v>45</v>
       </c>
       <c r="AG35" s="25"/>
@@ -27701,13 +27755,13 @@
       <c r="B36" s="222" t="s">
         <v>153</v>
       </c>
-      <c r="C36" s="263" t="s">
-        <v>45</v>
-      </c>
-      <c r="D36" s="244" t="s">
-        <v>45</v>
-      </c>
-      <c r="E36" s="251" t="s">
+      <c r="C36" s="262" t="s">
+        <v>45</v>
+      </c>
+      <c r="D36" s="243" t="s">
+        <v>45</v>
+      </c>
+      <c r="E36" s="250" t="s">
         <v>44</v>
       </c>
       <c r="F36" s="231" t="s">
@@ -27728,7 +27782,7 @@
       <c r="K36" s="227" t="s">
         <v>45</v>
       </c>
-      <c r="L36" s="239" t="s">
+      <c r="L36" s="248" t="s">
         <v>44</v>
       </c>
       <c r="M36" s="226" t="s">
@@ -27740,16 +27794,16 @@
       <c r="O36" s="224" t="s">
         <v>53</v>
       </c>
-      <c r="P36" s="242" t="s">
-        <v>47</v>
-      </c>
-      <c r="Q36" s="242" t="s">
+      <c r="P36" s="241" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q36" s="241" t="s">
         <v>47</v>
       </c>
       <c r="R36" s="227" t="s">
         <v>45</v>
       </c>
-      <c r="S36" s="239" t="s">
+      <c r="S36" s="248" t="s">
         <v>45</v>
       </c>
       <c r="T36" s="226" t="s">
@@ -27761,16 +27815,16 @@
       <c r="V36" s="224" t="s">
         <v>53</v>
       </c>
-      <c r="W36" s="242" t="s">
-        <v>47</v>
-      </c>
-      <c r="X36" s="242" t="s">
+      <c r="W36" s="241" t="s">
+        <v>47</v>
+      </c>
+      <c r="X36" s="241" t="s">
         <v>47</v>
       </c>
       <c r="Y36" s="227" t="s">
         <v>45</v>
       </c>
-      <c r="Z36" s="239" t="s">
+      <c r="Z36" s="248" t="s">
         <v>44</v>
       </c>
       <c r="AA36" s="231" t="s">
@@ -27785,10 +27839,10 @@
       <c r="AD36" s="236" t="s">
         <v>47</v>
       </c>
-      <c r="AE36" s="244" t="s">
+      <c r="AE36" s="243" t="s">
         <v>46</v>
       </c>
-      <c r="AF36" s="239" t="s">
+      <c r="AF36" s="248" t="s">
         <v>45</v>
       </c>
       <c r="AG36" s="25"/>
@@ -27843,7 +27897,7 @@
       <c r="D37" s="227" t="s">
         <v>43</v>
       </c>
-      <c r="E37" s="251" t="s">
+      <c r="E37" s="250" t="s">
         <v>43</v>
       </c>
       <c r="F37" s="235" t="s">
@@ -27864,7 +27918,7 @@
       <c r="K37" s="228" t="s">
         <v>43</v>
       </c>
-      <c r="L37" s="252" t="s">
+      <c r="L37" s="251" t="s">
         <v>43</v>
       </c>
       <c r="M37" s="235" t="s">
@@ -27885,7 +27939,7 @@
       <c r="R37" s="227" t="s">
         <v>43</v>
       </c>
-      <c r="S37" s="252" t="s">
+      <c r="S37" s="251" t="s">
         <v>43</v>
       </c>
       <c r="T37" s="235" t="s">
@@ -27906,7 +27960,7 @@
       <c r="Y37" s="227" t="s">
         <v>43</v>
       </c>
-      <c r="Z37" s="239" t="s">
+      <c r="Z37" s="248" t="s">
         <v>43</v>
       </c>
       <c r="AA37" s="235" t="s">
@@ -27924,7 +27978,7 @@
       <c r="AE37" s="227" t="s">
         <v>47</v>
       </c>
-      <c r="AF37" s="239" t="s">
+      <c r="AF37" s="248" t="s">
         <v>43</v>
       </c>
       <c r="AG37" s="25"/>
@@ -27970,7 +28024,7 @@
       <c r="A38" s="232" t="s">
         <v>266</v>
       </c>
-      <c r="B38" s="262" t="s">
+      <c r="B38" s="261" t="s">
         <v>159</v>
       </c>
       <c r="C38" s="275" t="s">
@@ -27979,7 +28033,7 @@
       <c r="D38" s="227" t="s">
         <v>45</v>
       </c>
-      <c r="E38" s="251" t="s">
+      <c r="E38" s="250" t="s">
         <v>44</v>
       </c>
       <c r="F38" s="231" t="s">
@@ -28000,7 +28054,7 @@
       <c r="K38" s="227" t="s">
         <v>45</v>
       </c>
-      <c r="L38" s="239" t="s">
+      <c r="L38" s="248" t="s">
         <v>45</v>
       </c>
       <c r="M38" s="231" t="s">
@@ -28021,7 +28075,7 @@
       <c r="R38" s="227" t="s">
         <v>46</v>
       </c>
-      <c r="S38" s="239" t="s">
+      <c r="S38" s="248" t="s">
         <v>45</v>
       </c>
       <c r="T38" s="231" t="s">
@@ -28042,7 +28096,7 @@
       <c r="Y38" s="227" t="s">
         <v>45</v>
       </c>
-      <c r="Z38" s="247" t="s">
+      <c r="Z38" s="268" t="s">
         <v>49</v>
       </c>
       <c r="AA38" s="226" t="s">
@@ -28060,7 +28114,7 @@
       <c r="AE38" s="227" t="s">
         <v>46</v>
       </c>
-      <c r="AF38" s="239" t="s">
+      <c r="AF38" s="248" t="s">
         <v>47</v>
       </c>
       <c r="AG38" s="25"/>
@@ -28115,7 +28169,7 @@
       <c r="D39" s="228" t="s">
         <v>45</v>
       </c>
-      <c r="E39" s="253" t="s">
+      <c r="E39" s="252" t="s">
         <v>49</v>
       </c>
       <c r="F39" s="235" t="s">
@@ -28136,7 +28190,7 @@
       <c r="K39" s="227" t="s">
         <v>44</v>
       </c>
-      <c r="L39" s="252" t="s">
+      <c r="L39" s="251" t="s">
         <v>43</v>
       </c>
       <c r="M39" s="235" t="s">
@@ -28157,7 +28211,7 @@
       <c r="R39" s="227" t="s">
         <v>45</v>
       </c>
-      <c r="S39" s="247" t="s">
+      <c r="S39" s="268" t="s">
         <v>49</v>
       </c>
       <c r="T39" s="235" t="s">
@@ -28178,7 +28232,7 @@
       <c r="Y39" s="227" t="s">
         <v>44</v>
       </c>
-      <c r="Z39" s="252" t="s">
+      <c r="Z39" s="251" t="s">
         <v>43</v>
       </c>
       <c r="AA39" s="235" t="s">
@@ -28196,7 +28250,7 @@
       <c r="AE39" s="227" t="s">
         <v>43</v>
       </c>
-      <c r="AF39" s="239" t="s">
+      <c r="AF39" s="248" t="s">
         <v>43</v>
       </c>
       <c r="AG39" s="25"/>
@@ -28251,7 +28305,7 @@
       <c r="D40" s="227" t="s">
         <v>45</v>
       </c>
-      <c r="E40" s="251" t="s">
+      <c r="E40" s="250" t="s">
         <v>45</v>
       </c>
       <c r="F40" s="231" t="s">
@@ -28272,7 +28326,7 @@
       <c r="K40" s="227" t="s">
         <v>45</v>
       </c>
-      <c r="L40" s="239" t="s">
+      <c r="L40" s="248" t="s">
         <v>45</v>
       </c>
       <c r="M40" s="231" t="s">
@@ -28293,7 +28347,7 @@
       <c r="R40" s="227" t="s">
         <v>43</v>
       </c>
-      <c r="S40" s="247" t="s">
+      <c r="S40" s="268" t="s">
         <v>49</v>
       </c>
       <c r="T40" s="231" t="s">
@@ -28314,7 +28368,7 @@
       <c r="Y40" s="227" t="s">
         <v>45</v>
       </c>
-      <c r="Z40" s="239" t="s">
+      <c r="Z40" s="248" t="s">
         <v>45</v>
       </c>
       <c r="AA40" s="231" t="s">
@@ -28332,7 +28386,7 @@
       <c r="AE40" s="236" t="s">
         <v>47</v>
       </c>
-      <c r="AF40" s="239" t="s">
+      <c r="AF40" s="248" t="s">
         <v>47</v>
       </c>
       <c r="AG40" s="25"/>
@@ -28381,13 +28435,13 @@
       <c r="B41" s="222" t="s">
         <v>168</v>
       </c>
-      <c r="C41" s="256" t="s">
+      <c r="C41" s="255" t="s">
         <v>53</v>
       </c>
       <c r="D41" s="224" t="s">
         <v>53</v>
       </c>
-      <c r="E41" s="251" t="s">
+      <c r="E41" s="250" t="s">
         <v>46</v>
       </c>
       <c r="F41" s="231" t="s">
@@ -28408,7 +28462,7 @@
       <c r="K41" s="224" t="s">
         <v>53</v>
       </c>
-      <c r="L41" s="239" t="s">
+      <c r="L41" s="248" t="s">
         <v>46</v>
       </c>
       <c r="M41" s="231" t="s">
@@ -28429,7 +28483,7 @@
       <c r="R41" s="224" t="s">
         <v>53</v>
       </c>
-      <c r="S41" s="239" t="s">
+      <c r="S41" s="248" t="s">
         <v>46</v>
       </c>
       <c r="T41" s="231" t="s">
@@ -28450,7 +28504,7 @@
       <c r="Y41" s="224" t="s">
         <v>53</v>
       </c>
-      <c r="Z41" s="239" t="s">
+      <c r="Z41" s="248" t="s">
         <v>46</v>
       </c>
       <c r="AA41" s="231" t="s">
@@ -28517,7 +28571,7 @@
       <c r="B42" s="222" t="s">
         <v>171</v>
       </c>
-      <c r="C42" s="256" t="s">
+      <c r="C42" s="255" t="s">
         <v>53</v>
       </c>
       <c r="D42" s="236" t="s">
@@ -28565,7 +28619,7 @@
       <c r="R42" s="236" t="s">
         <v>47</v>
       </c>
-      <c r="S42" s="252" t="s">
+      <c r="S42" s="251" t="s">
         <v>45</v>
       </c>
       <c r="T42" s="277" t="s">
@@ -28604,7 +28658,7 @@
       <c r="AE42" s="224" t="s">
         <v>53</v>
       </c>
-      <c r="AF42" s="255" t="s">
+      <c r="AF42" s="254" t="s">
         <v>47</v>
       </c>
       <c r="AG42" s="25"/>
@@ -28653,13 +28707,13 @@
       <c r="B43" s="222" t="s">
         <v>174</v>
       </c>
-      <c r="C43" s="256" t="s">
+      <c r="C43" s="255" t="s">
         <v>53</v>
       </c>
       <c r="D43" s="236" t="s">
         <v>47</v>
       </c>
-      <c r="E43" s="251" t="s">
+      <c r="E43" s="250" t="s">
         <v>45</v>
       </c>
       <c r="F43" s="231" t="s">
@@ -28680,7 +28734,7 @@
       <c r="K43" s="227" t="s">
         <v>45</v>
       </c>
-      <c r="L43" s="239" t="s">
+      <c r="L43" s="248" t="s">
         <v>45</v>
       </c>
       <c r="M43" s="231" t="s">
@@ -28701,7 +28755,7 @@
       <c r="R43" s="227" t="s">
         <v>43</v>
       </c>
-      <c r="S43" s="239" t="s">
+      <c r="S43" s="248" t="s">
         <v>43</v>
       </c>
       <c r="T43" s="231" t="s">
@@ -28722,7 +28776,7 @@
       <c r="Y43" s="228" t="s">
         <v>45</v>
       </c>
-      <c r="Z43" s="239" t="s">
+      <c r="Z43" s="248" t="s">
         <v>43</v>
       </c>
       <c r="AA43" s="231" t="s">
@@ -28740,7 +28794,7 @@
       <c r="AE43" s="224" t="s">
         <v>53</v>
       </c>
-      <c r="AF43" s="239" t="s">
+      <c r="AF43" s="248" t="s">
         <v>45</v>
       </c>
       <c r="AG43" s="25"/>
@@ -28786,16 +28840,16 @@
       <c r="A44" s="232" t="s">
         <v>272</v>
       </c>
-      <c r="B44" s="262" t="s">
+      <c r="B44" s="261" t="s">
         <v>177</v>
       </c>
-      <c r="C44" s="246" t="s">
+      <c r="C44" s="245" t="s">
         <v>47</v>
       </c>
       <c r="D44" s="227" t="s">
         <v>47</v>
       </c>
-      <c r="E44" s="251" t="s">
+      <c r="E44" s="250" t="s">
         <v>45</v>
       </c>
       <c r="F44" s="231" t="s">
@@ -28816,7 +28870,7 @@
       <c r="K44" s="227" t="s">
         <v>46</v>
       </c>
-      <c r="L44" s="239" t="s">
+      <c r="L44" s="248" t="s">
         <v>44</v>
       </c>
       <c r="M44" s="226" t="s">
@@ -28837,7 +28891,7 @@
       <c r="R44" s="237" t="s">
         <v>49</v>
       </c>
-      <c r="S44" s="247" t="s">
+      <c r="S44" s="268" t="s">
         <v>49</v>
       </c>
       <c r="T44" s="226" t="s">
@@ -28858,10 +28912,10 @@
       <c r="Y44" s="228" t="s">
         <v>44</v>
       </c>
-      <c r="Z44" s="250" t="s">
+      <c r="Z44" s="249" t="s">
         <v>48</v>
       </c>
-      <c r="AA44" s="260" t="s">
+      <c r="AA44" s="259" t="s">
         <v>48</v>
       </c>
       <c r="AB44" s="238" t="s">
@@ -28876,7 +28930,7 @@
       <c r="AE44" s="227" t="s">
         <v>45</v>
       </c>
-      <c r="AF44" s="239" t="s">
+      <c r="AF44" s="248" t="s">
         <v>44</v>
       </c>
       <c r="AG44" s="25"/>
@@ -28922,16 +28976,16 @@
       <c r="A45" s="281" t="s">
         <v>273</v>
       </c>
-      <c r="B45" s="253" t="s">
+      <c r="B45" s="252" t="s">
         <v>180</v>
       </c>
-      <c r="C45" s="256" t="s">
+      <c r="C45" s="255" t="s">
         <v>53</v>
       </c>
       <c r="D45" s="237" t="s">
         <v>49</v>
       </c>
-      <c r="E45" s="253" t="s">
+      <c r="E45" s="252" t="s">
         <v>49</v>
       </c>
       <c r="F45" s="226" t="s">
@@ -28994,7 +29048,7 @@
       <c r="Y45" s="234" t="s">
         <v>47</v>
       </c>
-      <c r="Z45" s="239" t="s">
+      <c r="Z45" s="248" t="s">
         <v>47</v>
       </c>
       <c r="AA45" s="231" t="s">
@@ -29012,7 +29066,7 @@
       <c r="AE45" s="224" t="s">
         <v>53</v>
       </c>
-      <c r="AF45" s="247" t="s">
+      <c r="AF45" s="268" t="s">
         <v>49</v>
       </c>
       <c r="AG45" s="112"/>
@@ -29058,7 +29112,7 @@
       <c r="A46" s="282" t="s">
         <v>274</v>
       </c>
-      <c r="B46" s="253" t="s">
+      <c r="B46" s="252" t="s">
         <v>275</v>
       </c>
       <c r="C46" s="283" t="s">
@@ -30421,7 +30475,7 @@
       </c>
       <c r="AF56" s="327">
         <f t="shared" si="59"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG56" s="193"/>
       <c r="AH56" s="20"/>
@@ -30561,7 +30615,7 @@
       </c>
       <c r="AF57" s="327">
         <f t="shared" si="60"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AG57" s="193"/>
       <c r="AH57" s="20"/>
@@ -43088,7 +43142,7 @@
         <v>48</v>
       </c>
       <c r="AF5" s="340" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="AG5" s="339"/>
       <c r="AH5" s="339"/>
@@ -43388,7 +43442,7 @@
         <v>44</v>
       </c>
       <c r="AF8" s="340" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="AG8" s="339"/>
       <c r="AH8" s="339"/>
@@ -49619,7 +49673,7 @@
         <v>3.0</v>
       </c>
       <c r="AE9" s="351">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="10">
@@ -49714,7 +49768,7 @@
         <v>0.0</v>
       </c>
       <c r="AE10" s="351">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="11">
@@ -52319,7 +52373,7 @@
         <v>48</v>
       </c>
       <c r="AF5" s="340" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="AG5" s="339"/>
       <c r="AH5" s="339"/>
@@ -52619,7 +52673,7 @@
         <v>44</v>
       </c>
       <c r="AF8" s="340" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="AG8" s="339"/>
       <c r="AH8" s="339"/>

--- a/uploads/ORIGINAL7.xlsx
+++ b/uploads/ORIGINAL7.xlsx
@@ -24547,7 +24547,7 @@
         <v>47</v>
       </c>
       <c r="W12" s="227" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="X12" s="227" t="s">
         <v>43</v>
@@ -24579,11 +24579,11 @@
       <c r="AG12" s="25"/>
       <c r="AH12" s="47">
         <f t="shared" si="2"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AI12" s="48">
         <f t="shared" si="3"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AJ12" s="48">
         <f t="shared" si="4"/>
@@ -24599,7 +24599,7 @@
       </c>
       <c r="AM12" s="51">
         <f t="shared" si="7"/>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AN12" s="52">
         <f t="shared" ref="AN12:AO12" si="14">COUNTIF($C12:$AF12,"PH")</f>
@@ -25496,10 +25496,10 @@
         <v>45</v>
       </c>
       <c r="V19" s="227" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="W19" s="227" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="X19" s="224" t="s">
         <v>53</v>
@@ -25531,11 +25531,11 @@
       <c r="AG19" s="25"/>
       <c r="AH19" s="47">
         <f t="shared" si="2"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AI19" s="48">
         <f t="shared" si="3"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AJ19" s="48">
         <f t="shared" si="4"/>
@@ -25543,15 +25543,15 @@
       </c>
       <c r="AK19" s="49">
         <f t="shared" si="5"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AL19" s="50">
         <f t="shared" si="6"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AM19" s="51">
         <f t="shared" si="7"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AN19" s="52">
         <f t="shared" ref="AN19:AO19" si="21">COUNTIF($C19:$AF19,"PH")</f>
@@ -26992,7 +26992,7 @@
         <v>46</v>
       </c>
       <c r="V30" s="227" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="W30" s="227" t="s">
         <v>46</v>
@@ -27039,11 +27039,11 @@
       </c>
       <c r="AK30" s="49">
         <f t="shared" si="5"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AL30" s="50">
         <f t="shared" si="6"/>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AM30" s="51">
         <f t="shared" si="7"/>
@@ -43612,7 +43612,7 @@
         <v>47</v>
       </c>
       <c r="W10" s="339" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="X10" s="339" t="s">
         <v>43</v>
@@ -44309,10 +44309,10 @@
         <v>45</v>
       </c>
       <c r="V17" s="339" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="W17" s="339" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="X17" s="339" t="s">
         <v>53</v>
@@ -45409,7 +45409,7 @@
         <v>46</v>
       </c>
       <c r="V28" s="339" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="W28" s="339" t="s">
         <v>46</v>
@@ -52843,7 +52843,7 @@
         <v>47</v>
       </c>
       <c r="W10" s="339" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="X10" s="339" t="s">
         <v>43</v>
@@ -53540,10 +53540,10 @@
         <v>45</v>
       </c>
       <c r="V17" s="339" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="W17" s="339" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="X17" s="339" t="s">
         <v>53</v>
@@ -54640,7 +54640,7 @@
         <v>46</v>
       </c>
       <c r="V28" s="339" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="W28" s="339" t="s">
         <v>46</v>

--- a/uploads/ORIGINAL7.xlsx
+++ b/uploads/ORIGINAL7.xlsx
@@ -25704,7 +25704,7 @@
         <v>228</v>
       </c>
       <c r="O18" s="214" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="P18" s="214" t="s">
         <v>230</v>
@@ -25772,7 +25772,7 @@
       </c>
       <c r="AK18" s="49">
         <f t="shared" si="5"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AL18" s="50">
         <f t="shared" si="6"/>
@@ -25780,7 +25780,7 @@
       </c>
       <c r="AM18" s="51">
         <f t="shared" si="7"/>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AN18" s="52">
         <f t="shared" ref="AN18:AO18" si="20">COUNTIF($C18:$AF18,"PH")</f>
@@ -26779,8 +26779,8 @@
       <c r="J26" s="219" t="s">
         <v>229</v>
       </c>
-      <c r="K26" s="219" t="s">
-        <v>228</v>
+      <c r="K26" s="237" t="s">
+        <v>253</v>
       </c>
       <c r="L26" s="214" t="s">
         <v>231</v>
@@ -26868,7 +26868,7 @@
       </c>
       <c r="AM26" s="51">
         <f t="shared" si="7"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AN26" s="52">
         <f t="shared" ref="AN26:AO26" si="28">COUNTIF($C26:$AF26,"PH")</f>
@@ -26931,7 +26931,7 @@
         <v>47</v>
       </c>
       <c r="P27" s="214" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q27" s="219" t="s">
         <v>228</v>
@@ -27000,11 +27000,11 @@
       </c>
       <c r="AL27" s="50">
         <f t="shared" si="6"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AM27" s="51">
         <f t="shared" si="7"/>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AN27" s="52">
         <f t="shared" ref="AN27:AO27" si="29">COUNTIF($C27:$AF27,"PH")</f>
@@ -27336,7 +27336,7 @@
         <v>229</v>
       </c>
       <c r="O30" s="214" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="P30" s="214" t="s">
         <v>227</v>
@@ -27404,7 +27404,7 @@
       </c>
       <c r="AK30" s="49">
         <f t="shared" si="5"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AL30" s="50">
         <f t="shared" si="6"/>
@@ -27412,7 +27412,7 @@
       </c>
       <c r="AM30" s="51">
         <f t="shared" si="7"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AN30" s="52">
         <f t="shared" ref="AN30:AO30" si="32">COUNTIF($C30:$AF30,"PH")</f>
@@ -27611,7 +27611,7 @@
         <v>229</v>
       </c>
       <c r="P32" s="214" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="Q32" s="214" t="s">
         <v>228</v>
@@ -27680,11 +27680,11 @@
       </c>
       <c r="AL32" s="50">
         <f t="shared" si="6"/>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AM32" s="51">
         <f t="shared" si="7"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AN32" s="52">
         <f t="shared" ref="AN32:AO32" si="34">COUNTIF($C32:$AF32,"PH")</f>
@@ -29911,7 +29911,7 @@
       </c>
       <c r="K50" s="266">
         <f t="shared" si="48"/>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L50" s="267">
         <f t="shared" si="48"/>
@@ -31021,7 +31021,7 @@
       </c>
       <c r="K58" s="275">
         <f t="shared" si="61"/>
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L58" s="276">
         <f t="shared" si="61"/>
@@ -44541,7 +44541,7 @@
         <v>228</v>
       </c>
       <c r="O16" s="283" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="P16" s="283" t="s">
         <v>230</v>
@@ -45328,8 +45328,8 @@
       <c r="J24" s="282" t="s">
         <v>229</v>
       </c>
-      <c r="K24" s="282" t="s">
-        <v>228</v>
+      <c r="K24" s="283" t="s">
+        <v>253</v>
       </c>
       <c r="L24" s="283" t="s">
         <v>231</v>
@@ -45444,7 +45444,7 @@
         <v>47</v>
       </c>
       <c r="P25" s="283" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q25" s="282" t="s">
         <v>228</v>
@@ -45741,7 +45741,7 @@
         <v>229</v>
       </c>
       <c r="O28" s="283" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="P28" s="283" t="s">
         <v>227</v>
@@ -45944,7 +45944,7 @@
         <v>229</v>
       </c>
       <c r="P30" s="283" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="Q30" s="283" t="s">
         <v>228</v>
@@ -49388,7 +49388,7 @@
         <v>6.0</v>
       </c>
       <c r="J3" s="282">
-        <v>6.0</v>
+        <v>5.0</v>
       </c>
       <c r="K3" s="294">
         <v>5.0</v>
@@ -50138,7 +50138,7 @@
         <v>25.0</v>
       </c>
       <c r="J11" s="297">
-        <v>24.0</v>
+        <v>23.0</v>
       </c>
       <c r="K11" s="298">
         <v>23.0</v>
@@ -53760,7 +53760,7 @@
         <v>228</v>
       </c>
       <c r="O16" s="283" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="P16" s="283" t="s">
         <v>230</v>
@@ -54547,8 +54547,8 @@
       <c r="J24" s="282" t="s">
         <v>229</v>
       </c>
-      <c r="K24" s="282" t="s">
-        <v>228</v>
+      <c r="K24" s="283" t="s">
+        <v>253</v>
       </c>
       <c r="L24" s="283" t="s">
         <v>231</v>
@@ -54663,7 +54663,7 @@
         <v>47</v>
       </c>
       <c r="P25" s="283" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q25" s="282" t="s">
         <v>228</v>
@@ -54960,7 +54960,7 @@
         <v>229</v>
       </c>
       <c r="O28" s="283" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="P28" s="283" t="s">
         <v>227</v>
@@ -55163,7 +55163,7 @@
         <v>229</v>
       </c>
       <c r="P30" s="283" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="Q30" s="283" t="s">
         <v>228</v>
